--- a/exemples_risk_intelligence/ECOBANK_Executive_Report_2026-09-30.xlsx
+++ b/exemples_risk_intelligence/ECOBANK_Executive_Report_2026-09-30.xlsx
@@ -12,7 +12,7 @@
     <sheet name="_data" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'EXECUTIVE'!$A$1:$X$82</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'EXECUTIVE'!$A$1:$X$89</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[&gt;=1000000000]#,##0.00,,,&quot; Md&quot;;[&gt;=1000000]#,##0.0,,&quot; M&quot;;#,##0"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="47">
     <font>
       <sz val="10"/>
       <color rgb="FF0F172A"/>
@@ -38,47 +38,40 @@
     </font>
     <font>
       <b/>
-      <sz val="8"/>
+      <sz val="7.5"/>
       <color rgb="FFC8A951"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="17"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFE0EAFF"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FF003DA5"/>
+      <sz val="8.5"/>
+      <color rgb="FFE0EAFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7.5"/>
+      <color rgb="FFBFD3FF"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="21"/>
+      <sz val="22"/>
       <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="7.5"/>
       <color rgb="FFD6E4FF"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -91,21 +84,14 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="7.5"/>
-      <color rgb="FFD6E4FF"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
-      <sz val="21"/>
+      <sz val="22"/>
       <color rgb="FF001B4D"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="7.5"/>
       <color rgb="FF64748B"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -114,13 +100,6 @@
       <b/>
       <sz val="9.5"/>
       <color rgb="FFDC2626"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="7.5"/>
-      <color rgb="FF64748B"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -147,6 +126,27 @@
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF001B4D"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFDC2626"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF2563EB"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF001B4D"/>
       <name val="Segoe UI"/>
@@ -156,12 +156,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFDC2626"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="7.5"/>
-      <color rgb="FF64748B"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -180,6 +174,13 @@
       <family val="2"/>
     </font>
     <font>
+      <i/>
+      <sz val="7.5"/>
+      <color rgb="FF64748B"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
@@ -190,13 +191,6 @@
       <b/>
       <sz val="7.5"/>
       <color rgb="FFDC2626"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -254,7 +248,7 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9.5"/>
       <color rgb="FF334155"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -267,8 +261,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF334155"/>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF001B4D"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -290,6 +285,26 @@
       <b/>
       <sz val="18"/>
       <color rgb="FF16A34A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF2563EB"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF06B6D4"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF334155"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -327,7 +342,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -366,13 +381,29 @@
           <color rgb="FFC8A951"/>
         </stop>
         <stop position="1">
-          <color rgb="FFE9D9A6"/>
+          <color rgb="FFF3E7BF"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color rgb="FF003DA5"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FF2563EB"/>
         </stop>
       </gradientFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF2FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -387,10 +418,34 @@
       </gradientFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <gradientFill degree="0">
+        <stop position="0">
+          <color rgb="FFC9D5EA"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color rgb="FFC9D5EA"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFEAF2FF"/>
+        </stop>
+      </gradientFill>
     </fill>
     <fill>
       <gradientFill degree="45">
@@ -399,6 +454,16 @@
         </stop>
         <stop position="1">
           <color rgb="FF06B6D4"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="0">
+        <stop position="0">
+          <color rgb="FFD5DEEE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFFFFFFF"/>
         </stop>
       </gradientFill>
     </fill>
@@ -433,6 +498,76 @@
       </patternFill>
     </fill>
     <fill>
+      <gradientFill degree="0">
+        <stop position="0">
+          <color rgb="FFDC2626"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFEF9D9D"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="0">
+        <stop position="0">
+          <color rgb="FFC8A951"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFE6D8B1"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="0">
+        <stop position="0">
+          <color rgb="FFF97316"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFFCC096"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="0">
+        <stop position="0">
+          <color rgb="FFF59E0B"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFFBD391"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="0">
+        <stop position="0">
+          <color rgb="FF16A34A"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FF96D6AE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="0">
+        <stop position="0">
+          <color rgb="FF2563EB"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FF9DB9F6"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="0">
+        <stop position="0">
+          <color rgb="FF06B6D4"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FF8FDEEC"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F7FF"/>
         <bgColor indexed="64"/>
@@ -445,7 +580,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -476,6 +611,47 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFDBE6F7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDBE6F7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDBE6F7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDBE6F7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDBE6F7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFC8A951"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF003DA5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thick">
         <color rgb="FFC8A951"/>
       </left>
@@ -487,8 +663,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFC8A951"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF003DA5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF06B6D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
       <top style="thin">
-        <color rgb="FFC7D7F5"/>
+        <color rgb="FFDBE6F7"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -497,7 +695,55 @@
       <left style="thick">
         <color rgb="FF06B6D4"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF06B6D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDBE6F7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFF59E0B"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDBE6F7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFF59E0B"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -506,7 +752,35 @@
       <left style="thick">
         <color rgb="FFF59E0B"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDBE6F7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFF97316"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDBE6F7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFF97316"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -515,8 +789,97 @@
       <left style="thick">
         <color rgb="FFF97316"/>
       </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDBE6F7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFDC2626"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDBE6F7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFDC2626"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFDC2626"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDBE6F7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFC8A951"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDBE6F7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFC8A951"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFC8A951"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDBE6F7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFDC2626"/>
+      </left>
       <right/>
-      <top/>
+      <top style="thin">
+        <color rgb="FF003DA5"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -530,10 +893,84 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thick">
+        <color rgb="FFDC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF003DA5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDBE6F7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFC8A951"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDBE6F7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDBE6F7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDBE6F7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDBE6F7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFDC2626"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDBE6F7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF2563EB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF003DA5"/>
       </bottom>
       <diagonal/>
@@ -542,7 +979,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FFC8A951"/>
       </bottom>
       <diagonal/>
@@ -551,7 +988,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF06B6D4"/>
       </bottom>
       <diagonal/>
@@ -560,7 +997,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FFDC2626"/>
       </bottom>
       <diagonal/>
@@ -602,21 +1039,52 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFDBE6F7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FFDBE6F7"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color rgb="FF16A34A"/>
+      <left style="thin">
+        <color rgb="FFDBE6F7"/>
       </left>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFDBE6F7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDBE6F7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC8A951"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -632,8 +1100,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF16A34A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2563EB"/>
       </bottom>
       <diagonal/>
     </border>
@@ -641,7 +1118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -652,6 +1129,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="2"/>
     </xf>
@@ -659,321 +1139,387 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="25" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="27" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="26" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="25" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="25" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="25" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="27" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="15" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1013,12 +1559,12 @@
             <a:gradFill rotWithShape="1">
               <a:gsLst>
                 <a:gs pos="0">
-                  <a:srgbClr val="3B82F6">
+                  <a:srgbClr val="60A5FA">
                     <a:alpha val="55000"/>
                   </a:srgbClr>
                 </a:gs>
                 <a:gs pos="100000">
-                  <a:srgbClr val="3B82F6">
+                  <a:srgbClr val="60A5FA">
                     <a:alpha val="8000"/>
                   </a:srgbClr>
                 </a:gs>
@@ -1027,7 +1573,7 @@
             </a:gradFill>
             <a:ln w="22225" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="3B82F6"/>
+                <a:srgbClr val="60A5FA"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1639,10 +2185,8 @@
     <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9525">
-      <a:solidFill>
-        <a:srgbClr val="DBE6F7"/>
-      </a:solidFill>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
   </c:spPr>
   <c:txPr>
@@ -1830,10 +2374,8 @@
     <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9525">
-      <a:solidFill>
-        <a:srgbClr val="DBE6F7"/>
-      </a:solidFill>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
   </c:spPr>
   <c:txPr>
@@ -2368,10 +2910,8 @@
     <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9525">
-      <a:solidFill>
-        <a:srgbClr val="DBE6F7"/>
-      </a:solidFill>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
   </c:spPr>
   <c:txPr>
@@ -2395,13 +2935,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2425,13 +2965,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2455,13 +2995,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2490,54 +3030,72 @@
     <tabColor rgb="FF003DA5"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X82"/>
+  <dimension ref="A1:Y89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.4" customWidth="1"/>
-    <col min="2" max="2" width="5.4" customWidth="1"/>
-    <col min="3" max="3" width="5.4" customWidth="1"/>
-    <col min="4" max="4" width="5.4" customWidth="1"/>
-    <col min="5" max="5" width="5.4" customWidth="1"/>
-    <col min="6" max="6" width="5.4" customWidth="1"/>
-    <col min="7" max="7" width="5.4" customWidth="1"/>
-    <col min="8" max="8" width="5.4" customWidth="1"/>
-    <col min="9" max="9" width="5.4" customWidth="1"/>
-    <col min="10" max="10" width="5.4" customWidth="1"/>
-    <col min="11" max="11" width="5.4" customWidth="1"/>
-    <col min="12" max="12" width="5.4" customWidth="1"/>
-    <col min="13" max="13" width="5.4" customWidth="1"/>
-    <col min="14" max="14" width="5.4" customWidth="1"/>
-    <col min="15" max="15" width="5.4" customWidth="1"/>
-    <col min="16" max="16" width="5.4" customWidth="1"/>
-    <col min="17" max="17" width="5.4" customWidth="1"/>
-    <col min="18" max="18" width="5.4" customWidth="1"/>
-    <col min="19" max="19" width="5.4" customWidth="1"/>
-    <col min="20" max="20" width="5.4" customWidth="1"/>
-    <col min="21" max="21" width="5.4" customWidth="1"/>
-    <col min="22" max="22" width="5.4" customWidth="1"/>
-    <col min="23" max="23" width="5.4" customWidth="1"/>
-    <col min="24" max="24" width="5.4" customWidth="1"/>
+    <col min="1" max="1" width="6.1" customWidth="1"/>
+    <col min="2" max="2" width="6.1" customWidth="1"/>
+    <col min="3" max="3" width="6.1" customWidth="1"/>
+    <col min="4" max="4" width="6.1" customWidth="1"/>
+    <col min="5" max="5" width="1.6" customWidth="1"/>
+    <col min="6" max="6" width="6.1" customWidth="1"/>
+    <col min="7" max="7" width="6.1" customWidth="1"/>
+    <col min="8" max="8" width="6.1" customWidth="1"/>
+    <col min="9" max="9" width="6.1" customWidth="1"/>
+    <col min="10" max="10" width="1.6" customWidth="1"/>
+    <col min="11" max="11" width="6.1" customWidth="1"/>
+    <col min="12" max="12" width="6.1" customWidth="1"/>
+    <col min="13" max="13" width="6.1" customWidth="1"/>
+    <col min="14" max="14" width="6.1" customWidth="1"/>
+    <col min="15" max="15" width="1.6" customWidth="1"/>
+    <col min="16" max="16" width="6.1" customWidth="1"/>
+    <col min="17" max="17" width="6.1" customWidth="1"/>
+    <col min="18" max="18" width="6.1" customWidth="1"/>
+    <col min="19" max="19" width="6.1" customWidth="1"/>
+    <col min="20" max="20" width="1.6" customWidth="1"/>
+    <col min="21" max="21" width="6.1" customWidth="1"/>
+    <col min="22" max="22" width="6.1" customWidth="1"/>
+    <col min="23" max="23" width="6.1" customWidth="1"/>
+    <col min="24" max="24" width="6.1" customWidth="1"/>
+    <col min="25" max="25" width="1.6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
-              <b/>
               <color rgb="FFC8A951"/>
-              <sz val="9"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">◆ </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="8.5"/>
             </rPr>
             <t xml:space="preserve">ECOBANK SÉNÉGAL</t>
           </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
-              <color rgb="FFC7D7F5"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">   ·   CREDIT RISK INTELLIGENCE</t>
+              <color rgb="FF9DB4E0"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">   ·   CREDIT RISK INTELLIGENCE   ·   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFFFFFFF"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">EXECUTIVE</t>
           </r>
         </is>
       </c>
@@ -2564,7 +3122,7 @@
             <rPr>
               <rFont val="Segoe UI"/>
               <color rgb="FF8EA6D6"/>
-              <sz val="8"/>
+              <sz val="7.5"/>
             </rPr>
             <t xml:space="preserve">INTERNAL USE ONLY  ·  </t>
           </r>
@@ -2573,27 +3131,37 @@
               <rFont val="Segoe UI"/>
               <b/>
               <color rgb="FFC8A951"/>
-              <sz val="8"/>
+              <sz val="7.5"/>
             </rPr>
             <t xml:space="preserve">RI 1.0</t>
           </r>
         </is>
       </c>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+    </row>
+    <row r="2" ht="10" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
               <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">E C O B A N K   S É N É G A L
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
               <color rgb="FFFFFFFF"/>
-              <sz val="22"/>
+              <sz val="26"/>
             </rPr>
             <t xml:space="preserve">CREDIT RISK INTELLIGENCE
 </t>
@@ -2602,19 +3170,9 @@
             <rPr>
               <rFont val="Segoe UI"/>
               <color rgb="FFC7D7F5"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Portfolio Monitoring &amp; Early Warning · Vue Comité des Risques
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b/>
-              <color rgb="FFC8A951"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">ECOBANK SÉNÉGAL · DIRECTION DES RISQUES</t>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">Portfolio Monitoring &amp; Early Warning  ·  Vue Comité des Risques</t>
           </r>
         </is>
       </c>
@@ -2632,11 +3190,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
-      <c r="P2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REPORTING DATE</t>
-        </is>
-      </c>
+      <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
@@ -2646,7 +3200,7 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -2664,7 +3218,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/09/2026</t>
+          <t xml:space="preserve">REPORTING DATE</t>
         </is>
       </c>
       <c r="Q3" s="5"/>
@@ -2676,7 +3230,7 @@
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2692,21 +3246,21 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PERIMETER</t>
-        </is>
-      </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 SEPTEMBER 2026</t>
+        </is>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2722,64 +3276,60 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORTFOLIO MONITORING</t>
+        </is>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Portefeuille Ecobank Sénégal · 700 clients · 2 500 lignes ACTE 7</t>
         </is>
       </c>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-    </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EXECUTIVE</t>
-        </is>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INSIGHTS</t>
-        </is>
-      </c>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+    </row>
+    <row r="7" ht="2.5" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
@@ -2787,11 +3337,7 @@
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
-      <c r="Q7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AUDIT</t>
-        </is>
-      </c>
+      <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
       <c r="T7" s="9"/>
@@ -2800,16 +3346,14 @@
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
     </row>
-    <row r="8" ht="8" customHeight="1"/>
-    <row r="9" ht="6" customHeight="1"/>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="8" ht="23" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
               <color rgb="FFC8A951"/>
-              <sz val="8"/>
+              <sz val="8.5"/>
             </rPr>
             <t xml:space="preserve">◆  </t>
           </r>
@@ -2817,23 +3361,254 @@
             <rPr>
               <rFont val="Segoe UI"/>
               <b/>
+              <color rgb="FFFFFFFF"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">EXECUTIVE</t>
+          </r>
+        </is>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FF7C93C9"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">✦  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF003DA5"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">INSIGHTS</t>
+          </r>
+        </is>
+      </c>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FF7C93C9"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">§  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF003DA5"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">AUDIT</t>
+          </r>
+        </is>
+      </c>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+    </row>
+    <row r="9" ht="5" customHeight="1"/>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFF97316"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">● </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">PORTFOLIO STATUS  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">VIGILANCE</t>
+          </r>
+        </is>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFF59E0B"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">● </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">JEV · PD 12M  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">3,8 % · MARKOV</t>
+          </r>
+        </is>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FF06B6D4"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">● </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">TYPESAFE  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">24 retours · 8 en revue</t>
+          </r>
+        </is>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FF16A34A"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">● </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">CONTRÔLES  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">10 / 10 conformes</t>
+          </r>
+        </is>
+      </c>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+    </row>
+    <row r="11" ht="10" customHeight="1"/>
+    <row r="12" ht="6" customHeight="1"/>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFC8A951"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">◆  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
               <color rgb="FFE6EEFF"/>
-              <sz val="8"/>
+              <sz val="7.5"/>
             </rPr>
             <t xml:space="preserve">TOTAL EXPOSURE</t>
           </r>
         </is>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
               <color rgb="FF06B6D4"/>
-              <sz val="8"/>
+              <sz val="9"/>
             </rPr>
             <t xml:space="preserve">●  </t>
           </r>
@@ -2842,22 +3617,22 @@
               <rFont val="Segoe UI"/>
               <b/>
               <color rgb="FF334155"/>
-              <sz val="8"/>
+              <sz val="7.5"/>
             </rPr>
             <t xml:space="preserve">TOTAL ARREARS</t>
           </r>
         </is>
       </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="K13" s="28" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
               <color rgb="FFF59E0B"/>
-              <sz val="8"/>
+              <sz val="9"/>
             </rPr>
             <t xml:space="preserve">◔  </t>
           </r>
@@ -2866,22 +3641,22 @@
               <rFont val="Segoe UI"/>
               <b/>
               <color rgb="FF334155"/>
-              <sz val="8"/>
+              <sz val="7.5"/>
             </rPr>
             <t xml:space="preserve">31–60 DAYS</t>
           </r>
         </is>
       </c>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="P10" s="29" t="inlineStr">
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="P13" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
               <color rgb="FFF97316"/>
-              <sz val="8"/>
+              <sz val="9"/>
             </rPr>
             <t xml:space="preserve">◑  </t>
           </r>
@@ -2890,22 +3665,22 @@
               <rFont val="Segoe UI"/>
               <b/>
               <color rgb="FF334155"/>
-              <sz val="8"/>
+              <sz val="7.5"/>
             </rPr>
             <t xml:space="preserve">61–90 DAYS</t>
           </r>
         </is>
       </c>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="U10" s="34" t="inlineStr">
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
+      <c r="U13" s="39" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
               <color rgb="FFDC2626"/>
-              <sz val="8"/>
+              <sz val="9"/>
             </rPr>
             <t xml:space="preserve">●  </t>
           </r>
@@ -2914,229 +3689,775 @@
               <rFont val="Segoe UI"/>
               <b/>
               <color rgb="FF334155"/>
-              <sz val="8"/>
+              <sz val="7.5"/>
             </rPr>
             <t xml:space="preserve">&gt; 90 DAYS / S3</t>
           </r>
         </is>
       </c>
-      <c r="V10" s="34"/>
-      <c r="W10" s="34"/>
-      <c r="X10" s="34"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="11">
+      <c r="V13" s="39"/>
+      <c r="W13" s="39"/>
+      <c r="X13" s="39"/>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="15">
         <v>850385585746</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="F11" s="18">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="23">
         <v>31893133004</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="K11" s="24">
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="29">
         <v>86369133509</v>
       </c>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="P11" s="30">
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="35">
         <v>0</v>
       </c>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="U11" s="35">
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="40">
         <v>323775211401</v>
       </c>
-      <c r="V11" s="35"/>
-      <c r="W11" s="35"/>
-      <c r="X11" s="35"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="35"/>
-      <c r="W12" s="35"/>
-      <c r="X12" s="35"/>
-    </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">XOF · encours brut · 700 clients</t>
-        </is>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">XOF · impayés · 547 clients</t>
-        </is>
-      </c>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="K13" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">XOF · encours · 84 clients</t>
-        </is>
-      </c>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="P13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">XOF · encours · 0 clients</t>
-        </is>
-      </c>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="U13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">XOF · encours · 264 clients</t>
-        </is>
-      </c>
-      <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="36"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">■ 0,0 %</t>
-        </is>
-      </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">▲ 1,1 %</t>
-        </is>
-      </c>
-      <c r="G14" s="20"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="K14" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">▼ -3,5 %</t>
-        </is>
-      </c>
-      <c r="L14" s="26"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="P14" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="U14" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">▲ 1,1 %</t>
-        </is>
-      </c>
-      <c r="V14" s="37"/>
-      <c r="W14" s="27"/>
-      <c r="X14" s="27"/>
-    </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vs 31/08/2026</t>
-        </is>
-      </c>
+      <c r="V14" s="40"/>
+      <c r="W14" s="40"/>
+      <c r="X14" s="40"/>
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="15"/>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vs 31/08/2026</t>
-        </is>
-      </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="K15" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vs 31/08/2026</t>
-        </is>
-      </c>
-      <c r="L15" s="28"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="28"/>
-      <c r="P15" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vs 31/08/2026</t>
-        </is>
-      </c>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="U15" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vs 31/08/2026</t>
-        </is>
-      </c>
-      <c r="V15" s="38"/>
-      <c r="W15" s="38"/>
-      <c r="X15" s="38"/>
-    </row>
-    <row r="16" ht="8" customHeight="1">
-      <c r="A16" s="16"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="40"/>
+      <c r="Y15" s="20"/>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XOF · encours brut · 700 clients</t>
+        </is>
+      </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-    </row>
-    <row r="17" ht="10" customHeight="1"/>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="E16" s="20"/>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XOF · impayés · 547 clients</t>
+        </is>
+      </c>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XOF · encours · 84 clients</t>
+        </is>
+      </c>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XOF · encours · 0 clients</t>
+        </is>
+      </c>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
+      <c r="S16" s="36"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XOF · encours · 264 clients</t>
+        </is>
+      </c>
+      <c r="V16" s="41"/>
+      <c r="W16" s="41"/>
+      <c r="X16" s="41"/>
+      <c r="Y16" s="20"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">■ 0,0 %</t>
+        </is>
+      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">▲ 1,1 %</t>
+        </is>
+      </c>
+      <c r="G17" s="25"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">▼ -3,5 %</t>
+        </is>
+      </c>
+      <c r="L17" s="31"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Q17" s="37"/>
+      <c r="R17" s="26"/>
+      <c r="S17" s="26"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">▲ 1,1 %</t>
+        </is>
+      </c>
+      <c r="V17" s="42"/>
+      <c r="W17" s="32"/>
+      <c r="X17" s="32"/>
+      <c r="Y17" s="20"/>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <i/>
+              <color rgb="FFD6E4FF"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">vs 31/08/2026   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF86EFAC"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">● FAVORABLE</t>
+          </r>
+        </is>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="27" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <i/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">vs 31/08/2026   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFF59E0B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">● À SURVEILLER</t>
+          </r>
+        </is>
+      </c>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="33" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <i/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">vs 31/08/2026   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF16A34A"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">● FAVORABLE</t>
+          </r>
+        </is>
+      </c>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="38" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <i/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">vs 31/08/2026   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="38"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="43" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <i/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">vs 31/08/2026   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFF59E0B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">● À SURVEILLER</t>
+          </r>
+        </is>
+      </c>
+      <c r="V18" s="43"/>
+      <c r="W18" s="43"/>
+      <c r="X18" s="43"/>
+      <c r="Y18" s="20"/>
+    </row>
+    <row r="19" ht="5" customHeight="1">
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="20"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="20"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="20"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="20"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="21"/>
+      <c r="Y19" s="20"/>
+    </row>
+    <row r="20" ht="10" customHeight="1"/>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
               <color rgb="FFC8A951"/>
-              <sz val="8"/>
+              <sz val="9"/>
             </rPr>
             <t xml:space="preserve">▲  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t xml:space="preserve">STAGE 2</t>
+          </r>
+        </is>
+      </c>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="F21" s="39" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFDC2626"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">▲  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t xml:space="preserve">STAGE 3</t>
+          </r>
+        </is>
+      </c>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="K21" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFC8A951"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">◆  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFE6EEFF"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t xml:space="preserve">PROVISIONS (ECL)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="49"/>
+      <c r="P21" s="55" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFF59E0B"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">◉  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t xml:space="preserve">WATCHLIST</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="55"/>
+      <c r="U21" s="60" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFC8A951"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">■  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFE6EEFF"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t xml:space="preserve">CRITICAL EXPOSURES</t>
+          </r>
+        </is>
+      </c>
+      <c r="V21" s="60"/>
+      <c r="W21" s="60"/>
+      <c r="X21" s="60"/>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="45">
+        <v>259457540560</v>
+      </c>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="40">
+        <v>323775211401</v>
+      </c>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="50">
+        <v>37319879435</v>
+      </c>
+      <c r="L22" s="50"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="56">
+        <v>289</v>
+      </c>
+      <c r="Q22" s="56"/>
+      <c r="R22" s="56"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="61">
+        <v>3489258395</v>
+      </c>
+      <c r="V22" s="61"/>
+      <c r="W22" s="61"/>
+      <c r="X22" s="61"/>
+      <c r="Y22" s="20"/>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="45"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="56"/>
+      <c r="Q23" s="56"/>
+      <c r="R23" s="56"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="61"/>
+      <c r="V23" s="61"/>
+      <c r="W23" s="61"/>
+      <c r="X23" s="61"/>
+      <c r="Y23" s="20"/>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XOF · 30,5 % de l'encours</t>
+        </is>
+      </c>
+      <c r="B24" s="46"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XOF · 38,1 % de l'encours</t>
+        </is>
+      </c>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XOF · couverture 4,4 %</t>
+        </is>
+      </c>
+      <c r="L24" s="51"/>
+      <c r="M24" s="51"/>
+      <c r="N24" s="51"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dossiers · 322,71 Md XOF</t>
+        </is>
+      </c>
+      <c r="Q24" s="57"/>
+      <c r="R24" s="57"/>
+      <c r="S24" s="57"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XOF · 6 dossiers critiques</t>
+        </is>
+      </c>
+      <c r="V24" s="62"/>
+      <c r="W24" s="62"/>
+      <c r="X24" s="62"/>
+      <c r="Y24" s="20"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">▼ -0,4 %</t>
+        </is>
+      </c>
+      <c r="B25" s="47"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">▲ 1,1 %</t>
+        </is>
+      </c>
+      <c r="G25" s="42"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">▲ 0,5 %</t>
+        </is>
+      </c>
+      <c r="L25" s="52"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Q25" s="58"/>
+      <c r="R25" s="26"/>
+      <c r="S25" s="26"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="V25" s="63"/>
+      <c r="W25" s="18"/>
+      <c r="X25" s="18"/>
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <i/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">vs 31/08/2026   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF16A34A"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">● FAVORABLE</t>
+          </r>
+        </is>
+      </c>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="43" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <i/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">vs 31/08/2026   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFF59E0B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">● À SURVEILLER</t>
+          </r>
+        </is>
+      </c>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="54" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <i/>
+              <color rgb="FFD6E4FF"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">vs 31/08/2026   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFD6E4FF"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">● STABLE</t>
+          </r>
+        </is>
+      </c>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="59" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <i/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">vs 31/08/2026   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="Q26" s="59"/>
+      <c r="R26" s="59"/>
+      <c r="S26" s="59"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="64" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <i/>
+              <color rgb="FFD6E4FF"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">vs 31/08/2026   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFD6E4FF"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve"/>
+          </r>
+        </is>
+      </c>
+      <c r="V26" s="64"/>
+      <c r="W26" s="64"/>
+      <c r="X26" s="64"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" ht="5" customHeight="1">
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="20"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="20"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="20"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="21"/>
+      <c r="T27" s="20"/>
+      <c r="V27" s="21"/>
+      <c r="W27" s="21"/>
+      <c r="X27" s="21"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" ht="12" customHeight="1"/>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="65" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">⚠  </t>
           </r>
           <r>
             <rPr>
@@ -3145,20 +4466,26 @@
               <color rgb="FF334155"/>
               <sz val="8"/>
             </rPr>
-            <t xml:space="preserve">STAGE 2</t>
-          </r>
-        </is>
-      </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="F18" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
+            <t xml:space="preserve">CONCENTRATION ALERT</t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="65"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="65"/>
+      <c r="K29" s="69" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
               <color rgb="FFDC2626"/>
-              <sz val="8"/>
+              <sz val="10"/>
             </rPr>
             <t xml:space="preserve">▲  </t>
           </r>
@@ -3169,46 +4496,28 @@
               <color rgb="FF334155"/>
               <sz val="8"/>
             </rPr>
-            <t xml:space="preserve">STAGE 3</t>
-          </r>
-        </is>
-      </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="K18" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <color rgb="FFC8A951"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">◆  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b/>
-              <color rgb="FFE6EEFF"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">PROVISIONS (ECL)</t>
-          </r>
-        </is>
-      </c>
-      <c r="L18" s="44"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="44"/>
-      <c r="P18" s="50" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <color rgb="FFF59E0B"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">◉  </t>
+            <t xml:space="preserve">NEW ARREARS</t>
+          </r>
+        </is>
+      </c>
+      <c r="L29" s="69"/>
+      <c r="M29" s="69"/>
+      <c r="N29" s="69"/>
+      <c r="O29" s="69"/>
+      <c r="P29" s="69"/>
+      <c r="Q29" s="69"/>
+      <c r="R29" s="69"/>
+      <c r="S29" s="69"/>
+      <c r="U29" s="71" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF2563EB"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">✦  </t>
           </r>
           <r>
             <rPr>
@@ -3217,243 +4526,109 @@
               <color rgb="FF334155"/>
               <sz val="8"/>
             </rPr>
-            <t xml:space="preserve">WATCHLIST</t>
-          </r>
-        </is>
-      </c>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="50"/>
-      <c r="S18" s="50"/>
-      <c r="U18" s="55" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
+            <t xml:space="preserve">JEV OUTLOOK</t>
+          </r>
+        </is>
+      </c>
+      <c r="V29" s="71"/>
+      <c r="W29" s="71"/>
+      <c r="X29" s="71"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOP 5 CLIENTS = 4,4 %</t>
+        </is>
+      </c>
+      <c r="B30" s="66"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="68"/>
+      <c r="K30" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+333,3 M XOF</t>
+        </is>
+      </c>
+      <c r="L30" s="70"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="70"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="70"/>
+      <c r="Q30" s="70"/>
+      <c r="R30" s="70"/>
+      <c r="S30" s="70"/>
+      <c r="T30" s="68"/>
+      <c r="U30" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PD 12M 3,8 %</t>
+        </is>
+      </c>
+      <c r="V30" s="72"/>
+      <c r="W30" s="72"/>
+      <c r="X30" s="72"/>
+      <c r="Y30" s="68"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+0,0 pts vs 31/08/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nouveaux impayés et aggravations · aucune régularisation sur la période</t>
+        </is>
+      </c>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="67"/>
+      <c r="S31" s="67"/>
+      <c r="T31" s="68"/>
+      <c r="U31" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARKOV · confiance faible · indicatif</t>
+        </is>
+      </c>
+      <c r="V31" s="67"/>
+      <c r="W31" s="67"/>
+      <c r="X31" s="67"/>
+      <c r="Y31" s="68"/>
+    </row>
+    <row r="32">
+      <c r="J32" s="68"/>
+      <c r="T32" s="68"/>
+      <c r="Y32" s="68"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="73" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
               <color rgb="FFC8A951"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">■  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b/>
-              <color rgb="FFE6EEFF"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">CRITICAL EXPOSURES</t>
-          </r>
-        </is>
-      </c>
-      <c r="V18" s="55"/>
-      <c r="W18" s="55"/>
-      <c r="X18" s="55"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="40">
-        <v>259457540560</v>
-      </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="F19" s="35">
-        <v>323775211401</v>
-      </c>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="K19" s="45">
-        <v>37319879435</v>
-      </c>
-      <c r="L19" s="45"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="P19" s="51">
-        <v>289</v>
-      </c>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="51"/>
-      <c r="S19" s="51"/>
-      <c r="U19" s="56">
-        <v>3489258395</v>
-      </c>
-      <c r="V19" s="56"/>
-      <c r="W19" s="56"/>
-      <c r="X19" s="56"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="45"/>
-      <c r="N20" s="45"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="51"/>
-      <c r="R20" s="51"/>
-      <c r="S20" s="51"/>
-      <c r="U20" s="56"/>
-      <c r="V20" s="56"/>
-      <c r="W20" s="56"/>
-      <c r="X20" s="56"/>
-    </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">XOF · 30,5 % de l'encours</t>
-        </is>
-      </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="F21" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">XOF · 38,1 % de l'encours</t>
-        </is>
-      </c>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="K21" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">XOF · couverture 4,4 %</t>
-        </is>
-      </c>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
-      <c r="P21" s="52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dossiers · 322,71 Md XOF</t>
-        </is>
-      </c>
-      <c r="Q21" s="52"/>
-      <c r="R21" s="52"/>
-      <c r="S21" s="52"/>
-      <c r="U21" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">XOF · 6 dossiers critiques</t>
-        </is>
-      </c>
-      <c r="V21" s="57"/>
-      <c r="W21" s="57"/>
-      <c r="X21" s="57"/>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">▼ -0,4 %</t>
-        </is>
-      </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="F22" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">▲ 1,1 %</t>
-        </is>
-      </c>
-      <c r="G22" s="37"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="K22" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">▲ 0,5 %</t>
-        </is>
-      </c>
-      <c r="L22" s="47"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="48"/>
-      <c r="P22" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="Q22" s="53"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="21"/>
-      <c r="U22" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="V22" s="58"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-    </row>
-    <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vs 31/08/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="F23" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vs 31/08/2026</t>
-        </is>
-      </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="K23" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vs 31/08/2026</t>
-        </is>
-      </c>
-      <c r="L23" s="49"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="49"/>
-      <c r="P23" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vs 31/08/2026</t>
-        </is>
-      </c>
-      <c r="Q23" s="54"/>
-      <c r="R23" s="54"/>
-      <c r="S23" s="54"/>
-      <c r="U23" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vs 31/08/2026</t>
-        </is>
-      </c>
-      <c r="V23" s="59"/>
-      <c r="W23" s="59"/>
-      <c r="X23" s="59"/>
-    </row>
-    <row r="24" ht="8" customHeight="1">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="60" t="inlineStr">
-        <is>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">01  </t>
+          </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
@@ -3466,29 +4641,39 @@
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
+              <i/>
               <color rgb="FF64748B"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">   encours (aire) · impayés, Stage 2, Stage 3 (courbes, axe droit)</t>
-          </r>
-        </is>
-      </c>
-      <c r="B26" s="60"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="60"/>
-      <c r="J26" s="60"/>
-      <c r="K26" s="60"/>
-      <c r="L26" s="60"/>
-      <c r="M26" s="60"/>
-      <c r="N26" s="60"/>
-      <c r="O26" s="60"/>
-      <c r="Q26" s="61" t="inlineStr">
-        <is>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">    encours (aire) · impayés, Stage 2, Stage 3 (courbes, axe droit)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B33" s="73"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="73"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="73"/>
+      <c r="O33" s="73"/>
+      <c r="Q33" s="74" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">·  </t>
+          </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
@@ -3501,24 +4686,34 @@
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
+              <i/>
               <color rgb="FF64748B"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">   encours par stage IFRS 9</t>
-          </r>
-        </is>
-      </c>
-      <c r="R26" s="61"/>
-      <c r="S26" s="61"/>
-      <c r="T26" s="61"/>
-      <c r="U26" s="61"/>
-      <c r="V26" s="61"/>
-      <c r="W26" s="61"/>
-      <c r="X26" s="61"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="62" t="inlineStr">
-        <is>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">    encours par stage IFRS 9</t>
+          </r>
+        </is>
+      </c>
+      <c r="R33" s="74"/>
+      <c r="S33" s="74"/>
+      <c r="T33" s="74"/>
+      <c r="U33" s="74"/>
+      <c r="V33" s="74"/>
+      <c r="W33" s="74"/>
+      <c r="X33" s="74"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="75" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">02  </t>
+          </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
@@ -3531,29 +4726,39 @@
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
+              <i/>
               <color rgb="FF64748B"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">   pont des impayés 31/08/2026 → 30/09/2026</t>
-          </r>
-        </is>
-      </c>
-      <c r="B43" s="62"/>
-      <c r="C43" s="62"/>
-      <c r="D43" s="62"/>
-      <c r="E43" s="62"/>
-      <c r="F43" s="62"/>
-      <c r="G43" s="62"/>
-      <c r="H43" s="62"/>
-      <c r="I43" s="62"/>
-      <c r="J43" s="62"/>
-      <c r="K43" s="62"/>
-      <c r="L43" s="62"/>
-      <c r="M43" s="62"/>
-      <c r="N43" s="62"/>
-      <c r="O43" s="62"/>
-      <c r="Q43" s="62" t="inlineStr">
-        <is>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">    pont des impayés 31/08/2026 → 30/09/2026</t>
+          </r>
+        </is>
+      </c>
+      <c r="B50" s="75"/>
+      <c r="C50" s="75"/>
+      <c r="D50" s="75"/>
+      <c r="E50" s="75"/>
+      <c r="F50" s="75"/>
+      <c r="G50" s="75"/>
+      <c r="H50" s="75"/>
+      <c r="I50" s="75"/>
+      <c r="J50" s="75"/>
+      <c r="K50" s="75"/>
+      <c r="L50" s="75"/>
+      <c r="M50" s="75"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="75"/>
+      <c r="Q50" s="75" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">·  </t>
+          </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
@@ -3566,248 +4771,258 @@
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
+              <i/>
               <color rgb="FF64748B"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">   plus fortes variations d'impayés</t>
-          </r>
-        </is>
-      </c>
-      <c r="R43" s="62"/>
-      <c r="S43" s="62"/>
-      <c r="T43" s="62"/>
-      <c r="U43" s="62"/>
-      <c r="V43" s="62"/>
-      <c r="W43" s="62"/>
-      <c r="X43" s="62"/>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="Q44" s="63" t="inlineStr">
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">    plus fortes variations d'impayés</t>
+          </r>
+        </is>
+      </c>
+      <c r="R50" s="75"/>
+      <c r="S50" s="75"/>
+      <c r="T50" s="75"/>
+      <c r="U50" s="75"/>
+      <c r="V50" s="75"/>
+      <c r="W50" s="75"/>
+      <c r="X50" s="75"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="Q51" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">SOCIETE 0403</t>
         </is>
       </c>
-      <c r="R44" s="63"/>
-      <c r="S44" s="63"/>
-      <c r="T44" s="63"/>
-      <c r="U44" s="63"/>
-      <c r="V44" s="64" t="inlineStr">
+      <c r="R51" s="76"/>
+      <c r="S51" s="76"/>
+      <c r="T51" s="76"/>
+      <c r="U51" s="76"/>
+      <c r="V51" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">+280,1 M</t>
         </is>
       </c>
-      <c r="W44" s="64"/>
-      <c r="X44" s="64"/>
-    </row>
-    <row r="45" ht="13" customHeight="1">
-      <c r="Q45" s="65" t="inlineStr">
+      <c r="W51" s="77"/>
+      <c r="X51" s="77"/>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="Q52" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">459,0 M XOF d'impayés · 33 j · Stage 2 · GUEYE</t>
         </is>
       </c>
-      <c r="R45" s="65"/>
-      <c r="S45" s="65"/>
-      <c r="T45" s="65"/>
-      <c r="U45" s="65"/>
-      <c r="V45" s="65"/>
-      <c r="W45" s="65"/>
-      <c r="X45" s="65"/>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="Q46" s="63" t="inlineStr">
+      <c r="R52" s="78"/>
+      <c r="S52" s="78"/>
+      <c r="T52" s="78"/>
+      <c r="U52" s="78"/>
+      <c r="V52" s="78"/>
+      <c r="W52" s="78"/>
+      <c r="X52" s="78"/>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="Q53" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">SOCIETE 0666</t>
         </is>
       </c>
-      <c r="R46" s="63"/>
-      <c r="S46" s="63"/>
-      <c r="T46" s="63"/>
-      <c r="U46" s="63"/>
-      <c r="V46" s="64" t="inlineStr">
+      <c r="R53" s="76"/>
+      <c r="S53" s="76"/>
+      <c r="T53" s="76"/>
+      <c r="U53" s="76"/>
+      <c r="V53" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">+29,5 M</t>
         </is>
       </c>
-      <c r="W46" s="64"/>
-      <c r="X46" s="64"/>
-    </row>
-    <row r="47" ht="13" customHeight="1">
-      <c r="Q47" s="65" t="inlineStr">
+      <c r="W53" s="77"/>
+      <c r="X53" s="77"/>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="Q54" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">30,2 M XOF d'impayés · 308 j · Stage 3 · GUEYE</t>
         </is>
       </c>
-      <c r="R47" s="65"/>
-      <c r="S47" s="65"/>
-      <c r="T47" s="65"/>
-      <c r="U47" s="65"/>
-      <c r="V47" s="65"/>
-      <c r="W47" s="65"/>
-      <c r="X47" s="65"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="Q48" s="63" t="inlineStr">
+      <c r="R54" s="78"/>
+      <c r="S54" s="78"/>
+      <c r="T54" s="78"/>
+      <c r="U54" s="78"/>
+      <c r="V54" s="78"/>
+      <c r="W54" s="78"/>
+      <c r="X54" s="78"/>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="Q55" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">SOCIETE 0518</t>
         </is>
       </c>
-      <c r="R48" s="63"/>
-      <c r="S48" s="63"/>
-      <c r="T48" s="63"/>
-      <c r="U48" s="63"/>
-      <c r="V48" s="64" t="inlineStr">
+      <c r="R55" s="76"/>
+      <c r="S55" s="76"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">+5,6 M</t>
         </is>
       </c>
-      <c r="W48" s="64"/>
-      <c r="X48" s="64"/>
-    </row>
-    <row r="49" ht="13" customHeight="1">
-      <c r="Q49" s="65" t="inlineStr">
+      <c r="W55" s="77"/>
+      <c r="X55" s="77"/>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="Q56" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">5,6 M XOF d'impayés · 12 j · Stage 2 · GUEYE</t>
         </is>
       </c>
-      <c r="R49" s="65"/>
-      <c r="S49" s="65"/>
-      <c r="T49" s="65"/>
-      <c r="U49" s="65"/>
-      <c r="V49" s="65"/>
-      <c r="W49" s="65"/>
-      <c r="X49" s="65"/>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="Q50" s="63" t="inlineStr">
+      <c r="R56" s="78"/>
+      <c r="S56" s="78"/>
+      <c r="T56" s="78"/>
+      <c r="U56" s="78"/>
+      <c r="V56" s="78"/>
+      <c r="W56" s="78"/>
+      <c r="X56" s="78"/>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="Q57" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">SOCIETE 0043</t>
         </is>
       </c>
-      <c r="R50" s="63"/>
-      <c r="S50" s="63"/>
-      <c r="T50" s="63"/>
-      <c r="U50" s="63"/>
-      <c r="V50" s="64" t="inlineStr">
+      <c r="R57" s="76"/>
+      <c r="S57" s="76"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">+3,8 M</t>
         </is>
       </c>
-      <c r="W50" s="64"/>
-      <c r="X50" s="64"/>
-    </row>
-    <row r="51" ht="13" customHeight="1">
-      <c r="Q51" s="65" t="inlineStr">
+      <c r="W57" s="77"/>
+      <c r="X57" s="77"/>
+    </row>
+    <row r="58" ht="13" customHeight="1">
+      <c r="Q58" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">5,6 M XOF d'impayés · 19 j · Stage 2 · GUEYE</t>
         </is>
       </c>
-      <c r="R51" s="65"/>
-      <c r="S51" s="65"/>
-      <c r="T51" s="65"/>
-      <c r="U51" s="65"/>
-      <c r="V51" s="65"/>
-      <c r="W51" s="65"/>
-      <c r="X51" s="65"/>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="Q52" s="63" t="inlineStr">
+      <c r="R58" s="78"/>
+      <c r="S58" s="78"/>
+      <c r="T58" s="78"/>
+      <c r="U58" s="78"/>
+      <c r="V58" s="78"/>
+      <c r="W58" s="78"/>
+      <c r="X58" s="78"/>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="Q59" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">SOCIETE 0170</t>
         </is>
       </c>
-      <c r="R52" s="63"/>
-      <c r="S52" s="63"/>
-      <c r="T52" s="63"/>
-      <c r="U52" s="63"/>
-      <c r="V52" s="64" t="inlineStr">
+      <c r="R59" s="76"/>
+      <c r="S59" s="76"/>
+      <c r="T59" s="76"/>
+      <c r="U59" s="76"/>
+      <c r="V59" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">+3,4 M</t>
         </is>
       </c>
-      <c r="W52" s="64"/>
-      <c r="X52" s="64"/>
-    </row>
-    <row r="53" ht="13" customHeight="1">
-      <c r="Q53" s="65" t="inlineStr">
+      <c r="W59" s="77"/>
+      <c r="X59" s="77"/>
+    </row>
+    <row r="60" ht="13" customHeight="1">
+      <c r="Q60" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">4,4 M XOF d'impayés · 11 j · Stage 2 · GUEYE</t>
         </is>
       </c>
-      <c r="R53" s="65"/>
-      <c r="S53" s="65"/>
-      <c r="T53" s="65"/>
-      <c r="U53" s="65"/>
-      <c r="V53" s="65"/>
-      <c r="W53" s="65"/>
-      <c r="X53" s="65"/>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="Q54" s="63" t="inlineStr">
+      <c r="R60" s="78"/>
+      <c r="S60" s="78"/>
+      <c r="T60" s="78"/>
+      <c r="U60" s="78"/>
+      <c r="V60" s="78"/>
+      <c r="W60" s="78"/>
+      <c r="X60" s="78"/>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="Q61" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">SOCIETE 0041</t>
         </is>
       </c>
-      <c r="R54" s="63"/>
-      <c r="S54" s="63"/>
-      <c r="T54" s="63"/>
-      <c r="U54" s="63"/>
-      <c r="V54" s="64" t="inlineStr">
+      <c r="R61" s="76"/>
+      <c r="S61" s="76"/>
+      <c r="T61" s="76"/>
+      <c r="U61" s="76"/>
+      <c r="V61" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">+2,9 M</t>
         </is>
       </c>
-      <c r="W54" s="64"/>
-      <c r="X54" s="64"/>
-    </row>
-    <row r="55" ht="13" customHeight="1">
-      <c r="Q55" s="65" t="inlineStr">
+      <c r="W61" s="77"/>
+      <c r="X61" s="77"/>
+    </row>
+    <row r="62" ht="13" customHeight="1">
+      <c r="Q62" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">2,9 M XOF d'impayés · 38 j · Stage 2 · GUEYE</t>
         </is>
       </c>
-      <c r="R55" s="65"/>
-      <c r="S55" s="65"/>
-      <c r="T55" s="65"/>
-      <c r="U55" s="65"/>
-      <c r="V55" s="65"/>
-      <c r="W55" s="65"/>
-      <c r="X55" s="65"/>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="Q56" s="63" t="inlineStr">
+      <c r="R62" s="78"/>
+      <c r="S62" s="78"/>
+      <c r="T62" s="78"/>
+      <c r="U62" s="78"/>
+      <c r="V62" s="78"/>
+      <c r="W62" s="78"/>
+      <c r="X62" s="78"/>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="Q63" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">SOCIETE 0038</t>
         </is>
       </c>
-      <c r="R56" s="63"/>
-      <c r="S56" s="63"/>
-      <c r="T56" s="63"/>
-      <c r="U56" s="63"/>
-      <c r="V56" s="64" t="inlineStr">
+      <c r="R63" s="76"/>
+      <c r="S63" s="76"/>
+      <c r="T63" s="76"/>
+      <c r="U63" s="76"/>
+      <c r="V63" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">+2,8 M</t>
         </is>
       </c>
-      <c r="W56" s="64"/>
-      <c r="X56" s="64"/>
-    </row>
-    <row r="57" ht="13" customHeight="1">
-      <c r="Q57" s="65" t="inlineStr">
+      <c r="W63" s="77"/>
+      <c r="X63" s="77"/>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="Q64" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">8,4 M XOF d'impayés · 281 j · Stage 3 · GUEYE</t>
         </is>
       </c>
-      <c r="R57" s="65"/>
-      <c r="S57" s="65"/>
-      <c r="T57" s="65"/>
-      <c r="U57" s="65"/>
-      <c r="V57" s="65"/>
-      <c r="W57" s="65"/>
-      <c r="X57" s="65"/>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="66" t="inlineStr">
-        <is>
+      <c r="R64" s="78"/>
+      <c r="S64" s="78"/>
+      <c r="T64" s="78"/>
+      <c r="U64" s="78"/>
+      <c r="V64" s="78"/>
+      <c r="W64" s="78"/>
+      <c r="X64" s="78"/>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="79" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">03  </t>
+          </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
@@ -3820,29 +5035,39 @@
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
+              <i/>
               <color rgb="FF64748B"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">   dossiers prioritaires classés par criticité puis impayé</t>
-          </r>
-        </is>
-      </c>
-      <c r="B60" s="66"/>
-      <c r="C60" s="66"/>
-      <c r="D60" s="66"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="66"/>
-      <c r="G60" s="66"/>
-      <c r="H60" s="66"/>
-      <c r="I60" s="66"/>
-      <c r="J60" s="66"/>
-      <c r="K60" s="66"/>
-      <c r="L60" s="66"/>
-      <c r="M60" s="66"/>
-      <c r="N60" s="66"/>
-      <c r="O60" s="66"/>
-      <c r="Q60" s="61" t="inlineStr">
-        <is>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">    dossiers prioritaires classés par criticité puis impayé</t>
+          </r>
+        </is>
+      </c>
+      <c r="B67" s="79"/>
+      <c r="C67" s="79"/>
+      <c r="D67" s="79"/>
+      <c r="E67" s="79"/>
+      <c r="F67" s="79"/>
+      <c r="G67" s="79"/>
+      <c r="H67" s="79"/>
+      <c r="I67" s="79"/>
+      <c r="J67" s="79"/>
+      <c r="K67" s="79"/>
+      <c r="L67" s="79"/>
+      <c r="M67" s="79"/>
+      <c r="N67" s="79"/>
+      <c r="O67" s="79"/>
+      <c r="Q67" s="74" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">·  </t>
+          </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
@@ -3855,54 +5080,55 @@
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
+              <i/>
               <color rgb="FF64748B"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">   tableau de bord du plan d'actions</t>
-          </r>
-        </is>
-      </c>
-      <c r="R60" s="61"/>
-      <c r="S60" s="61"/>
-      <c r="T60" s="61"/>
-      <c r="U60" s="61"/>
-      <c r="V60" s="61"/>
-      <c r="W60" s="61"/>
-      <c r="X60" s="61"/>
-    </row>
-    <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="67" t="inlineStr">
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">    tableau de bord du plan d'actions</t>
+          </r>
+        </is>
+      </c>
+      <c r="R67" s="74"/>
+      <c r="S67" s="74"/>
+      <c r="T67" s="74"/>
+      <c r="U67" s="74"/>
+      <c r="V67" s="74"/>
+      <c r="W67" s="74"/>
+      <c r="X67" s="74"/>
+    </row>
+    <row r="68" ht="19" customHeight="1">
+      <c r="A68" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">#01</t>
         </is>
       </c>
-      <c r="B61" s="67"/>
-      <c r="C61" s="68" t="inlineStr">
+      <c r="B68" s="80"/>
+      <c r="C68" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">SOCIETE 0078</t>
         </is>
       </c>
-      <c r="D61" s="68"/>
-      <c r="E61" s="68"/>
-      <c r="F61" s="68"/>
-      <c r="G61" s="68"/>
-      <c r="H61" s="68"/>
-      <c r="I61" s="68"/>
-      <c r="J61" s="68"/>
-      <c r="K61" s="71"/>
-      <c r="L61" s="71"/>
-      <c r="M61" s="72" t="inlineStr">
+      <c r="D68" s="81"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
+      <c r="H68" s="81"/>
+      <c r="I68" s="81"/>
+      <c r="J68" s="81"/>
+      <c r="K68" s="84"/>
+      <c r="L68" s="84"/>
+      <c r="M68" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">CRITICAL</t>
         </is>
       </c>
-      <c r="N61" s="72"/>
-      <c r="O61" s="72"/>
-      <c r="Q61" s="75">
+      <c r="N68" s="85"/>
+      <c r="O68" s="85"/>
+      <c r="Q68" s="88">
         <v>6</v>
       </c>
-      <c r="R61" s="75"/>
-      <c r="S61" s="76" t="inlineStr">
+      <c r="R68" s="88"/>
+      <c r="S68" s="89" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3923,16 +5149,16 @@
           </r>
         </is>
       </c>
-      <c r="T61" s="76"/>
-      <c r="U61" s="76"/>
-      <c r="V61" s="76"/>
-      <c r="W61" s="76"/>
-      <c r="X61" s="76"/>
-    </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="67"/>
-      <c r="B62" s="67"/>
-      <c r="C62" s="69" t="inlineStr">
+      <c r="T68" s="89"/>
+      <c r="U68" s="89"/>
+      <c r="V68" s="89"/>
+      <c r="W68" s="89"/>
+      <c r="X68" s="89"/>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="80"/>
+      <c r="B69" s="80"/>
+      <c r="C69" s="82" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3962,113 +5188,113 @@
           </r>
         </is>
       </c>
-      <c r="D62" s="69"/>
-      <c r="E62" s="69"/>
-      <c r="F62" s="69"/>
-      <c r="G62" s="69"/>
-      <c r="H62" s="69"/>
-      <c r="I62" s="69"/>
-      <c r="J62" s="69"/>
-      <c r="K62" s="71"/>
-      <c r="L62" s="71"/>
-      <c r="M62" s="73" t="inlineStr">
+      <c r="D69" s="82"/>
+      <c r="E69" s="82"/>
+      <c r="F69" s="82"/>
+      <c r="G69" s="82"/>
+      <c r="H69" s="82"/>
+      <c r="I69" s="82"/>
+      <c r="J69" s="82"/>
+      <c r="K69" s="84"/>
+      <c r="L69" s="84"/>
+      <c r="M69" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">ACTION REQUIRED</t>
         </is>
       </c>
-      <c r="N62" s="73"/>
-      <c r="O62" s="73"/>
-      <c r="Q62" s="75"/>
-      <c r="R62" s="75"/>
-      <c r="S62" s="77" t="inlineStr">
+      <c r="N69" s="86"/>
+      <c r="O69" s="86"/>
+      <c r="Q69" s="88"/>
+      <c r="R69" s="88"/>
+      <c r="S69" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">encours 3,49 Md XOF</t>
         </is>
       </c>
-      <c r="T62" s="77"/>
-      <c r="U62" s="77"/>
-      <c r="V62" s="77"/>
-      <c r="W62" s="77"/>
-      <c r="X62" s="77"/>
-    </row>
-    <row r="63" ht="14" customHeight="1">
-      <c r="A63" s="67"/>
-      <c r="B63" s="67"/>
-      <c r="C63" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contrepartie déjà douteuse : mise en demeure et proposition d'un protocole d'apurement daté avant le 15/10/2026 ; rechercher des actifs sais · GUEYE</t>
-        </is>
-      </c>
-      <c r="D63" s="70"/>
-      <c r="E63" s="70"/>
-      <c r="F63" s="70"/>
-      <c r="G63" s="70"/>
-      <c r="H63" s="70"/>
-      <c r="I63" s="70"/>
-      <c r="J63" s="70"/>
-      <c r="S63" s="79">
+      <c r="T69" s="90"/>
+      <c r="U69" s="90"/>
+      <c r="V69" s="90"/>
+      <c r="W69" s="90"/>
+      <c r="X69" s="90"/>
+    </row>
+    <row r="70" ht="14" customHeight="1">
+      <c r="A70" s="80"/>
+      <c r="B70" s="80"/>
+      <c r="C70" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEV PD 12M 15,4 % (HYBRID)  ·  Contrepartie déjà douteuse : mise en demeure et proposition d'un protocole d'apurement daté avant le 15/10/2026 ; rechercher des actifs sais</t>
+        </is>
+      </c>
+      <c r="D70" s="83"/>
+      <c r="E70" s="83"/>
+      <c r="F70" s="83"/>
+      <c r="G70" s="83"/>
+      <c r="H70" s="83"/>
+      <c r="I70" s="83"/>
+      <c r="J70" s="83"/>
+      <c r="S70" s="92">
         <v>0</v>
       </c>
-      <c r="T63" s="78"/>
-      <c r="U63" s="78"/>
-      <c r="V63" s="78"/>
-      <c r="W63" s="80" t="inlineStr">
+      <c r="T70" s="91"/>
+      <c r="U70" s="91"/>
+      <c r="V70" s="91"/>
+      <c r="W70" s="93" t="inlineStr">
         <is>
           <t xml:space="preserve">avancement</t>
         </is>
       </c>
-      <c r="X63" s="80"/>
-    </row>
-    <row r="64" ht="7" customHeight="1">
-      <c r="A64" s="74"/>
-      <c r="B64" s="74"/>
-      <c r="C64" s="74"/>
-      <c r="D64" s="74"/>
-      <c r="E64" s="74"/>
-      <c r="F64" s="74"/>
-      <c r="G64" s="74"/>
-      <c r="H64" s="74"/>
-      <c r="I64" s="74"/>
-      <c r="J64" s="74"/>
-      <c r="K64" s="74"/>
-      <c r="L64" s="74"/>
-      <c r="M64" s="74"/>
-      <c r="N64" s="74"/>
-      <c r="O64" s="74"/>
-    </row>
-    <row r="65" ht="19" customHeight="1">
-      <c r="A65" s="67" t="inlineStr">
+      <c r="X70" s="93"/>
+    </row>
+    <row r="71" ht="7" customHeight="1">
+      <c r="A71" s="87"/>
+      <c r="B71" s="87"/>
+      <c r="C71" s="87"/>
+      <c r="D71" s="87"/>
+      <c r="E71" s="87"/>
+      <c r="F71" s="87"/>
+      <c r="G71" s="87"/>
+      <c r="H71" s="87"/>
+      <c r="I71" s="87"/>
+      <c r="J71" s="87"/>
+      <c r="K71" s="87"/>
+      <c r="L71" s="87"/>
+      <c r="M71" s="87"/>
+      <c r="N71" s="87"/>
+      <c r="O71" s="87"/>
+    </row>
+    <row r="72" ht="19" customHeight="1">
+      <c r="A72" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">#02</t>
         </is>
       </c>
-      <c r="B65" s="67"/>
-      <c r="C65" s="68" t="inlineStr">
+      <c r="B72" s="80"/>
+      <c r="C72" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">SOCIETE 0450</t>
         </is>
       </c>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="68"/>
-      <c r="H65" s="68"/>
-      <c r="I65" s="68"/>
-      <c r="J65" s="68"/>
-      <c r="K65" s="71"/>
-      <c r="L65" s="71"/>
-      <c r="M65" s="72" t="inlineStr">
+      <c r="D72" s="81"/>
+      <c r="E72" s="81"/>
+      <c r="F72" s="81"/>
+      <c r="G72" s="81"/>
+      <c r="H72" s="81"/>
+      <c r="I72" s="81"/>
+      <c r="J72" s="81"/>
+      <c r="K72" s="84"/>
+      <c r="L72" s="84"/>
+      <c r="M72" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">CRITICAL</t>
         </is>
       </c>
-      <c r="N65" s="72"/>
-      <c r="O65" s="72"/>
-      <c r="Q65" s="81">
+      <c r="N72" s="85"/>
+      <c r="O72" s="85"/>
+      <c r="Q72" s="94">
         <v>48</v>
       </c>
-      <c r="R65" s="81"/>
-      <c r="S65" s="76" t="inlineStr">
+      <c r="R72" s="94"/>
+      <c r="S72" s="89" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4089,16 +5315,16 @@
           </r>
         </is>
       </c>
-      <c r="T65" s="76"/>
-      <c r="U65" s="76"/>
-      <c r="V65" s="76"/>
-      <c r="W65" s="76"/>
-      <c r="X65" s="76"/>
-    </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="67"/>
-      <c r="B66" s="67"/>
-      <c r="C66" s="69" t="inlineStr">
+      <c r="T72" s="89"/>
+      <c r="U72" s="89"/>
+      <c r="V72" s="89"/>
+      <c r="W72" s="89"/>
+      <c r="X72" s="89"/>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="80"/>
+      <c r="B73" s="80"/>
+      <c r="C73" s="82" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4128,113 +5354,113 @@
           </r>
         </is>
       </c>
-      <c r="D66" s="69"/>
-      <c r="E66" s="69"/>
-      <c r="F66" s="69"/>
-      <c r="G66" s="69"/>
-      <c r="H66" s="69"/>
-      <c r="I66" s="69"/>
-      <c r="J66" s="69"/>
-      <c r="K66" s="71"/>
-      <c r="L66" s="71"/>
-      <c r="M66" s="73" t="inlineStr">
+      <c r="D73" s="82"/>
+      <c r="E73" s="82"/>
+      <c r="F73" s="82"/>
+      <c r="G73" s="82"/>
+      <c r="H73" s="82"/>
+      <c r="I73" s="82"/>
+      <c r="J73" s="82"/>
+      <c r="K73" s="84"/>
+      <c r="L73" s="84"/>
+      <c r="M73" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">ACTION REQUIRED</t>
         </is>
       </c>
-      <c r="N66" s="73"/>
-      <c r="O66" s="73"/>
-      <c r="Q66" s="81"/>
-      <c r="R66" s="81"/>
-      <c r="S66" s="77" t="inlineStr">
+      <c r="N73" s="86"/>
+      <c r="O73" s="86"/>
+      <c r="Q73" s="94"/>
+      <c r="R73" s="94"/>
+      <c r="S73" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">encours 130,04 Md XOF</t>
         </is>
       </c>
-      <c r="T66" s="77"/>
-      <c r="U66" s="77"/>
-      <c r="V66" s="77"/>
-      <c r="W66" s="77"/>
-      <c r="X66" s="77"/>
-    </row>
-    <row r="67" ht="14" customHeight="1">
-      <c r="A67" s="67"/>
-      <c r="B67" s="67"/>
-      <c r="C67" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surveillance renforcée · GUEYE</t>
-        </is>
-      </c>
-      <c r="D67" s="70"/>
-      <c r="E67" s="70"/>
-      <c r="F67" s="70"/>
-      <c r="G67" s="70"/>
-      <c r="H67" s="70"/>
-      <c r="I67" s="70"/>
-      <c r="J67" s="70"/>
-      <c r="S67" s="79">
-        <v>0</v>
-      </c>
-      <c r="T67" s="78"/>
-      <c r="U67" s="78"/>
-      <c r="V67" s="78"/>
-      <c r="W67" s="80" t="inlineStr">
+      <c r="T73" s="90"/>
+      <c r="U73" s="90"/>
+      <c r="V73" s="90"/>
+      <c r="W73" s="90"/>
+      <c r="X73" s="90"/>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="80"/>
+      <c r="B74" s="80"/>
+      <c r="C74" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEV PD 12M 100,0 % (OBSERVED)  ·  Surveillance renforcée</t>
+        </is>
+      </c>
+      <c r="D74" s="83"/>
+      <c r="E74" s="83"/>
+      <c r="F74" s="83"/>
+      <c r="G74" s="83"/>
+      <c r="H74" s="83"/>
+      <c r="I74" s="83"/>
+      <c r="J74" s="83"/>
+      <c r="S74" s="92">
+        <v>0.15</v>
+      </c>
+      <c r="T74" s="91"/>
+      <c r="U74" s="91"/>
+      <c r="V74" s="91"/>
+      <c r="W74" s="93" t="inlineStr">
         <is>
           <t xml:space="preserve">avancement</t>
         </is>
       </c>
-      <c r="X67" s="80"/>
-    </row>
-    <row r="68" ht="7" customHeight="1">
-      <c r="A68" s="74"/>
-      <c r="B68" s="74"/>
-      <c r="C68" s="74"/>
-      <c r="D68" s="74"/>
-      <c r="E68" s="74"/>
-      <c r="F68" s="74"/>
-      <c r="G68" s="74"/>
-      <c r="H68" s="74"/>
-      <c r="I68" s="74"/>
-      <c r="J68" s="74"/>
-      <c r="K68" s="74"/>
-      <c r="L68" s="74"/>
-      <c r="M68" s="74"/>
-      <c r="N68" s="74"/>
-      <c r="O68" s="74"/>
-    </row>
-    <row r="69" ht="19" customHeight="1">
-      <c r="A69" s="67" t="inlineStr">
+      <c r="X74" s="93"/>
+    </row>
+    <row r="75" ht="7" customHeight="1">
+      <c r="A75" s="87"/>
+      <c r="B75" s="87"/>
+      <c r="C75" s="87"/>
+      <c r="D75" s="87"/>
+      <c r="E75" s="87"/>
+      <c r="F75" s="87"/>
+      <c r="G75" s="87"/>
+      <c r="H75" s="87"/>
+      <c r="I75" s="87"/>
+      <c r="J75" s="87"/>
+      <c r="K75" s="87"/>
+      <c r="L75" s="87"/>
+      <c r="M75" s="87"/>
+      <c r="N75" s="87"/>
+      <c r="O75" s="87"/>
+    </row>
+    <row r="76" ht="19" customHeight="1">
+      <c r="A76" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">#03</t>
         </is>
       </c>
-      <c r="B69" s="67"/>
-      <c r="C69" s="68" t="inlineStr">
+      <c r="B76" s="80"/>
+      <c r="C76" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">SOCIETE 0088</t>
         </is>
       </c>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
-      <c r="H69" s="68"/>
-      <c r="I69" s="68"/>
-      <c r="J69" s="68"/>
-      <c r="K69" s="71"/>
-      <c r="L69" s="71"/>
-      <c r="M69" s="72" t="inlineStr">
+      <c r="D76" s="81"/>
+      <c r="E76" s="81"/>
+      <c r="F76" s="81"/>
+      <c r="G76" s="81"/>
+      <c r="H76" s="81"/>
+      <c r="I76" s="81"/>
+      <c r="J76" s="81"/>
+      <c r="K76" s="84"/>
+      <c r="L76" s="84"/>
+      <c r="M76" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">CRITICAL</t>
         </is>
       </c>
-      <c r="N69" s="72"/>
-      <c r="O69" s="72"/>
-      <c r="Q69" s="82">
+      <c r="N76" s="85"/>
+      <c r="O76" s="85"/>
+      <c r="Q76" s="95">
         <v>235</v>
       </c>
-      <c r="R69" s="82"/>
-      <c r="S69" s="76" t="inlineStr">
+      <c r="R76" s="95"/>
+      <c r="S76" s="89" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4255,16 +5481,16 @@
           </r>
         </is>
       </c>
-      <c r="T69" s="76"/>
-      <c r="U69" s="76"/>
-      <c r="V69" s="76"/>
-      <c r="W69" s="76"/>
-      <c r="X69" s="76"/>
-    </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="67"/>
-      <c r="B70" s="67"/>
-      <c r="C70" s="69" t="inlineStr">
+      <c r="T76" s="89"/>
+      <c r="U76" s="89"/>
+      <c r="V76" s="89"/>
+      <c r="W76" s="89"/>
+      <c r="X76" s="89"/>
+    </row>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="80"/>
+      <c r="B77" s="80"/>
+      <c r="C77" s="82" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4294,113 +5520,113 @@
           </r>
         </is>
       </c>
-      <c r="D70" s="69"/>
-      <c r="E70" s="69"/>
-      <c r="F70" s="69"/>
-      <c r="G70" s="69"/>
-      <c r="H70" s="69"/>
-      <c r="I70" s="69"/>
-      <c r="J70" s="69"/>
-      <c r="K70" s="71"/>
-      <c r="L70" s="71"/>
-      <c r="M70" s="73" t="inlineStr">
+      <c r="D77" s="82"/>
+      <c r="E77" s="82"/>
+      <c r="F77" s="82"/>
+      <c r="G77" s="82"/>
+      <c r="H77" s="82"/>
+      <c r="I77" s="82"/>
+      <c r="J77" s="82"/>
+      <c r="K77" s="84"/>
+      <c r="L77" s="84"/>
+      <c r="M77" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">ACTION REQUIRED</t>
         </is>
       </c>
-      <c r="N70" s="73"/>
-      <c r="O70" s="73"/>
-      <c r="Q70" s="82"/>
-      <c r="R70" s="82"/>
-      <c r="S70" s="77" t="inlineStr">
+      <c r="N77" s="86"/>
+      <c r="O77" s="86"/>
+      <c r="Q77" s="95"/>
+      <c r="R77" s="95"/>
+      <c r="S77" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">encours 189,18 Md XOF</t>
         </is>
       </c>
-      <c r="T70" s="77"/>
-      <c r="U70" s="77"/>
-      <c r="V70" s="77"/>
-      <c r="W70" s="77"/>
-      <c r="X70" s="77"/>
-    </row>
-    <row r="71" ht="14" customHeight="1">
-      <c r="A71" s="67"/>
-      <c r="B71" s="67"/>
-      <c r="C71" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surveillance renforcée · GUEYE</t>
-        </is>
-      </c>
-      <c r="D71" s="70"/>
-      <c r="E71" s="70"/>
-      <c r="F71" s="70"/>
-      <c r="G71" s="70"/>
-      <c r="H71" s="70"/>
-      <c r="I71" s="70"/>
-      <c r="J71" s="70"/>
-      <c r="S71" s="79">
+      <c r="T77" s="90"/>
+      <c r="U77" s="90"/>
+      <c r="V77" s="90"/>
+      <c r="W77" s="90"/>
+      <c r="X77" s="90"/>
+    </row>
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="80"/>
+      <c r="B78" s="80"/>
+      <c r="C78" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEV PD 12M 100,0 % (OBSERVED)  ·  Surveillance renforcée</t>
+        </is>
+      </c>
+      <c r="D78" s="83"/>
+      <c r="E78" s="83"/>
+      <c r="F78" s="83"/>
+      <c r="G78" s="83"/>
+      <c r="H78" s="83"/>
+      <c r="I78" s="83"/>
+      <c r="J78" s="83"/>
+      <c r="S78" s="92">
         <v>0</v>
       </c>
-      <c r="T71" s="78"/>
-      <c r="U71" s="78"/>
-      <c r="V71" s="78"/>
-      <c r="W71" s="80" t="inlineStr">
+      <c r="T78" s="91"/>
+      <c r="U78" s="91"/>
+      <c r="V78" s="91"/>
+      <c r="W78" s="93" t="inlineStr">
         <is>
           <t xml:space="preserve">avancement</t>
         </is>
       </c>
-      <c r="X71" s="80"/>
-    </row>
-    <row r="72" ht="7" customHeight="1">
-      <c r="A72" s="74"/>
-      <c r="B72" s="74"/>
-      <c r="C72" s="74"/>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="74"/>
-      <c r="G72" s="74"/>
-      <c r="H72" s="74"/>
-      <c r="I72" s="74"/>
-      <c r="J72" s="74"/>
-      <c r="K72" s="74"/>
-      <c r="L72" s="74"/>
-      <c r="M72" s="74"/>
-      <c r="N72" s="74"/>
-      <c r="O72" s="74"/>
-    </row>
-    <row r="73" ht="19" customHeight="1">
-      <c r="A73" s="67" t="inlineStr">
+      <c r="X78" s="93"/>
+    </row>
+    <row r="79" ht="7" customHeight="1">
+      <c r="A79" s="87"/>
+      <c r="B79" s="87"/>
+      <c r="C79" s="87"/>
+      <c r="D79" s="87"/>
+      <c r="E79" s="87"/>
+      <c r="F79" s="87"/>
+      <c r="G79" s="87"/>
+      <c r="H79" s="87"/>
+      <c r="I79" s="87"/>
+      <c r="J79" s="87"/>
+      <c r="K79" s="87"/>
+      <c r="L79" s="87"/>
+      <c r="M79" s="87"/>
+      <c r="N79" s="87"/>
+      <c r="O79" s="87"/>
+    </row>
+    <row r="80" ht="19" customHeight="1">
+      <c r="A80" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">#04</t>
         </is>
       </c>
-      <c r="B73" s="67"/>
-      <c r="C73" s="68" t="inlineStr">
+      <c r="B80" s="80"/>
+      <c r="C80" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">SOCIETE 0208</t>
         </is>
       </c>
-      <c r="D73" s="68"/>
-      <c r="E73" s="68"/>
-      <c r="F73" s="68"/>
-      <c r="G73" s="68"/>
-      <c r="H73" s="68"/>
-      <c r="I73" s="68"/>
-      <c r="J73" s="68"/>
-      <c r="K73" s="71"/>
-      <c r="L73" s="71"/>
-      <c r="M73" s="72" t="inlineStr">
+      <c r="D80" s="81"/>
+      <c r="E80" s="81"/>
+      <c r="F80" s="81"/>
+      <c r="G80" s="81"/>
+      <c r="H80" s="81"/>
+      <c r="I80" s="81"/>
+      <c r="J80" s="81"/>
+      <c r="K80" s="84"/>
+      <c r="L80" s="84"/>
+      <c r="M80" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">CRITICAL</t>
         </is>
       </c>
-      <c r="N73" s="72"/>
-      <c r="O73" s="72"/>
-      <c r="Q73" s="83">
+      <c r="N80" s="85"/>
+      <c r="O80" s="85"/>
+      <c r="Q80" s="96">
         <v>0</v>
       </c>
-      <c r="R73" s="83"/>
-      <c r="S73" s="76" t="inlineStr">
+      <c r="R80" s="96"/>
+      <c r="S80" s="89" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4421,16 +5647,16 @@
           </r>
         </is>
       </c>
-      <c r="T73" s="76"/>
-      <c r="U73" s="76"/>
-      <c r="V73" s="76"/>
-      <c r="W73" s="76"/>
-      <c r="X73" s="76"/>
-    </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="67"/>
-      <c r="B74" s="67"/>
-      <c r="C74" s="69" t="inlineStr">
+      <c r="T80" s="89"/>
+      <c r="U80" s="89"/>
+      <c r="V80" s="89"/>
+      <c r="W80" s="89"/>
+      <c r="X80" s="89"/>
+    </row>
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="80"/>
+      <c r="B81" s="80"/>
+      <c r="C81" s="82" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4460,83 +5686,92 @@
           </r>
         </is>
       </c>
-      <c r="D74" s="69"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="69"/>
-      <c r="H74" s="69"/>
-      <c r="I74" s="69"/>
-      <c r="J74" s="69"/>
-      <c r="K74" s="71"/>
-      <c r="L74" s="71"/>
-      <c r="M74" s="73" t="inlineStr">
+      <c r="D81" s="82"/>
+      <c r="E81" s="82"/>
+      <c r="F81" s="82"/>
+      <c r="G81" s="82"/>
+      <c r="H81" s="82"/>
+      <c r="I81" s="82"/>
+      <c r="J81" s="82"/>
+      <c r="K81" s="84"/>
+      <c r="L81" s="84"/>
+      <c r="M81" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">ACTION REQUIRED</t>
         </is>
       </c>
-      <c r="N74" s="73"/>
-      <c r="O74" s="73"/>
-      <c r="Q74" s="83"/>
-      <c r="R74" s="83"/>
-      <c r="S74" s="77" t="inlineStr">
+      <c r="N81" s="86"/>
+      <c r="O81" s="86"/>
+      <c r="Q81" s="96"/>
+      <c r="R81" s="96"/>
+      <c r="S81" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">impayés résorbés 0 XOF</t>
         </is>
       </c>
-      <c r="T74" s="77"/>
-      <c r="U74" s="77"/>
-      <c r="V74" s="77"/>
-      <c r="W74" s="77"/>
-      <c r="X74" s="77"/>
-    </row>
-    <row r="75" ht="14" customHeight="1">
-      <c r="A75" s="67"/>
-      <c r="B75" s="67"/>
-      <c r="C75" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surveillance renforcée · GUEYE</t>
-        </is>
-      </c>
-      <c r="D75" s="70"/>
-      <c r="E75" s="70"/>
-      <c r="F75" s="70"/>
-      <c r="G75" s="70"/>
-      <c r="H75" s="70"/>
-      <c r="I75" s="70"/>
-      <c r="J75" s="70"/>
-      <c r="S75" s="79">
+      <c r="T81" s="90"/>
+      <c r="U81" s="90"/>
+      <c r="V81" s="90"/>
+      <c r="W81" s="90"/>
+      <c r="X81" s="90"/>
+    </row>
+    <row r="82" ht="14" customHeight="1">
+      <c r="A82" s="80"/>
+      <c r="B82" s="80"/>
+      <c r="C82" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEV PD 12M 100,0 % (OBSERVED)  ·  Surveillance renforcée</t>
+        </is>
+      </c>
+      <c r="D82" s="83"/>
+      <c r="E82" s="83"/>
+      <c r="F82" s="83"/>
+      <c r="G82" s="83"/>
+      <c r="H82" s="83"/>
+      <c r="I82" s="83"/>
+      <c r="J82" s="83"/>
+      <c r="S82" s="92">
         <v>0</v>
       </c>
-      <c r="T75" s="78"/>
-      <c r="U75" s="78"/>
-      <c r="V75" s="78"/>
-      <c r="W75" s="80" t="inlineStr">
+      <c r="T82" s="91"/>
+      <c r="U82" s="91"/>
+      <c r="V82" s="91"/>
+      <c r="W82" s="93" t="inlineStr">
         <is>
           <t xml:space="preserve">avancement</t>
         </is>
       </c>
-      <c r="X75" s="80"/>
-    </row>
-    <row r="76" ht="7" customHeight="1">
-      <c r="A76" s="74"/>
-      <c r="B76" s="74"/>
-      <c r="C76" s="74"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="74"/>
-      <c r="H76" s="74"/>
-      <c r="I76" s="74"/>
-      <c r="J76" s="74"/>
-      <c r="K76" s="74"/>
-      <c r="L76" s="74"/>
-      <c r="M76" s="74"/>
-      <c r="N76" s="74"/>
-      <c r="O76" s="74"/>
-    </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="61" t="inlineStr">
-        <is>
+      <c r="X82" s="93"/>
+    </row>
+    <row r="83" ht="7" customHeight="1">
+      <c r="A83" s="87"/>
+      <c r="B83" s="87"/>
+      <c r="C83" s="87"/>
+      <c r="D83" s="87"/>
+      <c r="E83" s="87"/>
+      <c r="F83" s="87"/>
+      <c r="G83" s="87"/>
+      <c r="H83" s="87"/>
+      <c r="I83" s="87"/>
+      <c r="J83" s="87"/>
+      <c r="K83" s="87"/>
+      <c r="L83" s="87"/>
+      <c r="M83" s="87"/>
+      <c r="N83" s="87"/>
+      <c r="O83" s="87"/>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="74" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">04  </t>
+          </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
@@ -4549,39 +5784,40 @@
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
+              <i/>
               <color rgb="FF64748B"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">   calculés sur les données de l'arrêté</t>
-          </r>
-        </is>
-      </c>
-      <c r="B79" s="61"/>
-      <c r="C79" s="61"/>
-      <c r="D79" s="61"/>
-      <c r="E79" s="61"/>
-      <c r="F79" s="61"/>
-      <c r="G79" s="61"/>
-      <c r="H79" s="61"/>
-      <c r="I79" s="61"/>
-      <c r="J79" s="61"/>
-      <c r="K79" s="61"/>
-      <c r="L79" s="61"/>
-      <c r="M79" s="61"/>
-      <c r="N79" s="61"/>
-      <c r="O79" s="61"/>
-      <c r="P79" s="61"/>
-      <c r="Q79" s="61"/>
-      <c r="R79" s="61"/>
-      <c r="S79" s="61"/>
-      <c r="T79" s="61"/>
-      <c r="U79" s="61"/>
-      <c r="V79" s="61"/>
-      <c r="W79" s="61"/>
-      <c r="X79" s="61"/>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="84" t="inlineStr">
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">    calculés sur les données de l'arrêté</t>
+          </r>
+        </is>
+      </c>
+      <c r="B86" s="74"/>
+      <c r="C86" s="74"/>
+      <c r="D86" s="74"/>
+      <c r="E86" s="74"/>
+      <c r="F86" s="74"/>
+      <c r="G86" s="74"/>
+      <c r="H86" s="74"/>
+      <c r="I86" s="74"/>
+      <c r="J86" s="74"/>
+      <c r="K86" s="74"/>
+      <c r="L86" s="74"/>
+      <c r="M86" s="74"/>
+      <c r="N86" s="74"/>
+      <c r="O86" s="74"/>
+      <c r="P86" s="74"/>
+      <c r="Q86" s="74"/>
+      <c r="R86" s="74"/>
+      <c r="S86" s="74"/>
+      <c r="T86" s="74"/>
+      <c r="U86" s="74"/>
+      <c r="V86" s="74"/>
+      <c r="W86" s="74"/>
+      <c r="X86" s="74"/>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="97" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4603,12 +5839,12 @@
           </r>
         </is>
       </c>
-      <c r="B80" s="84"/>
-      <c r="C80" s="84"/>
-      <c r="D80" s="84"/>
-      <c r="E80" s="84"/>
-      <c r="F80" s="84"/>
-      <c r="G80" s="87" t="inlineStr">
+      <c r="B87" s="97"/>
+      <c r="C87" s="97"/>
+      <c r="D87" s="97"/>
+      <c r="E87" s="97"/>
+      <c r="F87" s="97"/>
+      <c r="G87" s="100" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4630,12 +5866,12 @@
           </r>
         </is>
       </c>
-      <c r="H80" s="87"/>
-      <c r="I80" s="87"/>
-      <c r="J80" s="87"/>
-      <c r="K80" s="87"/>
-      <c r="L80" s="87"/>
-      <c r="M80" s="89" t="inlineStr">
+      <c r="H87" s="100"/>
+      <c r="I87" s="100"/>
+      <c r="J87" s="100"/>
+      <c r="K87" s="100"/>
+      <c r="L87" s="100"/>
+      <c r="M87" s="102" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4657,12 +5893,12 @@
           </r>
         </is>
       </c>
-      <c r="N80" s="89"/>
-      <c r="O80" s="89"/>
-      <c r="P80" s="89"/>
-      <c r="Q80" s="89"/>
-      <c r="R80" s="89"/>
-      <c r="S80" s="84" t="inlineStr">
+      <c r="N87" s="102"/>
+      <c r="O87" s="102"/>
+      <c r="P87" s="102"/>
+      <c r="Q87" s="102"/>
+      <c r="R87" s="102"/>
+      <c r="S87" s="97" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4684,258 +5920,272 @@
           </r>
         </is>
       </c>
-      <c r="T80" s="84"/>
-      <c r="U80" s="84"/>
-      <c r="V80" s="84"/>
-      <c r="W80" s="84"/>
-      <c r="X80" s="84"/>
-    </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="85" t="inlineStr">
+      <c r="T87" s="97"/>
+      <c r="U87" s="97"/>
+      <c r="V87" s="97"/>
+      <c r="W87" s="97"/>
+      <c r="X87" s="97"/>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="98" t="inlineStr">
         <is>
           <t xml:space="preserve">+333,3 M XOF</t>
         </is>
       </c>
-      <c r="B81" s="85"/>
-      <c r="C81" s="85"/>
-      <c r="D81" s="85"/>
-      <c r="E81" s="85"/>
-      <c r="F81" s="85"/>
-      <c r="G81" s="88" t="inlineStr">
+      <c r="B88" s="98"/>
+      <c r="C88" s="98"/>
+      <c r="D88" s="98"/>
+      <c r="E88" s="98"/>
+      <c r="F88" s="98"/>
+      <c r="G88" s="101" t="inlineStr">
         <is>
           <t xml:space="preserve">TOP 10 = 8,3 %</t>
         </is>
       </c>
-      <c r="H81" s="88"/>
-      <c r="I81" s="88"/>
-      <c r="J81" s="88"/>
-      <c r="K81" s="88"/>
-      <c r="L81" s="88"/>
-      <c r="M81" s="90" t="inlineStr">
+      <c r="H88" s="101"/>
+      <c r="I88" s="101"/>
+      <c r="J88" s="101"/>
+      <c r="K88" s="101"/>
+      <c r="L88" s="101"/>
+      <c r="M88" s="103" t="inlineStr">
         <is>
           <t xml:space="preserve">9 dossiers</t>
         </is>
       </c>
-      <c r="N81" s="90"/>
-      <c r="O81" s="90"/>
-      <c r="P81" s="90"/>
-      <c r="Q81" s="90"/>
-      <c r="R81" s="90"/>
-      <c r="S81" s="85" t="inlineStr">
+      <c r="N88" s="103"/>
+      <c r="O88" s="103"/>
+      <c r="P88" s="103"/>
+      <c r="Q88" s="103"/>
+      <c r="R88" s="103"/>
+      <c r="S88" s="98" t="inlineStr">
         <is>
           <t xml:space="preserve">54 dossiers</t>
         </is>
       </c>
-      <c r="T81" s="85"/>
-      <c r="U81" s="85"/>
-      <c r="V81" s="85"/>
-      <c r="W81" s="85"/>
-      <c r="X81" s="85"/>
-    </row>
-    <row r="82" ht="46" customHeight="1">
-      <c r="A82" s="86" t="inlineStr">
+      <c r="T88" s="98"/>
+      <c r="U88" s="98"/>
+      <c r="V88" s="98"/>
+      <c r="W88" s="98"/>
+      <c r="X88" s="98"/>
+    </row>
+    <row r="89" ht="46" customHeight="1">
+      <c r="A89" s="99" t="inlineStr">
         <is>
           <t xml:space="preserve">Les impayés passent de 31,56 Md à 31,89 Md XOF depuis le 31/08/2026. Nouveaux impayés : 8,5 M (3 % des hausses) ; régularisations : 0 ; remboursements partiels : 0.</t>
         </is>
       </c>
-      <c r="B82" s="86"/>
-      <c r="C82" s="86"/>
-      <c r="D82" s="86"/>
-      <c r="E82" s="86"/>
-      <c r="F82" s="86"/>
-      <c r="G82" s="86" t="inlineStr">
+      <c r="B89" s="99"/>
+      <c r="C89" s="99"/>
+      <c r="D89" s="99"/>
+      <c r="E89" s="99"/>
+      <c r="F89" s="99"/>
+      <c r="G89" s="99" t="inlineStr">
         <is>
           <t xml:space="preserve">Les 10 premiers clients portent 70,74 Md XOF sur 850,39 Md. Premier client : SOCIETE 0378 (1,0 %). Premier segment : X (100 %).</t>
         </is>
       </c>
-      <c r="H82" s="86"/>
-      <c r="I82" s="86"/>
-      <c r="J82" s="86"/>
-      <c r="K82" s="86"/>
-      <c r="L82" s="86"/>
-      <c r="M82" s="86" t="inlineStr">
+      <c r="H89" s="99"/>
+      <c r="I89" s="99"/>
+      <c r="J89" s="99"/>
+      <c r="K89" s="99"/>
+      <c r="L89" s="99"/>
+      <c r="M89" s="99" t="inlineStr">
         <is>
           <t xml:space="preserve">9 clients ont migré vers une tranche d'impayé plus dégradée (1,3 % des clients suivis), dont 6 au-delà de 90 jours ou en Stage 3 pour 3,49 Md XOF d'encours.</t>
         </is>
       </c>
-      <c r="N82" s="86"/>
-      <c r="O82" s="86"/>
-      <c r="P82" s="86"/>
-      <c r="Q82" s="86"/>
-      <c r="R82" s="86"/>
-      <c r="S82" s="86" t="inlineStr">
+      <c r="N89" s="99"/>
+      <c r="O89" s="99"/>
+      <c r="P89" s="99"/>
+      <c r="Q89" s="99"/>
+      <c r="R89" s="99"/>
+      <c r="S89" s="99" t="inlineStr">
         <is>
           <t xml:space="preserve">6 dossiers critiques (3,49 Md XOF) et 48 en priorité haute nécessitent une intervention. Premier dossier : SOCIETE 0450 (3,03 Md, 304 j).</t>
         </is>
       </c>
-      <c r="T82" s="86"/>
-      <c r="U82" s="86"/>
-      <c r="V82" s="86"/>
-      <c r="W82" s="86"/>
-      <c r="X82" s="86"/>
+      <c r="T89" s="99"/>
+      <c r="U89" s="99"/>
+      <c r="V89" s="99"/>
+      <c r="W89" s="99"/>
+      <c r="X89" s="99"/>
     </row>
   </sheetData>
-  <mergeCells count="158">
+  <mergeCells count="172">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="S1:X1"/>
-    <mergeCell ref="A2:O5"/>
+    <mergeCell ref="A2:O6"/>
     <mergeCell ref="P2:X2"/>
     <mergeCell ref="P3:X3"/>
     <mergeCell ref="P4:X4"/>
     <mergeCell ref="P5:X5"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="I7:P7"/>
-    <mergeCell ref="Q7:X7"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D12"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="I8:P8"/>
+    <mergeCell ref="Q8:X8"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="M10:R10"/>
+    <mergeCell ref="S10:X10"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F11:I12"/>
+    <mergeCell ref="A14:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="F13:I13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="K11:N12"/>
+    <mergeCell ref="F14:I15"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="F18:I18"/>
     <mergeCell ref="K13:N13"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="P10:S10"/>
-    <mergeCell ref="P11:S12"/>
+    <mergeCell ref="K14:N15"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="K18:N18"/>
     <mergeCell ref="P13:S13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="P15:S15"/>
-    <mergeCell ref="U10:X10"/>
-    <mergeCell ref="U11:X12"/>
+    <mergeCell ref="P14:S15"/>
+    <mergeCell ref="P16:S16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="P18:S18"/>
     <mergeCell ref="U13:X13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="U15:X15"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A19:D20"/>
+    <mergeCell ref="U14:X15"/>
+    <mergeCell ref="U16:X16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="U18:X18"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="F19:I20"/>
+    <mergeCell ref="A22:D23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="F21:I21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="K19:N20"/>
+    <mergeCell ref="F22:I23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="F26:I26"/>
     <mergeCell ref="K21:N21"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="P18:S18"/>
-    <mergeCell ref="P19:S20"/>
+    <mergeCell ref="K22:N23"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="K26:N26"/>
     <mergeCell ref="P21:S21"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="P23:S23"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="U19:X20"/>
+    <mergeCell ref="P22:S23"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="P26:S26"/>
     <mergeCell ref="U21:X21"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="A26:O26"/>
-    <mergeCell ref="Q26:X26"/>
-    <mergeCell ref="A43:O43"/>
-    <mergeCell ref="Q43:X43"/>
-    <mergeCell ref="Q44:U44"/>
-    <mergeCell ref="V44:X44"/>
-    <mergeCell ref="Q45:X45"/>
-    <mergeCell ref="Q46:U46"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="Q47:X47"/>
-    <mergeCell ref="Q48:U48"/>
-    <mergeCell ref="V48:X48"/>
-    <mergeCell ref="Q49:X49"/>
-    <mergeCell ref="Q50:U50"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="Q51:X51"/>
-    <mergeCell ref="Q52:U52"/>
-    <mergeCell ref="V52:X52"/>
-    <mergeCell ref="Q53:X53"/>
-    <mergeCell ref="Q54:U54"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="Q55:X55"/>
-    <mergeCell ref="Q56:U56"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="Q57:X57"/>
-    <mergeCell ref="A60:O60"/>
+    <mergeCell ref="U22:X23"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="K29:S29"/>
+    <mergeCell ref="K30:S30"/>
+    <mergeCell ref="K31:S31"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="A33:O33"/>
+    <mergeCell ref="Q33:X33"/>
+    <mergeCell ref="A50:O50"/>
+    <mergeCell ref="Q50:X50"/>
+    <mergeCell ref="Q51:U51"/>
+    <mergeCell ref="V51:X51"/>
+    <mergeCell ref="Q52:X52"/>
+    <mergeCell ref="Q53:U53"/>
+    <mergeCell ref="V53:X53"/>
+    <mergeCell ref="Q54:X54"/>
+    <mergeCell ref="Q55:U55"/>
+    <mergeCell ref="V55:X55"/>
+    <mergeCell ref="Q56:X56"/>
+    <mergeCell ref="Q57:U57"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="Q58:X58"/>
+    <mergeCell ref="Q59:U59"/>
+    <mergeCell ref="V59:X59"/>
     <mergeCell ref="Q60:X60"/>
-    <mergeCell ref="A61:B63"/>
-    <mergeCell ref="C61:J61"/>
-    <mergeCell ref="C62:J62"/>
-    <mergeCell ref="C63:J63"/>
-    <mergeCell ref="K61:L62"/>
-    <mergeCell ref="M61:O61"/>
-    <mergeCell ref="M62:O62"/>
-    <mergeCell ref="A65:B67"/>
-    <mergeCell ref="C65:J65"/>
-    <mergeCell ref="C66:J66"/>
-    <mergeCell ref="C67:J67"/>
-    <mergeCell ref="K65:L66"/>
-    <mergeCell ref="M65:O65"/>
-    <mergeCell ref="M66:O66"/>
-    <mergeCell ref="A69:B71"/>
+    <mergeCell ref="Q61:U61"/>
+    <mergeCell ref="V61:X61"/>
+    <mergeCell ref="Q62:X62"/>
+    <mergeCell ref="Q63:U63"/>
+    <mergeCell ref="V63:X63"/>
+    <mergeCell ref="Q64:X64"/>
+    <mergeCell ref="A67:O67"/>
+    <mergeCell ref="Q67:X67"/>
+    <mergeCell ref="A68:B70"/>
+    <mergeCell ref="C68:J68"/>
     <mergeCell ref="C69:J69"/>
     <mergeCell ref="C70:J70"/>
-    <mergeCell ref="C71:J71"/>
-    <mergeCell ref="K69:L70"/>
+    <mergeCell ref="K68:L69"/>
+    <mergeCell ref="M68:O68"/>
     <mergeCell ref="M69:O69"/>
-    <mergeCell ref="M70:O70"/>
-    <mergeCell ref="A73:B75"/>
+    <mergeCell ref="A72:B74"/>
+    <mergeCell ref="C72:J72"/>
     <mergeCell ref="C73:J73"/>
     <mergeCell ref="C74:J74"/>
-    <mergeCell ref="C75:J75"/>
-    <mergeCell ref="K73:L74"/>
+    <mergeCell ref="K72:L73"/>
+    <mergeCell ref="M72:O72"/>
     <mergeCell ref="M73:O73"/>
-    <mergeCell ref="M74:O74"/>
-    <mergeCell ref="Q61:R62"/>
-    <mergeCell ref="S61:X61"/>
-    <mergeCell ref="S62:X62"/>
-    <mergeCell ref="S63:V63"/>
-    <mergeCell ref="W63:X63"/>
-    <mergeCell ref="Q65:R66"/>
-    <mergeCell ref="S65:X65"/>
-    <mergeCell ref="S66:X66"/>
-    <mergeCell ref="S67:V67"/>
-    <mergeCell ref="W67:X67"/>
-    <mergeCell ref="Q69:R70"/>
+    <mergeCell ref="A76:B78"/>
+    <mergeCell ref="C76:J76"/>
+    <mergeCell ref="C77:J77"/>
+    <mergeCell ref="C78:J78"/>
+    <mergeCell ref="K76:L77"/>
+    <mergeCell ref="M76:O76"/>
+    <mergeCell ref="M77:O77"/>
+    <mergeCell ref="A80:B82"/>
+    <mergeCell ref="C80:J80"/>
+    <mergeCell ref="C81:J81"/>
+    <mergeCell ref="C82:J82"/>
+    <mergeCell ref="K80:L81"/>
+    <mergeCell ref="M80:O80"/>
+    <mergeCell ref="M81:O81"/>
+    <mergeCell ref="Q68:R69"/>
+    <mergeCell ref="S68:X68"/>
     <mergeCell ref="S69:X69"/>
-    <mergeCell ref="S70:X70"/>
-    <mergeCell ref="S71:V71"/>
-    <mergeCell ref="W71:X71"/>
-    <mergeCell ref="Q73:R74"/>
+    <mergeCell ref="S70:V70"/>
+    <mergeCell ref="W70:X70"/>
+    <mergeCell ref="Q72:R73"/>
+    <mergeCell ref="S72:X72"/>
     <mergeCell ref="S73:X73"/>
-    <mergeCell ref="S74:X74"/>
-    <mergeCell ref="S75:V75"/>
-    <mergeCell ref="W75:X75"/>
-    <mergeCell ref="A79:X79"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="G80:L80"/>
-    <mergeCell ref="G81:L81"/>
-    <mergeCell ref="G82:L82"/>
-    <mergeCell ref="M80:R80"/>
-    <mergeCell ref="M81:R81"/>
-    <mergeCell ref="M82:R82"/>
+    <mergeCell ref="S74:V74"/>
+    <mergeCell ref="W74:X74"/>
+    <mergeCell ref="Q76:R77"/>
+    <mergeCell ref="S76:X76"/>
+    <mergeCell ref="S77:X77"/>
+    <mergeCell ref="S78:V78"/>
+    <mergeCell ref="W78:X78"/>
+    <mergeCell ref="Q80:R81"/>
     <mergeCell ref="S80:X80"/>
     <mergeCell ref="S81:X81"/>
-    <mergeCell ref="S82:X82"/>
+    <mergeCell ref="S82:V82"/>
+    <mergeCell ref="W82:X82"/>
+    <mergeCell ref="A86:X86"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="G87:L87"/>
+    <mergeCell ref="G88:L88"/>
+    <mergeCell ref="G89:L89"/>
+    <mergeCell ref="M87:R87"/>
+    <mergeCell ref="M88:R88"/>
+    <mergeCell ref="M89:R89"/>
+    <mergeCell ref="S87:X87"/>
+    <mergeCell ref="S88:X88"/>
+    <mergeCell ref="S89:X89"/>
   </mergeCells>
-  <conditionalFormatting sqref="S63">
+  <conditionalFormatting sqref="S70">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4944,7 +6194,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S67">
+  <conditionalFormatting sqref="S74">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4953,7 +6203,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S71">
+  <conditionalFormatting sqref="S78">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4962,7 +6212,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S75">
+  <conditionalFormatting sqref="S82">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4972,8 +6222,8 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="I7" location="'INSIGHTS'!A1" display="INSIGHTS"/>
-    <hyperlink ref="Q7" location="'AUDIT'!A1" display="AUDIT"/>
+    <hyperlink ref="I8" location="'INSIGHTS'!A1" display="INSIGHTS"/>
+    <hyperlink ref="Q8" location="'AUDIT'!A1" display="AUDIT"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.45" bottom="0.5" header="0.2" footer="0.25"/>
@@ -4983,8 +6233,8 @@
     <oddFooter>&amp;L&amp;8&amp;K64748BEXECUTIVE · INTERNAL USE ONLY&amp;R&amp;8&amp;K64748BPage &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="25" max="16383" man="1"/>
-    <brk id="59" max="16383" man="1"/>
+    <brk id="32" max="16383" man="1"/>
+    <brk id="66" max="16383" man="1"/>
   </rowBreaks>
   <drawing r:id="rId1"/>
   <extLst>
@@ -5002,7 +6252,7 @@
           <x14:sparklines>
             <x14:sparkline>
               <xm:f>'_data'!B1:J1</xm:f>
-              <xm:sqref>C14</xm:sqref>
+              <xm:sqref>C17</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -5018,7 +6268,7 @@
           <x14:sparklines>
             <x14:sparkline>
               <xm:f>'_data'!B2:J2</xm:f>
-              <xm:sqref>H14</xm:sqref>
+              <xm:sqref>H17</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -5034,7 +6284,7 @@
           <x14:sparklines>
             <x14:sparkline>
               <xm:f>'_data'!B3:J3</xm:f>
-              <xm:sqref>M14</xm:sqref>
+              <xm:sqref>M17</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -5050,7 +6300,7 @@
           <x14:sparklines>
             <x14:sparkline>
               <xm:f>'_data'!B4:J4</xm:f>
-              <xm:sqref>R14</xm:sqref>
+              <xm:sqref>R17</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -5066,7 +6316,7 @@
           <x14:sparklines>
             <x14:sparkline>
               <xm:f>'_data'!B5:J5</xm:f>
-              <xm:sqref>W14</xm:sqref>
+              <xm:sqref>W17</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -5082,7 +6332,7 @@
           <x14:sparklines>
             <x14:sparkline>
               <xm:f>'_data'!B6:J6</xm:f>
-              <xm:sqref>C22</xm:sqref>
+              <xm:sqref>C25</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -5098,7 +6348,7 @@
           <x14:sparklines>
             <x14:sparkline>
               <xm:f>'_data'!B7:J7</xm:f>
-              <xm:sqref>H22</xm:sqref>
+              <xm:sqref>H25</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -5114,7 +6364,7 @@
           <x14:sparklines>
             <x14:sparkline>
               <xm:f>'_data'!B8:J8</xm:f>
-              <xm:sqref>M22</xm:sqref>
+              <xm:sqref>M25</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -5130,7 +6380,7 @@
           <x14:sparklines>
             <x14:sparkline>
               <xm:f>'_data'!B9:J9</xm:f>
-              <xm:sqref>K61</xm:sqref>
+              <xm:sqref>K68</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -5146,7 +6396,7 @@
           <x14:sparklines>
             <x14:sparkline>
               <xm:f>'_data'!B10:J10</xm:f>
-              <xm:sqref>K65</xm:sqref>
+              <xm:sqref>K72</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -5162,7 +6412,7 @@
           <x14:sparklines>
             <x14:sparkline>
               <xm:f>'_data'!B11:J11</xm:f>
-              <xm:sqref>K69</xm:sqref>
+              <xm:sqref>K76</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -5178,7 +6428,7 @@
           <x14:sparklines>
             <x14:sparkline>
               <xm:f>'_data'!B12:J12</xm:f>
-              <xm:sqref>K73</xm:sqref>
+              <xm:sqref>K80</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -5194,7 +6444,7 @@
     <tabColor rgb="FFC8A951"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.4" customWidth="1"/>
@@ -5208,7 +6458,7 @@
     <col min="9" max="9" width="5.4" customWidth="1"/>
     <col min="10" max="10" width="5.4" customWidth="1"/>
     <col min="11" max="11" width="5.4" customWidth="1"/>
-    <col min="12" max="12" width="5.4" customWidth="1"/>
+    <col min="12" max="12" width="1.6" customWidth="1"/>
     <col min="13" max="13" width="5.4" customWidth="1"/>
     <col min="14" max="14" width="5.4" customWidth="1"/>
     <col min="15" max="15" width="5.4" customWidth="1"/>
@@ -5221,27 +6471,45 @@
     <col min="22" max="22" width="5.4" customWidth="1"/>
     <col min="23" max="23" width="5.4" customWidth="1"/>
     <col min="24" max="24" width="5.4" customWidth="1"/>
+    <col min="25" max="25" width="1.6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
-              <b/>
               <color rgb="FFC8A951"/>
-              <sz val="9"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">◆ </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="8.5"/>
             </rPr>
             <t xml:space="preserve">ECOBANK SÉNÉGAL</t>
           </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
-              <color rgb="FFC7D7F5"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">   ·   CREDIT RISK INTELLIGENCE</t>
+              <color rgb="FF9DB4E0"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">   ·   CREDIT RISK INTELLIGENCE   ·   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFFFFFFF"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">INSIGHTS</t>
           </r>
         </is>
       </c>
@@ -5268,7 +6536,7 @@
             <rPr>
               <rFont val="Segoe UI"/>
               <color rgb="FF8EA6D6"/>
-              <sz val="8"/>
+              <sz val="7.5"/>
             </rPr>
             <t xml:space="preserve">INTERNAL USE ONLY  ·  </t>
           </r>
@@ -5277,27 +6545,37 @@
               <rFont val="Segoe UI"/>
               <b/>
               <color rgb="FFC8A951"/>
-              <sz val="8"/>
+              <sz val="7.5"/>
             </rPr>
             <t xml:space="preserve">RI 1.0</t>
           </r>
         </is>
       </c>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+    </row>
+    <row r="2" ht="10" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
               <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">E C O B A N K   S É N É G A L
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
               <color rgb="FFFFFFFF"/>
-              <sz val="22"/>
+              <sz val="26"/>
             </rPr>
             <t xml:space="preserve">INSIGHTS
 </t>
@@ -5306,19 +6584,9 @@
             <rPr>
               <rFont val="Segoe UI"/>
               <color rgb="FFC7D7F5"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Lecture éditoriale de l'arrêté · chaque chiffre est calculé sur les données
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b/>
-              <color rgb="FFC8A951"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">ECOBANK SÉNÉGAL · DIRECTION DES RISQUES</t>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">Lecture éditoriale de l'arrêté · chaque chiffre est calculé sur les données</t>
           </r>
         </is>
       </c>
@@ -5336,11 +6604,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
-      <c r="P2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REPORTING DATE</t>
-        </is>
-      </c>
+      <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
@@ -5350,7 +6614,7 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -5368,7 +6632,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/09/2026</t>
+          <t xml:space="preserve">REPORTING DATE</t>
         </is>
       </c>
       <c r="Q3" s="5"/>
@@ -5380,7 +6644,7 @@
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -5396,21 +6660,21 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PERIMETER</t>
-        </is>
-      </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 SEPTEMBER 2026</t>
+        </is>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -5426,52 +6690,52 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORTFOLIO MONITORING</t>
+        </is>
+      </c>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Portefeuille Ecobank Sénégal · 700 clients · 2 500 lignes ACTE 7</t>
         </is>
       </c>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-    </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EXECUTIVE</t>
-        </is>
-      </c>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+    </row>
+    <row r="7" ht="2.5" customHeight="1">
+      <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -5479,23 +6743,15 @@
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INSIGHTS</t>
-        </is>
-      </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AUDIT</t>
-        </is>
-      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
       <c r="T7" s="9"/>
@@ -5504,419 +6760,1121 @@
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
     </row>
-    <row r="8" ht="8" customHeight="1"/>
-    <row r="9" ht="12" customHeight="1"/>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="91" t="inlineStr">
+    <row r="8" ht="23" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FF7C93C9"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">◆  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF003DA5"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">EXECUTIVE</t>
+          </r>
+        </is>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFC8A951"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">✦  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFFFFFFF"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">INSIGHTS</t>
+          </r>
+        </is>
+      </c>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FF7C93C9"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">§  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF003DA5"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">AUDIT</t>
+          </r>
+        </is>
+      </c>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+    </row>
+    <row r="9" ht="5" customHeight="1"/>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFF97316"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">● </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">PORTFOLIO STATUS  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">VIGILANCE</t>
+          </r>
+        </is>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFF59E0B"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">● </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">JEV · PD 12M  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">3,8 % · MARKOV</t>
+          </r>
+        </is>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FF06B6D4"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">● </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">TYPESAFE  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">24 retours · 8 en revue</t>
+          </r>
+        </is>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FF16A34A"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">● </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">CONTRÔLES  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">10 / 10 conformes</t>
+          </r>
+        </is>
+      </c>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+    </row>
+    <row r="11" ht="10" customHeight="1"/>
+    <row r="12" ht="8" customHeight="1">
+      <c r="A12" s="104"/>
+      <c r="B12" s="104"/>
+      <c r="C12" s="104"/>
+      <c r="D12" s="104"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="104"/>
+      <c r="M12" s="113"/>
+      <c r="N12" s="113"/>
+      <c r="O12" s="113"/>
+      <c r="P12" s="113"/>
+      <c r="Q12" s="113"/>
+      <c r="R12" s="113"/>
+      <c r="S12" s="113"/>
+      <c r="T12" s="113"/>
+      <c r="U12" s="113"/>
+      <c r="V12" s="113"/>
+      <c r="W12" s="113"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">01</t>
         </is>
       </c>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91"/>
-      <c r="D10" s="92" t="inlineStr">
+      <c r="B13" s="105"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">IMPAYÉS EN HAUSSE</t>
         </is>
       </c>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="92"/>
-      <c r="K10" s="92"/>
-      <c r="M10" s="96" t="inlineStr">
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="106"/>
+      <c r="K13" s="106"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">02</t>
         </is>
       </c>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="92" t="inlineStr">
+      <c r="N13" s="105"/>
+      <c r="O13" s="105"/>
+      <c r="P13" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">CONCENTRATION</t>
         </is>
       </c>
-      <c r="Q10" s="92"/>
-      <c r="R10" s="92"/>
-      <c r="S10" s="92"/>
-      <c r="T10" s="92"/>
-      <c r="U10" s="92"/>
-      <c r="V10" s="92"/>
-      <c r="W10" s="92"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="91"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="93" t="inlineStr">
+      <c r="Q13" s="106"/>
+      <c r="R13" s="106"/>
+      <c r="S13" s="106"/>
+      <c r="T13" s="106"/>
+      <c r="U13" s="106"/>
+      <c r="V13" s="106"/>
+      <c r="W13" s="106"/>
+      <c r="X13" s="20"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="105"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="105"/>
+      <c r="D14" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">+333,3 M XOF</t>
         </is>
       </c>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="93"/>
-      <c r="K11" s="93"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="96"/>
-      <c r="P11" s="97" t="inlineStr">
+      <c r="E14" s="107"/>
+      <c r="F14" s="107"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="107"/>
+      <c r="J14" s="107"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="105"/>
+      <c r="N14" s="105"/>
+      <c r="O14" s="105"/>
+      <c r="P14" s="114" t="inlineStr">
         <is>
           <t xml:space="preserve">TOP 10 = 8,3 %</t>
         </is>
       </c>
-      <c r="Q11" s="97"/>
-      <c r="R11" s="97"/>
-      <c r="S11" s="97"/>
-      <c r="T11" s="97"/>
-      <c r="U11" s="97"/>
-      <c r="V11" s="97"/>
-      <c r="W11" s="97"/>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="D12" s="94" t="inlineStr">
+      <c r="Q14" s="114"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="114"/>
+      <c r="T14" s="114"/>
+      <c r="U14" s="114"/>
+      <c r="V14" s="114"/>
+      <c r="W14" s="114"/>
+      <c r="X14" s="20"/>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="108"/>
+      <c r="B15" s="108"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">Les impayés passent de 31,56 Md à 31,89 Md XOF depuis le 31/08/2026. Nouveaux impayés : 8,5 M (3 % des hausses) ; régularisations : 0 ; remboursements partiels : 0.</t>
         </is>
       </c>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
-      <c r="P12" s="94" t="inlineStr">
+      <c r="E15" s="109"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="109"/>
+      <c r="J15" s="109"/>
+      <c r="K15" s="109"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="108"/>
+      <c r="N15" s="108"/>
+      <c r="O15" s="108"/>
+      <c r="P15" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">Les 10 premiers clients portent 70,74 Md XOF sur 850,39 Md. Premier client : SOCIETE 0378 (1,0 %). Premier segment : X (100 %).</t>
         </is>
       </c>
-      <c r="Q12" s="94"/>
-      <c r="R12" s="94"/>
-      <c r="S12" s="94"/>
-      <c r="T12" s="94"/>
-      <c r="U12" s="94"/>
-      <c r="V12" s="94"/>
-      <c r="W12" s="94"/>
-    </row>
-    <row r="13" ht="8" customHeight="1">
-      <c r="A13" s="95"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="95"/>
-      <c r="K13" s="95"/>
-      <c r="M13" s="95"/>
-      <c r="N13" s="95"/>
-      <c r="O13" s="95"/>
-      <c r="P13" s="95"/>
-      <c r="Q13" s="95"/>
-      <c r="R13" s="95"/>
-      <c r="S13" s="95"/>
-      <c r="T13" s="95"/>
-      <c r="U13" s="95"/>
-      <c r="V13" s="95"/>
-      <c r="W13" s="95"/>
-    </row>
-    <row r="14" ht="6" customHeight="1"/>
-    <row r="16" ht="12" customHeight="1"/>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="98" t="inlineStr">
+      <c r="Q15" s="109"/>
+      <c r="R15" s="109"/>
+      <c r="S15" s="109"/>
+      <c r="T15" s="109"/>
+      <c r="U15" s="109"/>
+      <c r="V15" s="109"/>
+      <c r="W15" s="109"/>
+      <c r="X15" s="20"/>
+    </row>
+    <row r="16" ht="8" customHeight="1">
+      <c r="A16" s="111"/>
+      <c r="B16" s="110"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="110"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="110"/>
+      <c r="P16" s="110"/>
+      <c r="Q16" s="110"/>
+      <c r="R16" s="110"/>
+      <c r="S16" s="110"/>
+      <c r="T16" s="110"/>
+      <c r="U16" s="110"/>
+      <c r="V16" s="110"/>
+      <c r="W16" s="112"/>
+      <c r="X16" s="20"/>
+    </row>
+    <row r="17" ht="8" customHeight="1">
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="20"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
+      <c r="V17" s="21"/>
+      <c r="W17" s="21"/>
+      <c r="X17" s="20"/>
+    </row>
+    <row r="19" ht="8" customHeight="1">
+      <c r="A19" s="115"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="115"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="115"/>
+      <c r="M19" s="104"/>
+      <c r="N19" s="104"/>
+      <c r="O19" s="104"/>
+      <c r="P19" s="104"/>
+      <c r="Q19" s="104"/>
+      <c r="R19" s="104"/>
+      <c r="S19" s="104"/>
+      <c r="T19" s="104"/>
+      <c r="U19" s="104"/>
+      <c r="V19" s="104"/>
+      <c r="W19" s="104"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">03</t>
         </is>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="92" t="inlineStr">
+      <c r="B20" s="105"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">MIGRATION</t>
         </is>
       </c>
-      <c r="E17" s="92"/>
-      <c r="F17" s="92"/>
-      <c r="G17" s="92"/>
-      <c r="H17" s="92"/>
-      <c r="I17" s="92"/>
-      <c r="J17" s="92"/>
-      <c r="K17" s="92"/>
-      <c r="M17" s="91" t="inlineStr">
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">04</t>
         </is>
       </c>
-      <c r="N17" s="91"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="92" t="inlineStr">
+      <c r="N20" s="105"/>
+      <c r="O20" s="105"/>
+      <c r="P20" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">ACTION</t>
         </is>
       </c>
-      <c r="Q17" s="92"/>
-      <c r="R17" s="92"/>
-      <c r="S17" s="92"/>
-      <c r="T17" s="92"/>
-      <c r="U17" s="92"/>
-      <c r="V17" s="92"/>
-      <c r="W17" s="92"/>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="98"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="99" t="inlineStr">
+      <c r="Q20" s="106"/>
+      <c r="R20" s="106"/>
+      <c r="S20" s="106"/>
+      <c r="T20" s="106"/>
+      <c r="U20" s="106"/>
+      <c r="V20" s="106"/>
+      <c r="W20" s="106"/>
+      <c r="X20" s="20"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="105"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="116" t="inlineStr">
         <is>
           <t xml:space="preserve">9 dossiers</t>
         </is>
       </c>
-      <c r="E18" s="99"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="99"/>
-      <c r="H18" s="99"/>
-      <c r="I18" s="99"/>
-      <c r="J18" s="99"/>
-      <c r="K18" s="99"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="93" t="inlineStr">
+      <c r="E21" s="116"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="116"/>
+      <c r="I21" s="116"/>
+      <c r="J21" s="116"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="105"/>
+      <c r="N21" s="105"/>
+      <c r="O21" s="105"/>
+      <c r="P21" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">54 dossiers</t>
         </is>
       </c>
-      <c r="Q18" s="93"/>
-      <c r="R18" s="93"/>
-      <c r="S18" s="93"/>
-      <c r="T18" s="93"/>
-      <c r="U18" s="93"/>
-      <c r="V18" s="93"/>
-      <c r="W18" s="93"/>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="D19" s="94" t="inlineStr">
+      <c r="Q21" s="107"/>
+      <c r="R21" s="107"/>
+      <c r="S21" s="107"/>
+      <c r="T21" s="107"/>
+      <c r="U21" s="107"/>
+      <c r="V21" s="107"/>
+      <c r="W21" s="107"/>
+      <c r="X21" s="20"/>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">9 clients ont migré vers une tranche d'impayé plus dégradée (1,3 % des clients suivis), dont 6 au-delà de 90 jours ou en Stage 3 pour 3,49 Md XOF d'encours.</t>
         </is>
       </c>
-      <c r="E19" s="94"/>
-      <c r="F19" s="94"/>
-      <c r="G19" s="94"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="94"/>
-      <c r="J19" s="94"/>
-      <c r="K19" s="94"/>
-      <c r="P19" s="94" t="inlineStr">
+      <c r="E22" s="109"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="109"/>
+      <c r="H22" s="109"/>
+      <c r="I22" s="109"/>
+      <c r="J22" s="109"/>
+      <c r="K22" s="109"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="108"/>
+      <c r="N22" s="108"/>
+      <c r="O22" s="108"/>
+      <c r="P22" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">6 dossiers critiques (3,49 Md XOF) et 48 en priorité haute nécessitent une intervention. Premier dossier : SOCIETE 0450 (3,03 Md, 304 j).</t>
         </is>
       </c>
-      <c r="Q19" s="94"/>
-      <c r="R19" s="94"/>
-      <c r="S19" s="94"/>
-      <c r="T19" s="94"/>
-      <c r="U19" s="94"/>
-      <c r="V19" s="94"/>
-      <c r="W19" s="94"/>
-    </row>
-    <row r="20" ht="8" customHeight="1">
-      <c r="A20" s="95"/>
-      <c r="B20" s="95"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="95"/>
-      <c r="I20" s="95"/>
-      <c r="J20" s="95"/>
-      <c r="K20" s="95"/>
-      <c r="M20" s="95"/>
-      <c r="N20" s="95"/>
-      <c r="O20" s="95"/>
-      <c r="P20" s="95"/>
-      <c r="Q20" s="95"/>
-      <c r="R20" s="95"/>
-      <c r="S20" s="95"/>
-      <c r="T20" s="95"/>
-      <c r="U20" s="95"/>
-      <c r="V20" s="95"/>
-      <c r="W20" s="95"/>
-    </row>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="23" ht="12" customHeight="1"/>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="100" t="inlineStr">
+      <c r="Q22" s="109"/>
+      <c r="R22" s="109"/>
+      <c r="S22" s="109"/>
+      <c r="T22" s="109"/>
+      <c r="U22" s="109"/>
+      <c r="V22" s="109"/>
+      <c r="W22" s="109"/>
+      <c r="X22" s="20"/>
+    </row>
+    <row r="23" ht="8" customHeight="1">
+      <c r="A23" s="111"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="111"/>
+      <c r="N23" s="110"/>
+      <c r="O23" s="110"/>
+      <c r="P23" s="110"/>
+      <c r="Q23" s="110"/>
+      <c r="R23" s="110"/>
+      <c r="S23" s="110"/>
+      <c r="T23" s="110"/>
+      <c r="U23" s="110"/>
+      <c r="V23" s="110"/>
+      <c r="W23" s="112"/>
+      <c r="X23" s="20"/>
+    </row>
+    <row r="24" ht="8" customHeight="1">
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="20"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="21"/>
+      <c r="U24" s="21"/>
+      <c r="V24" s="21"/>
+      <c r="W24" s="21"/>
+      <c r="X24" s="20"/>
+    </row>
+    <row r="26" ht="8" customHeight="1">
+      <c r="A26" s="117"/>
+      <c r="B26" s="117"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="117"/>
+      <c r="M26" s="119"/>
+      <c r="N26" s="119"/>
+      <c r="O26" s="119"/>
+      <c r="P26" s="119"/>
+      <c r="Q26" s="119"/>
+      <c r="R26" s="119"/>
+      <c r="S26" s="119"/>
+      <c r="T26" s="119"/>
+      <c r="U26" s="119"/>
+      <c r="V26" s="119"/>
+      <c r="W26" s="119"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">05</t>
         </is>
       </c>
-      <c r="B24" s="100"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="92" t="inlineStr">
+      <c r="B27" s="105"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">STAGE 2 &amp; 3</t>
         </is>
       </c>
-      <c r="E24" s="92"/>
-      <c r="F24" s="92"/>
-      <c r="G24" s="92"/>
-      <c r="H24" s="92"/>
-      <c r="I24" s="92"/>
-      <c r="J24" s="92"/>
-      <c r="K24" s="92"/>
-      <c r="M24" s="102" t="inlineStr">
+      <c r="E27" s="106"/>
+      <c r="F27" s="106"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="106"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="106"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">06</t>
         </is>
       </c>
-      <c r="N24" s="102"/>
-      <c r="O24" s="102"/>
-      <c r="P24" s="92" t="inlineStr">
+      <c r="N27" s="105"/>
+      <c r="O27" s="105"/>
+      <c r="P27" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">RÉGULARISATIONS</t>
         </is>
       </c>
-      <c r="Q24" s="92"/>
-      <c r="R24" s="92"/>
-      <c r="S24" s="92"/>
-      <c r="T24" s="92"/>
-      <c r="U24" s="92"/>
-      <c r="V24" s="92"/>
-      <c r="W24" s="92"/>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="100"/>
-      <c r="B25" s="100"/>
-      <c r="C25" s="100"/>
-      <c r="D25" s="101" t="inlineStr">
+      <c r="Q27" s="106"/>
+      <c r="R27" s="106"/>
+      <c r="S27" s="106"/>
+      <c r="T27" s="106"/>
+      <c r="U27" s="106"/>
+      <c r="V27" s="106"/>
+      <c r="W27" s="106"/>
+      <c r="X27" s="20"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="105"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">583,23 Md XOF</t>
         </is>
       </c>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="101"/>
-      <c r="H25" s="101"/>
-      <c r="I25" s="101"/>
-      <c r="J25" s="101"/>
-      <c r="K25" s="101"/>
-      <c r="M25" s="102"/>
-      <c r="N25" s="102"/>
-      <c r="O25" s="102"/>
-      <c r="P25" s="103" t="inlineStr">
+      <c r="E28" s="118"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="118"/>
+      <c r="H28" s="118"/>
+      <c r="I28" s="118"/>
+      <c r="J28" s="118"/>
+      <c r="K28" s="118"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="105"/>
+      <c r="N28" s="105"/>
+      <c r="O28" s="105"/>
+      <c r="P28" s="120" t="inlineStr">
         <is>
           <t xml:space="preserve">0 dossiers</t>
         </is>
       </c>
-      <c r="Q25" s="103"/>
-      <c r="R25" s="103"/>
-      <c r="S25" s="103"/>
-      <c r="T25" s="103"/>
-      <c r="U25" s="103"/>
-      <c r="V25" s="103"/>
-      <c r="W25" s="103"/>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="D26" s="94" t="inlineStr">
+      <c r="Q28" s="120"/>
+      <c r="R28" s="120"/>
+      <c r="S28" s="120"/>
+      <c r="T28" s="120"/>
+      <c r="U28" s="120"/>
+      <c r="V28" s="120"/>
+      <c r="W28" s="120"/>
+      <c r="X28" s="20"/>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="108"/>
+      <c r="B29" s="108"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">Stage 2 : 259,46 Md (30,5 % de l'encours) ; −947,9 M sur le mois. Stage 3 : 323,78 Md (38,1 %) ; +3,49 Md. Provisions : 37,32 Md XOF.</t>
         </is>
       </c>
-      <c r="E26" s="94"/>
-      <c r="F26" s="94"/>
-      <c r="G26" s="94"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="94"/>
-      <c r="J26" s="94"/>
-      <c r="K26" s="94"/>
-      <c r="P26" s="94" t="inlineStr">
+      <c r="E29" s="109"/>
+      <c r="F29" s="109"/>
+      <c r="G29" s="109"/>
+      <c r="H29" s="109"/>
+      <c r="I29" s="109"/>
+      <c r="J29" s="109"/>
+      <c r="K29" s="109"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="108"/>
+      <c r="N29" s="108"/>
+      <c r="O29" s="108"/>
+      <c r="P29" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">0 clients en impayé au 31/08/2026 sont revenus à jour, soit 0 XOF d'impayés résorbés.</t>
         </is>
       </c>
-      <c r="Q26" s="94"/>
-      <c r="R26" s="94"/>
-      <c r="S26" s="94"/>
-      <c r="T26" s="94"/>
-      <c r="U26" s="94"/>
-      <c r="V26" s="94"/>
-      <c r="W26" s="94"/>
-    </row>
-    <row r="27" ht="8" customHeight="1">
-      <c r="A27" s="95"/>
-      <c r="B27" s="95"/>
-      <c r="C27" s="95"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="95"/>
-      <c r="G27" s="95"/>
-      <c r="H27" s="95"/>
-      <c r="I27" s="95"/>
-      <c r="J27" s="95"/>
-      <c r="K27" s="95"/>
-      <c r="M27" s="95"/>
-      <c r="N27" s="95"/>
-      <c r="O27" s="95"/>
-      <c r="P27" s="95"/>
-      <c r="Q27" s="95"/>
-      <c r="R27" s="95"/>
-      <c r="S27" s="95"/>
-      <c r="T27" s="95"/>
-      <c r="U27" s="95"/>
-      <c r="V27" s="95"/>
-      <c r="W27" s="95"/>
-    </row>
-    <row r="28" ht="6" customHeight="1"/>
+      <c r="Q29" s="109"/>
+      <c r="R29" s="109"/>
+      <c r="S29" s="109"/>
+      <c r="T29" s="109"/>
+      <c r="U29" s="109"/>
+      <c r="V29" s="109"/>
+      <c r="W29" s="109"/>
+      <c r="X29" s="20"/>
+    </row>
+    <row r="30" ht="8" customHeight="1">
+      <c r="A30" s="111"/>
+      <c r="B30" s="110"/>
+      <c r="C30" s="110"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="110"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="112"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="111"/>
+      <c r="N30" s="110"/>
+      <c r="O30" s="110"/>
+      <c r="P30" s="110"/>
+      <c r="Q30" s="110"/>
+      <c r="R30" s="110"/>
+      <c r="S30" s="110"/>
+      <c r="T30" s="110"/>
+      <c r="U30" s="110"/>
+      <c r="V30" s="110"/>
+      <c r="W30" s="112"/>
+      <c r="X30" s="20"/>
+    </row>
+    <row r="31" ht="8" customHeight="1">
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="20"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
+      <c r="R31" s="21"/>
+      <c r="S31" s="21"/>
+      <c r="T31" s="21"/>
+      <c r="U31" s="21"/>
+      <c r="V31" s="21"/>
+      <c r="W31" s="21"/>
+      <c r="X31" s="20"/>
+    </row>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="121"/>
+      <c r="B33" s="121"/>
+      <c r="C33" s="121"/>
+      <c r="D33" s="121"/>
+      <c r="E33" s="121"/>
+      <c r="F33" s="121"/>
+      <c r="G33" s="121"/>
+      <c r="H33" s="121"/>
+      <c r="I33" s="121"/>
+      <c r="J33" s="121"/>
+      <c r="K33" s="121"/>
+      <c r="M33" s="123"/>
+      <c r="N33" s="123"/>
+      <c r="O33" s="123"/>
+      <c r="P33" s="123"/>
+      <c r="Q33" s="123"/>
+      <c r="R33" s="123"/>
+      <c r="S33" s="123"/>
+      <c r="T33" s="123"/>
+      <c r="U33" s="123"/>
+      <c r="V33" s="123"/>
+      <c r="W33" s="123"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07</t>
+        </is>
+      </c>
+      <c r="B34" s="105"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROSPECTIF · JEV</t>
+        </is>
+      </c>
+      <c r="E34" s="106"/>
+      <c r="F34" s="106"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="106"/>
+      <c r="I34" s="106"/>
+      <c r="J34" s="106"/>
+      <c r="K34" s="106"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08</t>
+        </is>
+      </c>
+      <c r="N34" s="105"/>
+      <c r="O34" s="105"/>
+      <c r="P34" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TYPESAFE · RETOURS</t>
+        </is>
+      </c>
+      <c r="Q34" s="106"/>
+      <c r="R34" s="106"/>
+      <c r="S34" s="106"/>
+      <c r="T34" s="106"/>
+      <c r="U34" s="106"/>
+      <c r="V34" s="106"/>
+      <c r="W34" s="106"/>
+      <c r="X34" s="20"/>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="105"/>
+      <c r="B35" s="105"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PD 12M = 3,8 %</t>
+        </is>
+      </c>
+      <c r="E35" s="122"/>
+      <c r="F35" s="122"/>
+      <c r="G35" s="122"/>
+      <c r="H35" s="122"/>
+      <c r="I35" s="122"/>
+      <c r="J35" s="122"/>
+      <c r="K35" s="122"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="105"/>
+      <c r="N35" s="105"/>
+      <c r="O35" s="105"/>
+      <c r="P35" s="124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 commentaires lus</t>
+        </is>
+      </c>
+      <c r="Q35" s="124"/>
+      <c r="R35" s="124"/>
+      <c r="S35" s="124"/>
+      <c r="T35" s="124"/>
+      <c r="U35" s="124"/>
+      <c r="V35" s="124"/>
+      <c r="W35" s="124"/>
+      <c r="X35" s="20"/>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="108"/>
+      <c r="B36" s="108"/>
+      <c r="C36" s="108"/>
+      <c r="D36" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probabilité qu'un client sain aujourd'hui devienne douteux sous 12 mois (MARKOV, N = 17 850, 9 mois, confiance faible). Scénario sévère : 66,36 Md XOF d'entrées en douteux attendues (SIMULATED). Estimation indicative : historique insuffisant pour une calibration robuste.</t>
+        </is>
+      </c>
+      <c r="E36" s="109"/>
+      <c r="F36" s="109"/>
+      <c r="G36" s="109"/>
+      <c r="H36" s="109"/>
+      <c r="I36" s="109"/>
+      <c r="J36" s="109"/>
+      <c r="K36" s="109"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="108"/>
+      <c r="N36" s="108"/>
+      <c r="O36" s="108"/>
+      <c r="P36" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 dossiers en revue analyste (confiance faible ou incohérence), dont 0 par contrôle d'auto-cohérence ; 2 promesses tombent après la date de bascule. TypeSafe ne produit aucun chiffre.</t>
+        </is>
+      </c>
+      <c r="Q36" s="109"/>
+      <c r="R36" s="109"/>
+      <c r="S36" s="109"/>
+      <c r="T36" s="109"/>
+      <c r="U36" s="109"/>
+      <c r="V36" s="109"/>
+      <c r="W36" s="109"/>
+      <c r="X36" s="20"/>
+    </row>
+    <row r="37" ht="8" customHeight="1">
+      <c r="A37" s="111"/>
+      <c r="B37" s="110"/>
+      <c r="C37" s="110"/>
+      <c r="D37" s="110"/>
+      <c r="E37" s="110"/>
+      <c r="F37" s="110"/>
+      <c r="G37" s="110"/>
+      <c r="H37" s="110"/>
+      <c r="I37" s="110"/>
+      <c r="J37" s="110"/>
+      <c r="K37" s="112"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="111"/>
+      <c r="N37" s="110"/>
+      <c r="O37" s="110"/>
+      <c r="P37" s="110"/>
+      <c r="Q37" s="110"/>
+      <c r="R37" s="110"/>
+      <c r="S37" s="110"/>
+      <c r="T37" s="110"/>
+      <c r="U37" s="110"/>
+      <c r="V37" s="110"/>
+      <c r="W37" s="112"/>
+      <c r="X37" s="20"/>
+    </row>
+    <row r="38" ht="8" customHeight="1">
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="20"/>
+      <c r="N38" s="21"/>
+      <c r="O38" s="21"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="21"/>
+      <c r="R38" s="21"/>
+      <c r="S38" s="21"/>
+      <c r="T38" s="21"/>
+      <c r="U38" s="21"/>
+      <c r="V38" s="21"/>
+      <c r="W38" s="21"/>
+      <c r="X38" s="20"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="75" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">01  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">TYPESAFE · RETOURS GESTIONNAIRES</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <i/>
+              <color rgb="FF64748B"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">    jugements jev-latest sur les commentaires (aucun chiffre produit par TypeSafe)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B41" s="75"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="75"/>
+      <c r="E41" s="75"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="75"/>
+      <c r="H41" s="75"/>
+      <c r="I41" s="75"/>
+      <c r="J41" s="75"/>
+      <c r="K41" s="75"/>
+      <c r="L41" s="75"/>
+      <c r="M41" s="75"/>
+      <c r="N41" s="75"/>
+      <c r="O41" s="75"/>
+      <c r="P41" s="75"/>
+      <c r="Q41" s="75"/>
+      <c r="R41" s="75"/>
+      <c r="S41" s="75"/>
+      <c r="T41" s="75"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="75"/>
+      <c r="W41" s="75"/>
+      <c r="X41" s="75"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 retours lus · 8 en revue analyste · 2 promesses après la date de bascule · 3 sans commentaire</t>
+        </is>
+      </c>
+      <c r="B42" s="125"/>
+      <c r="C42" s="125"/>
+      <c r="D42" s="125"/>
+      <c r="E42" s="125"/>
+      <c r="F42" s="125"/>
+      <c r="G42" s="125"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="125"/>
+      <c r="L42" s="125"/>
+      <c r="M42" s="125"/>
+      <c r="N42" s="125"/>
+      <c r="O42" s="125"/>
+      <c r="P42" s="125"/>
+      <c r="Q42" s="125"/>
+      <c r="R42" s="125"/>
+      <c r="S42" s="125"/>
+      <c r="T42" s="125"/>
+      <c r="U42" s="125"/>
+      <c r="V42" s="125"/>
+      <c r="W42" s="125"/>
+      <c r="X42" s="125"/>
+    </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="57">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="S1:X1"/>
-    <mergeCell ref="A2:O5"/>
+    <mergeCell ref="A2:O6"/>
     <mergeCell ref="P2:X2"/>
     <mergeCell ref="P3:X3"/>
     <mergeCell ref="P4:X4"/>
     <mergeCell ref="P5:X5"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="I7:P7"/>
-    <mergeCell ref="Q7:X7"/>
-    <mergeCell ref="A10:C11"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="M10:O11"/>
-    <mergeCell ref="P10:W10"/>
-    <mergeCell ref="P11:W11"/>
-    <mergeCell ref="P12:W12"/>
-    <mergeCell ref="A17:C18"/>
-    <mergeCell ref="D17:K17"/>
-    <mergeCell ref="D18:K18"/>
-    <mergeCell ref="D19:K19"/>
-    <mergeCell ref="M17:O18"/>
-    <mergeCell ref="P17:W17"/>
-    <mergeCell ref="P18:W18"/>
-    <mergeCell ref="P19:W19"/>
-    <mergeCell ref="A24:C25"/>
-    <mergeCell ref="D24:K24"/>
-    <mergeCell ref="D25:K25"/>
-    <mergeCell ref="D26:K26"/>
-    <mergeCell ref="M24:O25"/>
-    <mergeCell ref="P24:W24"/>
-    <mergeCell ref="P25:W25"/>
-    <mergeCell ref="P26:W26"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="I8:P8"/>
+    <mergeCell ref="Q8:X8"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="M10:R10"/>
+    <mergeCell ref="S10:X10"/>
+    <mergeCell ref="A13:C14"/>
+    <mergeCell ref="D13:K13"/>
+    <mergeCell ref="D14:K14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:K15"/>
+    <mergeCell ref="M13:O14"/>
+    <mergeCell ref="P13:W13"/>
+    <mergeCell ref="P14:W14"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="P15:W15"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:K20"/>
+    <mergeCell ref="D21:K21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:K22"/>
+    <mergeCell ref="M20:O21"/>
+    <mergeCell ref="P20:W20"/>
+    <mergeCell ref="P21:W21"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="P22:W22"/>
+    <mergeCell ref="A27:C28"/>
+    <mergeCell ref="D27:K27"/>
+    <mergeCell ref="D28:K28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:K29"/>
+    <mergeCell ref="M27:O28"/>
+    <mergeCell ref="P27:W27"/>
+    <mergeCell ref="P28:W28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="P29:W29"/>
+    <mergeCell ref="A34:C35"/>
+    <mergeCell ref="D34:K34"/>
+    <mergeCell ref="D35:K35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:K36"/>
+    <mergeCell ref="M34:O35"/>
+    <mergeCell ref="P34:W34"/>
+    <mergeCell ref="P35:W35"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="P36:W36"/>
+    <mergeCell ref="A41:X41"/>
+    <mergeCell ref="A42:X42"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A7" location="'EXECUTIVE'!A1" display="EXECUTIVE"/>
-    <hyperlink ref="Q7" location="'AUDIT'!A1" display="AUDIT"/>
+    <hyperlink ref="A8" location="'EXECUTIVE'!A1" display="EXECUTIVE"/>
+    <hyperlink ref="Q8" location="'AUDIT'!A1" display="AUDIT"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.45" bottom="0.5" header="0.2" footer="0.25"/>
@@ -5925,6 +7883,9 @@
     <oddHeader>&amp;L&amp;8&amp;K003DA5ECOBANK SÉNÉGAL · CREDIT RISK INTELLIGENCE&amp;R&amp;8&amp;K64748BArrêté 30/09/2026</oddHeader>
     <oddFooter>&amp;L&amp;8&amp;K64748BINSIGHTS · INTERNAL USE ONLY&amp;R&amp;8&amp;K64748BPage &amp;P / &amp;N</oddFooter>
   </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -5934,39 +7895,56 @@
     <tabColor rgb="FF001B4D"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="7" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="9" max="9" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
-              <b/>
               <color rgb="FFC8A951"/>
-              <sz val="9"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">◆ </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="8.5"/>
             </rPr>
             <t xml:space="preserve">ECOBANK SÉNÉGAL</t>
           </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
-              <color rgb="FFC7D7F5"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">   ·   CREDIT RISK INTELLIGENCE</t>
+              <color rgb="FF9DB4E0"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">   ·   CREDIT RISK INTELLIGENCE   ·   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFFFFFFF"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">AUDIT</t>
           </r>
         </is>
       </c>
@@ -5978,7 +7956,7 @@
             <rPr>
               <rFont val="Segoe UI"/>
               <color rgb="FF8EA6D6"/>
-              <sz val="8"/>
+              <sz val="7.5"/>
             </rPr>
             <t xml:space="preserve">INTERNAL USE ONLY  ·  </t>
           </r>
@@ -5987,27 +7965,37 @@
               <rFont val="Segoe UI"/>
               <b/>
               <color rgb="FFC8A951"/>
-              <sz val="8"/>
+              <sz val="7.5"/>
             </rPr>
             <t xml:space="preserve">RI 1.0</t>
           </r>
         </is>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" ht="10" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
               <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">E C O B A N K   S É N É G A L
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
               <color rgb="FFFFFFFF"/>
-              <sz val="22"/>
+              <sz val="26"/>
             </rPr>
             <t xml:space="preserve">AUDIT REPORT
 </t>
@@ -6016,19 +8004,9 @@
             <rPr>
               <rFont val="Segoe UI"/>
               <color rgb="FFC7D7F5"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Traçabilité, contrôles automatiques et provenance
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b/>
-              <color rgb="FFC8A951"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">ECOBANK SÉNÉGAL · DIRECTION DES RISQUES</t>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">Traçabilité, contrôles automatiques et provenance</t>
           </r>
         </is>
       </c>
@@ -6037,15 +8015,11 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REPORTING DATE</t>
-        </is>
-      </c>
+      <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -6054,80 +8028,280 @@
       <c r="F3" s="3"/>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/09/2026</t>
+          <t xml:space="preserve">REPORTING DATE</t>
         </is>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" ht="38" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PERIMETER</t>
-        </is>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 SEPTEMBER 2026</t>
+        </is>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORTFOLIO MONITORING</t>
+        </is>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Portefeuille Ecobank Sénégal · 700 clients · 2 500 lignes ACTE 7</t>
         </is>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EXECUTIVE</t>
-        </is>
-      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" ht="2.5" customHeight="1">
+      <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INSIGHTS</t>
-        </is>
-      </c>
+      <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AUDIT</t>
-        </is>
-      </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" ht="8" customHeight="1"/>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="60" t="inlineStr">
-        <is>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" ht="23" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FF7C93C9"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">◆  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF003DA5"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">EXECUTIVE</t>
+          </r>
+        </is>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FF7C93C9"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">✦  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF003DA5"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">INSIGHTS</t>
+          </r>
+        </is>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFC8A951"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">§  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFFFFFFF"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">AUDIT</t>
+          </r>
+        </is>
+      </c>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" ht="5" customHeight="1"/>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFF97316"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">● </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">PORTFOLIO STATUS  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">VIGILANCE</t>
+          </r>
+        </is>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFF59E0B"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">● </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">JEV · PD 12M  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">3,8 % · MARKOV</t>
+          </r>
+        </is>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FF06B6D4"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">● </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">TYPESAFE  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">24 retours · 8 en revue</t>
+          </r>
+        </is>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FF16A34A"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">● </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF64748B"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">CONTRÔLES  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">10 / 10 conformes</t>
+          </r>
+        </is>
+      </c>
+      <c r="I10" s="13"/>
+    </row>
+    <row r="11" ht="10" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="73" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">01  </t>
+          </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
@@ -6140,245 +8314,255 @@
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
+              <i/>
               <color rgb="FF64748B"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">   arrêtés utilisés · source canonique unique</t>
-          </r>
-        </is>
-      </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="104" t="inlineStr">
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">    arrêtés utilisés · source canonique unique</t>
+          </r>
+        </is>
+      </c>
+      <c r="B12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">Arrêté</t>
         </is>
       </c>
-      <c r="B10" s="104" t="inlineStr">
+      <c r="B13" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">Fichier</t>
         </is>
       </c>
-      <c r="C10" s="104" t="inlineStr">
+      <c r="C13" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">Clients</t>
         </is>
       </c>
-      <c r="D10" s="104" t="inlineStr">
+      <c r="D13" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">Usage</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="105" t="inlineStr">
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">31/01/2026</t>
         </is>
       </c>
-      <c r="B11" s="105" t="inlineStr">
+      <c r="B14" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">M_01.xlsx</t>
         </is>
       </c>
-      <c r="C11" s="105" t="inlineStr">
+      <c r="C14" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">700</t>
         </is>
       </c>
-      <c r="D11" s="105" t="inlineStr">
+      <c r="D14" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Tendances et sparklines</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="106" t="inlineStr">
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">28/02/2026</t>
         </is>
       </c>
-      <c r="B12" s="106" t="inlineStr">
+      <c r="B15" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">M_02.xlsx</t>
         </is>
       </c>
-      <c r="C12" s="106" t="inlineStr">
+      <c r="C15" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">700</t>
         </is>
       </c>
-      <c r="D12" s="106" t="inlineStr">
+      <c r="D15" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">Tendances et sparklines</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="105" t="inlineStr">
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">31/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="105" t="inlineStr">
+      <c r="B16" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">M_03.xlsx</t>
         </is>
       </c>
-      <c r="C13" s="105" t="inlineStr">
+      <c r="C16" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">700</t>
         </is>
       </c>
-      <c r="D13" s="105" t="inlineStr">
+      <c r="D16" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Tendances et sparklines</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="106" t="inlineStr">
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">30/04/2026</t>
         </is>
       </c>
-      <c r="B14" s="106" t="inlineStr">
+      <c r="B17" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">M_04.xlsx</t>
         </is>
       </c>
-      <c r="C14" s="106" t="inlineStr">
+      <c r="C17" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">700</t>
         </is>
       </c>
-      <c r="D14" s="106" t="inlineStr">
+      <c r="D17" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">Tendances et sparklines</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="105" t="inlineStr">
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">31/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="105" t="inlineStr">
+      <c r="B18" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">M_05.xlsx</t>
         </is>
       </c>
-      <c r="C15" s="105" t="inlineStr">
+      <c r="C18" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">700</t>
         </is>
       </c>
-      <c r="D15" s="105" t="inlineStr">
+      <c r="D18" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Tendances et sparklines</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="106" t="inlineStr">
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">30/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="106" t="inlineStr">
+      <c r="B19" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">M_06.xlsx</t>
         </is>
       </c>
-      <c r="C16" s="106" t="inlineStr">
+      <c r="C19" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">700</t>
         </is>
       </c>
-      <c r="D16" s="106" t="inlineStr">
+      <c r="D19" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">Tendances et sparklines</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="105" t="inlineStr">
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">31/07/2026</t>
         </is>
       </c>
-      <c r="B17" s="105" t="inlineStr">
+      <c r="B20" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">M_07.xlsx</t>
         </is>
       </c>
-      <c r="C17" s="105" t="inlineStr">
+      <c r="C20" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">700</t>
         </is>
       </c>
-      <c r="D17" s="105" t="inlineStr">
+      <c r="D20" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Tendances et sparklines</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="106" t="inlineStr">
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">31/08/2026</t>
         </is>
       </c>
-      <c r="B18" s="106" t="inlineStr">
+      <c r="B21" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">M_08.xlsx</t>
         </is>
       </c>
-      <c r="C18" s="106" t="inlineStr">
+      <c r="C21" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">700</t>
         </is>
       </c>
-      <c r="D18" s="106" t="inlineStr">
+      <c r="D21" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">Comparaison (N-1), pont et migrations</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="105" t="inlineStr">
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">30/09/2026</t>
         </is>
       </c>
-      <c r="B19" s="105" t="inlineStr">
+      <c r="B22" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">M_09.xlsx</t>
         </is>
       </c>
-      <c r="C19" s="105" t="inlineStr">
+      <c r="C22" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">700</t>
         </is>
       </c>
-      <c r="D19" s="105" t="inlineStr">
+      <c r="D22" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Arrêté de référence (N)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="107" t="inlineStr">
-        <is>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="129" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">02  </t>
+          </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
@@ -6391,245 +8575,277 @@
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
+              <i/>
               <color rgb="FF64748B"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">   vérifiés à la génération</t>
-          </r>
-        </is>
-      </c>
-      <c r="B21" s="107"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="107"/>
-      <c r="H21" s="107"/>
-      <c r="I21" s="107"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="104" t="inlineStr">
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">    vérifiés à la génération</t>
+          </r>
+        </is>
+      </c>
+      <c r="B24" s="129"/>
+      <c r="C24" s="129"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="129"/>
+      <c r="H24" s="129"/>
+      <c r="I24" s="129"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">Contrôle</t>
         </is>
       </c>
-      <c r="B22" s="104" t="inlineStr">
+      <c r="B25" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">Valeur</t>
         </is>
       </c>
-      <c r="C22" s="104" t="inlineStr">
+      <c r="C25" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">Référence</t>
         </is>
       </c>
-      <c r="D22" s="104" t="inlineStr">
+      <c r="D25" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">Résultat</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="105" t="inlineStr">
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Encours : somme des clients = agrégat APEX</t>
         </is>
       </c>
-      <c r="B23" s="105" t="inlineStr">
+      <c r="B26" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">850 385 585 746</t>
         </is>
       </c>
-      <c r="C23" s="105" t="inlineStr">
+      <c r="C26" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">850 385 585 746</t>
         </is>
       </c>
-      <c r="D23" s="108" t="inlineStr">
+      <c r="D26" s="130" t="inlineStr">
         <is>
           <t xml:space="preserve">✔ CONFORME</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="106" t="inlineStr">
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">Impayés : somme des clients = agrégat APEX</t>
         </is>
       </c>
-      <c r="B24" s="106" t="inlineStr">
+      <c r="B27" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">31 893 133 004</t>
         </is>
       </c>
-      <c r="C24" s="106" t="inlineStr">
+      <c r="C27" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">31 893 133 004</t>
         </is>
       </c>
-      <c r="D24" s="108" t="inlineStr">
+      <c r="D27" s="130" t="inlineStr">
         <is>
           <t xml:space="preserve">✔ CONFORME</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="105" t="inlineStr">
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Pont des impayés : ouverture + mouvements = clôture</t>
         </is>
       </c>
-      <c r="B25" s="105" t="inlineStr">
+      <c r="B28" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="C25" s="105" t="inlineStr">
+      <c r="C28" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="D25" s="108" t="inlineStr">
+      <c r="D28" s="130" t="inlineStr">
         <is>
           <t xml:space="preserve">✔ CONFORME</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="106" t="inlineStr">
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">Tranches : somme des encours par tranche = encours total</t>
         </is>
       </c>
-      <c r="B26" s="106" t="inlineStr">
+      <c r="B29" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">850 385 585 746</t>
         </is>
       </c>
-      <c r="C26" s="106" t="inlineStr">
+      <c r="C29" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">850 385 585 746</t>
         </is>
       </c>
-      <c r="D26" s="108" t="inlineStr">
+      <c r="D29" s="130" t="inlineStr">
         <is>
           <t xml:space="preserve">✔ CONFORME</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="105" t="inlineStr">
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Watchlist : encours ≤ encours total</t>
         </is>
       </c>
-      <c r="B27" s="105" t="inlineStr">
+      <c r="B30" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">322 705 241 935</t>
         </is>
       </c>
-      <c r="C27" s="105" t="inlineStr">
+      <c r="C30" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">322 705 241 935</t>
         </is>
       </c>
-      <c r="D27" s="108" t="inlineStr">
+      <c r="D30" s="130" t="inlineStr">
         <is>
           <t xml:space="preserve">✔ CONFORME</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="106" t="inlineStr">
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">Clients en double</t>
         </is>
       </c>
-      <c r="B28" s="106" t="inlineStr">
+      <c r="B31" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">700</t>
         </is>
       </c>
-      <c r="C28" s="106" t="inlineStr">
+      <c r="C31" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">700</t>
         </is>
       </c>
-      <c r="D28" s="108" t="inlineStr">
+      <c r="D31" s="130" t="inlineStr">
         <is>
           <t xml:space="preserve">✔ CONFORME</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="105" t="inlineStr">
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Valeurs non numériques (NaN / Infini)</t>
         </is>
       </c>
-      <c r="B29" s="105" t="inlineStr">
+      <c r="B32" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="C29" s="105" t="inlineStr">
+      <c r="C32" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="D29" s="108" t="inlineStr">
+      <c r="D32" s="130" t="inlineStr">
         <is>
           <t xml:space="preserve">✔ CONFORME</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="106" t="inlineStr">
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">Provisions de l'historique sur base IFRS 9 (comparables)</t>
         </is>
       </c>
-      <c r="B30" s="106" t="inlineStr">
+      <c r="B33" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="C30" s="106" t="inlineStr">
+      <c r="C33" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="D30" s="108" t="inlineStr">
+      <c r="D33" s="130" t="inlineStr">
         <is>
           <t xml:space="preserve">✔ CONFORME</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="105" t="inlineStr">
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEV : PD avec provenance pour chaque client de la watchlist</t>
+        </is>
+      </c>
+      <c r="B34" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289</t>
+        </is>
+      </c>
+      <c r="C34" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289</t>
+        </is>
+      </c>
+      <c r="D34" s="130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ CONFORME</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">Historique disponible pour les tendances</t>
         </is>
       </c>
-      <c r="B31" s="105" t="inlineStr">
+      <c r="B35" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="C31" s="105" t="inlineStr">
+      <c r="C35" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="D31" s="108" t="inlineStr">
+      <c r="D35" s="130" t="inlineStr">
         <is>
           <t xml:space="preserve">✔ CONFORME</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="61" t="inlineStr">
-        <is>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="74" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">03  </t>
+          </r>
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
@@ -6642,195 +8858,485 @@
           <r>
             <rPr>
               <rFont val="Segoe UI"/>
+              <i/>
               <color rgb="FF64748B"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">   identiques à l'écran, au PDF et à toutes les feuilles</t>
-          </r>
-        </is>
-      </c>
-      <c r="B33" s="61"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="61"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="104" t="inlineStr">
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">    identiques à l'écran, au PDF et à toutes les feuilles</t>
+          </r>
+        </is>
+      </c>
+      <c r="B37" s="74"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="74"/>
+      <c r="H37" s="74"/>
+      <c r="I37" s="74"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">Indicateur</t>
         </is>
       </c>
-      <c r="B34" s="104" t="inlineStr">
+      <c r="B38" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">Règle</t>
         </is>
       </c>
-      <c r="C34" s="104"/>
-      <c r="D34" s="104"/>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="105" t="inlineStr">
+      <c r="C38" s="126"/>
+      <c r="D38" s="126"/>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Tranches d'impayé</t>
         </is>
       </c>
-      <c r="B35" s="109" t="inlineStr">
+      <c r="B39" s="131" t="inlineStr">
         <is>
           <t xml:space="preserve">Sain · 1-30 j · 31-60 j · 61-90 j · &gt; 90 j / S3 (Stage 3, classe III/IV/V ou GL 292)</t>
         </is>
       </c>
-      <c r="C35" s="105"/>
-      <c r="D35" s="105"/>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="106" t="inlineStr">
+      <c r="C39" s="127"/>
+      <c r="D39" s="127"/>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">Criticité</t>
         </is>
       </c>
-      <c r="B36" s="110" t="inlineStr">
+      <c r="B40" s="132" t="inlineStr">
         <is>
           <t xml:space="preserve">CRITICAL : criticité APEX « CRITIQUE », migration vers &gt; 90 j / S3, ou 76-90 j · HIGH : « ÉLEVÉE », tranche 61-90 j ou migration · WATCH : Stage 2, 31-60 j, impayé en hausse · CURED : impayé N-1 régularisé</t>
         </is>
       </c>
-      <c r="C36" s="106"/>
-      <c r="D36" s="106"/>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="105" t="inlineStr">
+      <c r="C40" s="128"/>
+      <c r="D40" s="128"/>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Pont des impayés</t>
         </is>
       </c>
-      <c r="B37" s="109" t="inlineStr">
+      <c r="B41" s="131" t="inlineStr">
         <is>
           <t xml:space="preserve">Ouverture (N-1) + nouveaux impayés + détériorations + nouveaux clients + régularisations + remboursements partiels + sorties = clôture (N)</t>
         </is>
       </c>
-      <c r="C37" s="105"/>
-      <c r="D37" s="105"/>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="106" t="inlineStr">
+      <c r="C41" s="127"/>
+      <c r="D41" s="127"/>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">Provisions</t>
         </is>
       </c>
-      <c r="B38" s="110" t="inlineStr">
+      <c r="B42" s="132" t="inlineStr">
         <is>
           <t xml:space="preserve">ECL réel de l'ACTE 7, sinon modélisé par stage (1 % / 25 % / 100 %) — règle APEX</t>
         </is>
       </c>
-      <c r="C38" s="106"/>
-      <c r="D38" s="106"/>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="105" t="inlineStr">
+      <c r="C42" s="128"/>
+      <c r="D42" s="128"/>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Concentration</t>
         </is>
       </c>
-      <c r="B39" s="109" t="inlineStr">
+      <c r="B43" s="131" t="inlineStr">
         <is>
           <t xml:space="preserve">Top 10 clients, part du premier client, HHI (somme des parts au carré × 10 000)</t>
         </is>
       </c>
-      <c r="C39" s="105"/>
-      <c r="D39" s="105"/>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="106" t="inlineStr">
+      <c r="C43" s="127"/>
+      <c r="D43" s="127"/>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">Classes et stages</t>
         </is>
       </c>
-      <c r="B40" s="110" t="inlineStr">
+      <c r="B44" s="132" t="inlineStr">
         <is>
           <t xml:space="preserve">BCEAO, IFRS 9 et ACTE 7 calculés par APEX ; ce moteur ne les modifie pas</t>
         </is>
       </c>
-      <c r="C40" s="106"/>
-      <c r="D40" s="106"/>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="105" t="inlineStr">
+      <c r="C44" s="128"/>
+      <c r="D44" s="128"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">TypeSafe</t>
         </is>
       </c>
-      <c r="B41" s="109" t="inlineStr">
+      <c r="B45" s="131" t="inlineStr">
         <is>
           <t xml:space="preserve">Jugements uniquement (motif, crédibilité, incohérence) ; aucun chiffre ; revue analyste si confiance faible</t>
         </is>
       </c>
-      <c r="C41" s="105"/>
-      <c r="D41" s="105"/>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="106" t="inlineStr">
+      <c r="C45" s="127"/>
+      <c r="D45" s="127"/>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="128" t="inlineStr">
         <is>
           <t xml:space="preserve">JEV</t>
         </is>
       </c>
-      <c r="B42" s="110" t="inlineStr">
+      <c r="B46" s="132" t="inlineStr">
         <is>
           <t xml:space="preserve">Probabilités avec provenance obligatoire (OBSERVED, EMPIRICAL, MARKOV, EXPERT, STRESS, SIMULATED, HYBRID)</t>
         </is>
       </c>
-      <c r="C42" s="106"/>
-      <c r="D42" s="106"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Généré le 03/10/2026 10:41:12 · RI 1.0 · APEX Credit Risk OS · source : M_09.xlsx</t>
-        </is>
-      </c>
-      <c r="B44" s="111"/>
-      <c r="C44" s="111"/>
-      <c r="D44" s="111"/>
-      <c r="E44" s="111"/>
-      <c r="F44" s="111"/>
-      <c r="G44" s="111"/>
-      <c r="H44" s="111"/>
-      <c r="I44" s="111"/>
+      <c r="C46" s="128"/>
+      <c r="D46" s="128"/>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="133" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">04  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF001B4D"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">COUVERTURE JEV &amp; TYPESAFE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <i/>
+              <color rgb="FF64748B"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">    tout ce qui peut relever d'un jugement ou d'une probabilité</t>
+          </r>
+        </is>
+      </c>
+      <c r="B48" s="133"/>
+      <c r="C48" s="133"/>
+      <c r="D48" s="133"/>
+      <c r="E48" s="133"/>
+      <c r="F48" s="133"/>
+      <c r="G48" s="133"/>
+      <c r="H48" s="133"/>
+      <c r="I48" s="133"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Domaine</t>
+        </is>
+      </c>
+      <c r="B49" s="126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contrôle</t>
+        </is>
+      </c>
+      <c r="C49" s="126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couverture</t>
+        </is>
+      </c>
+      <c r="D49" s="126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Détail</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="19" customHeight="1">
+      <c r="A50" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probabilité de dégradation (PD 3/6/12M)</t>
+        </is>
+      </c>
+      <c r="B50" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEV · MARKOV / HYBRID</t>
+        </is>
+      </c>
+      <c r="C50" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D50" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">calibré sur 9 arrêtés · MARKOV · Markov mensuel portefeuille · N = 17 850 · Historique = 9 mois · Horizon = 12 m · Confiance = faible</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taux observé (cohortes)</t>
+        </is>
+      </c>
+      <c r="B51" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEV · EMPIRICAL</t>
+        </is>
+      </c>
+      <c r="C51" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D51" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pas de cohorte complète à 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stress et scénarios</t>
+        </is>
+      </c>
+      <c r="B52" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEV · STRESS / SIMULATED</t>
+        </is>
+      </c>
+      <c r="C52" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D52" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">×1,5 et ×2,0 · Monte Carlo</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PD par dossier de la watchlist</t>
+        </is>
+      </c>
+      <c r="B53" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEV · HYBRID (Markov + EWS + expert)</t>
+        </is>
+      </c>
+      <c r="C53" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ 289 / 289</t>
+        </is>
+      </c>
+      <c r="D53" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signaux TypeSafe et APEX en multiplicateurs EXPERT affichés</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Effet des actions sur la PD</t>
+        </is>
+      </c>
+      <c r="B54" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEV · recalcul par le code</t>
+        </is>
+      </c>
+      <c r="C54" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D54" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">régularisation, règlement partiel, levée des signaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motif, crédibilité, incohérence, statut</t>
+        </is>
+      </c>
+      <c r="B55" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TypeSafe · Choice / Score / Noul</t>
+        </is>
+      </c>
+      <c r="C55" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ 24 dossiers</t>
+        </is>
+      </c>
+      <c r="D55" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commentaires gestionnaires (feuille _TYPESAFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="19" customHeight="1">
+      <c r="A56" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nature de l'entité, intra-groupe, segment</t>
+        </is>
+      </c>
+      <c r="B56" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TypeSafe · Choice / Noul</t>
+        </is>
+      </c>
+      <c r="C56" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D56" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">noms de clients</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="19" customHeight="1">
+      <c r="A57" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Urgence et orientation (re-classement, routage)</t>
+        </is>
+      </c>
+      <c r="B57" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TypeSafe · Score / Choice</t>
+        </is>
+      </c>
+      <c r="C57" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en attente</t>
+        </is>
+      </c>
+      <c r="D57" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">capacités avancées</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auto-cohérence et cohérence du plan</t>
+        </is>
+      </c>
+      <c r="B58" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TypeSafe · Noul + Choice croisés</t>
+        </is>
+      </c>
+      <c r="C58" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en attente</t>
+        </is>
+      </c>
+      <c r="D58" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">divergence → revue analyste</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montants, ratios, classes BCEAO / IFRS 9 / ACTE 7</t>
+        </is>
+      </c>
+      <c r="B59" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code APEX uniquement</t>
+        </is>
+      </c>
+      <c r="C59" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ code</t>
+        </is>
+      </c>
+      <c r="D59" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jamais confiés à TypeSafe ni à JEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Généré le 03/10/2026 13:32:39 · RI 1.0 · APEX Credit Risk OS · source : M_09.xlsx</t>
+        </is>
+      </c>
+      <c r="B61" s="134"/>
+      <c r="C61" s="134"/>
+      <c r="D61" s="134"/>
+      <c r="E61" s="134"/>
+      <c r="F61" s="134"/>
+      <c r="G61" s="134"/>
+      <c r="H61" s="134"/>
+      <c r="I61" s="134"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="28">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:I1"/>
-    <mergeCell ref="A2:F5"/>
+    <mergeCell ref="A2:F6"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A37:I37"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="B41:I41"/>
     <mergeCell ref="B42:I42"/>
-    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A61:I61"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A7" location="'EXECUTIVE'!A1" display="EXECUTIVE"/>
-    <hyperlink ref="D7" location="'INSIGHTS'!A1" display="INSIGHTS"/>
+    <hyperlink ref="A8" location="'EXECUTIVE'!A1" display="EXECUTIVE"/>
+    <hyperlink ref="D8" location="'INSIGHTS'!A1" display="INSIGHTS"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.45" bottom="0.5" header="0.2" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8&amp;K003DA5ECOBANK SÉNÉGAL · CREDIT RISK INTELLIGENCE&amp;R&amp;8&amp;K64748BArrêté 30/09/2026</oddHeader>
     <oddFooter>&amp;L&amp;8&amp;K64748BAUDIT · INTERNAL USE ONLY&amp;R&amp;8&amp;K64748BPage &amp;P / &amp;N</oddFooter>

--- a/exemples_risk_intelligence/ECOBANK_Executive_Report_2026-09-30.xlsx
+++ b/exemples_risk_intelligence/ECOBANK_Executive_Report_2026-09-30.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[&gt;=1000000000]#,##0.00,,,&quot; Md&quot;;[&gt;=1000000]#,##0.0,,&quot; M&quot;;#,##0"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="46">
     <font>
       <sz val="10"/>
       <color rgb="FF0F172A"/>
@@ -65,6 +65,7 @@
     </font>
     <font>
       <b/>
+      <shadow/>
       <sz val="22"/>
       <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
@@ -85,6 +86,7 @@
     </font>
     <font>
       <b/>
+      <shadow/>
       <sz val="22"/>
       <color rgb="FF001B4D"/>
       <name val="Segoe UI"/>
@@ -182,6 +184,7 @@
     </font>
     <font>
       <b/>
+      <shadow/>
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
@@ -228,14 +231,14 @@
     <font>
       <b/>
       <sz val="13"/>
-      <color rgb="FFC8A951"/>
+      <color rgb="FFF59E0B"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
-      <color rgb="FFF97316"/>
+      <color rgb="FF16A34A"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -248,29 +251,8 @@
     </font>
     <font>
       <b/>
-      <sz val="9.5"/>
-      <color rgb="FF334155"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color rgb="FFDC2626"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF001B4D"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFF97316"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -291,7 +273,21 @@
     <font>
       <b/>
       <sz val="18"/>
+      <color rgb="FFF97316"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color rgb="FF2563EB"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF001B4D"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -342,7 +338,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="29">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -402,10 +398,14 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFF2F7FF"/>
+        </stop>
+      </gradientFill>
     </fill>
     <fill>
       <gradientFill degree="45">
@@ -438,6 +438,12 @@
       </gradientFill>
     </fill>
     <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
       <gradientFill degree="90">
         <stop position="0">
           <color rgb="FFFFFFFF"/>
@@ -464,6 +470,16 @@
         </stop>
         <stop position="1">
           <color rgb="FFFFFFFF"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color rgb="FFE24D4D"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFDC2626"/>
         </stop>
       </gradientFill>
     </fill>
@@ -510,26 +526,6 @@
     <fill>
       <gradientFill degree="0">
         <stop position="0">
-          <color rgb="FFC8A951"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFE6D8B1"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill degree="0">
-        <stop position="0">
-          <color rgb="FFF97316"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFFCC096"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill degree="0">
-        <stop position="0">
           <color rgb="FFF59E0B"/>
         </stop>
         <stop position="1">
@@ -550,10 +546,30 @@
     <fill>
       <gradientFill degree="0">
         <stop position="0">
+          <color rgb="FFF97316"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFFCC096"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="0">
+        <stop position="0">
           <color rgb="FF2563EB"/>
         </stop>
         <stop position="1">
           <color rgb="FF9DB9F6"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="0">
+        <stop position="0">
+          <color rgb="FFC8A951"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFE6D8B1"/>
         </stop>
       </gradientFill>
     </fill>
@@ -580,7 +596,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="49">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -618,10 +634,10 @@
         <color rgb="FFDBE6F7"/>
       </right>
       <top style="thin">
-        <color rgb="FFDBE6F7"/>
+        <color rgb="FFFFFFFF"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFDBE6F7"/>
+      <bottom style="medium">
+        <color rgb="FFBCCBE3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,10 +649,10 @@
         <color rgb="FFDBE6F7"/>
       </right>
       <top style="thin">
-        <color rgb="FFDBE6F7"/>
+        <color rgb="FFFFFFFF"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFDBE6F7"/>
+      <bottom style="medium">
+        <color rgb="FFBCCBE3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -682,11 +698,11 @@
       <left style="thick">
         <color rgb="FF06B6D4"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
-      <top style="thin">
-        <color rgb="FFDBE6F7"/>
+      <top style="medium">
+        <color rgb="FFBCCBE3"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -695,8 +711,8 @@
       <left style="thick">
         <color rgb="FF06B6D4"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
       <top/>
       <bottom/>
@@ -704,8 +720,8 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
       <top/>
       <bottom/>
@@ -715,12 +731,12 @@
       <left style="thick">
         <color rgb="FF06B6D4"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FFDBE6F7"/>
+      <bottom style="medium">
+        <color rgb="FFBCCBE3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -728,11 +744,11 @@
       <left style="thick">
         <color rgb="FFF59E0B"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
-      <top style="thin">
-        <color rgb="FFDBE6F7"/>
+      <top style="medium">
+        <color rgb="FFBCCBE3"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -741,8 +757,8 @@
       <left style="thick">
         <color rgb="FFF59E0B"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
       <top/>
       <bottom/>
@@ -752,12 +768,12 @@
       <left style="thick">
         <color rgb="FFF59E0B"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FFDBE6F7"/>
+      <bottom style="medium">
+        <color rgb="FFBCCBE3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -765,11 +781,11 @@
       <left style="thick">
         <color rgb="FFF97316"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
-      <top style="thin">
-        <color rgb="FFDBE6F7"/>
+      <top style="medium">
+        <color rgb="FFBCCBE3"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -778,8 +794,8 @@
       <left style="thick">
         <color rgb="FFF97316"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
       <top/>
       <bottom/>
@@ -789,12 +805,12 @@
       <left style="thick">
         <color rgb="FFF97316"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FFDBE6F7"/>
+      <bottom style="medium">
+        <color rgb="FFBCCBE3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -802,11 +818,11 @@
       <left style="thick">
         <color rgb="FFDC2626"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
-      <top style="thin">
-        <color rgb="FFDBE6F7"/>
+      <top style="medium">
+        <color rgb="FFBCCBE3"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -815,8 +831,8 @@
       <left style="thick">
         <color rgb="FFDC2626"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
       <top/>
       <bottom/>
@@ -826,12 +842,12 @@
       <left style="thick">
         <color rgb="FFDC2626"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FFDBE6F7"/>
+      <bottom style="medium">
+        <color rgb="FFBCCBE3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -839,11 +855,11 @@
       <left style="thick">
         <color rgb="FFC8A951"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
-      <top style="thin">
-        <color rgb="FFDBE6F7"/>
+      <top style="medium">
+        <color rgb="FFBCCBE3"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -852,8 +868,8 @@
       <left style="thick">
         <color rgb="FFC8A951"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
       <top/>
       <bottom/>
@@ -863,12 +879,12 @@
       <left style="thick">
         <color rgb="FFC8A951"/>
       </left>
-      <right style="thin">
-        <color rgb="FFDBE6F7"/>
+      <right style="medium">
+        <color rgb="FFBCCBE3"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FFDBE6F7"/>
+      <bottom style="medium">
+        <color rgb="FFBCCBE3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1006,6 +1022,17 @@
       <left/>
       <right/>
       <top style="thin">
+        <color rgb="FFEE9393"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF991B1B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color rgb="FFE2E8F0"/>
       </top>
       <bottom/>
@@ -1024,7 +1051,7 @@
       <left/>
       <right/>
       <top style="thick">
-        <color rgb="FFC8A951"/>
+        <color rgb="FFF59E0B"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -1033,7 +1060,7 @@
       <left/>
       <right/>
       <top style="thick">
-        <color rgb="FFF97316"/>
+        <color rgb="FF16A34A"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -1043,6 +1070,15 @@
         <color rgb="FFDBE6F7"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDBE6F7"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1183,120 +1219,120 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
@@ -1312,28 +1348,28 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1372,16 +1408,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1390,25 +1426,25 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="26" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="26" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1417,109 +1453,109 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="8" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="12" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="27" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="29" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1577,6 +1613,20 @@
               </a:solidFill>
               <a:round/>
             </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                <a:srgbClr val="001B4D">
+                  <a:alpha val="38000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:scene3d>
+              <a:camera prst="orthographicFront"/>
+              <a:lightRig rig="threePt" dir="t"/>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="38100" h="25400"/>
+            </a:sp3d>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -1677,6 +1727,13 @@
               </a:solidFill>
               <a:round/>
             </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="38100" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                <a:srgbClr val="001B4D">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -1691,6 +1748,20 @@
                 </a:solidFill>
                 <a:round/>
               </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                  <a:srgbClr val="001B4D">
+                    <a:alpha val="38000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="38100" h="25400"/>
+              </a:sp3d>
             </c:spPr>
           </c:marker>
           <c:cat>
@@ -1787,6 +1858,13 @@
               </a:solidFill>
               <a:round/>
             </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="38100" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                <a:srgbClr val="001B4D">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -1801,6 +1879,20 @@
                 </a:solidFill>
                 <a:round/>
               </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                  <a:srgbClr val="001B4D">
+                    <a:alpha val="38000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="38100" h="25400"/>
+              </a:sp3d>
             </c:spPr>
           </c:marker>
           <c:cat>
@@ -1897,6 +1989,13 @@
               </a:solidFill>
               <a:round/>
             </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="38100" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                <a:srgbClr val="001B4D">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -1911,6 +2010,20 @@
                 </a:solidFill>
                 <a:round/>
               </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                  <a:srgbClr val="001B4D">
+                    <a:alpha val="38000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="38100" h="25400"/>
+              </a:sp3d>
             </c:spPr>
           </c:marker>
           <c:cat>
@@ -2240,6 +2353,20 @@
                 </a:solidFill>
                 <a:round/>
               </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                  <a:srgbClr val="001B4D">
+                    <a:alpha val="38000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="38100" h="25400"/>
+              </a:sp3d>
             </c:spPr>
           </c:dPt>
           <c:dPt>
@@ -2255,6 +2382,20 @@
                 </a:solidFill>
                 <a:round/>
               </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                  <a:srgbClr val="001B4D">
+                    <a:alpha val="38000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="38100" h="25400"/>
+              </a:sp3d>
             </c:spPr>
           </c:dPt>
           <c:dPt>
@@ -2270,6 +2411,20 @@
                 </a:solidFill>
                 <a:round/>
               </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                  <a:srgbClr val="001B4D">
+                    <a:alpha val="38000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="38100" h="25400"/>
+              </a:sp3d>
             </c:spPr>
           </c:dPt>
           <c:dLbls>
@@ -2398,9 +2553,14 @@
   <c:roundedCorners val="0"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
+    <c:view3D>
+      <c:rotX val="12"/>
+      <c:rotY val="16"/>
+      <c:rAngAx val="1"/>
+    </c:view3D>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
+      <c:bar3DChart>
         <c:barDir val="col"/>
         <c:grouping val="stacked"/>
         <c:varyColors val="0"/>
@@ -2510,6 +2670,20 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                  <a:srgbClr val="001B4D">
+                    <a:alpha val="38000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="38100" h="25400"/>
+              </a:sp3d>
             </c:spPr>
           </c:dPt>
           <c:dPt>
@@ -2535,6 +2709,20 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                  <a:srgbClr val="001B4D">
+                    <a:alpha val="38000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="38100" h="25400"/>
+              </a:sp3d>
             </c:spPr>
           </c:dPt>
           <c:dPt>
@@ -2560,6 +2748,20 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                  <a:srgbClr val="001B4D">
+                    <a:alpha val="38000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="38100" h="25400"/>
+              </a:sp3d>
             </c:spPr>
           </c:dPt>
           <c:dPt>
@@ -2585,6 +2787,20 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="25400" dir="5400000" algn="t" rotWithShape="0">
+                  <a:srgbClr val="001B4D">
+                    <a:alpha val="38000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="38100" h="25400"/>
+              </a:sp3d>
             </c:spPr>
           </c:dPt>
           <c:dLbls>
@@ -2616,7 +2832,6 @@
                   <a:noFill/>
                 </a:ln>
               </c:spPr>
-              <c:dLblPos val="inEnd"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -2652,7 +2867,6 @@
                   <a:noFill/>
                 </a:ln>
               </c:spPr>
-              <c:dLblPos val="inEnd"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -2688,7 +2902,6 @@
                   <a:noFill/>
                 </a:ln>
               </c:spPr>
-              <c:dLblPos val="inEnd"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -2724,7 +2937,6 @@
                   <a:noFill/>
                 </a:ln>
               </c:spPr>
-              <c:dLblPos val="inEnd"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -2754,7 +2966,6 @@
                 <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="inEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -2805,10 +3016,11 @@
           </c:val>
         </c:ser>
         <c:gapWidth val="40"/>
-        <c:overlap val="100"/>
+        <c:gapDepth val="90"/>
+        <c:shape val="box"/>
         <c:axId val="201"/>
         <c:axId val="202"/>
-      </c:barChart>
+      </c:bar3DChart>
       <c:catAx>
         <c:axId val="201"/>
         <c:scaling>
@@ -3021,6 +3233,133 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Visuel 3D ECOBANK" descr="Skyline de données en verre bleu et anneau or (rendu Blender)"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rIdI1"/>
+        <a:srcRect t="500" b="500"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Visuel 3D ECOBANK" descr="Skyline de données en verre bleu et anneau or (rendu Blender)"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rIdI1"/>
+        <a:srcRect l="1136" r="1136"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Visuel 3D ECOBANK" descr="Skyline de données en verre bleu et anneau or (rendu Blender)"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rIdI1"/>
+        <a:srcRect l="29545" r="29545"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3174,6 +3513,25 @@
             </rPr>
             <t xml:space="preserve">Portfolio Monitoring &amp; Early Warning  ·  Vue Comité des Risques</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+30 SEPTEMBER 2026   ·   PORTFOLIO MONITORING</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFBFD3FF"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t xml:space="preserve">
+Portefeuille Ecobank Sénégal · 700 clients · 2 500 lignes ACTE 7</t>
+          </r>
         </is>
       </c>
       <c r="B2" s="3"/>
@@ -3486,7 +3844,7 @@
               <color rgb="FF64748B"/>
               <sz val="7"/>
             </rPr>
-            <t xml:space="preserve">JEV · PD 12M  </t>
+            <t xml:space="preserve">OUTLOOK · PD 12M  </t>
           </r>
           <r>
             <rPr>
@@ -3521,7 +3879,7 @@
               <color rgb="FF64748B"/>
               <sz val="7"/>
             </rPr>
-            <t xml:space="preserve">TYPESAFE  </t>
+            <t xml:space="preserve">SÉMANTIQUE  </t>
           </r>
           <r>
             <rPr>
@@ -3530,7 +3888,7 @@
               <color rgb="FF001B4D"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">24 retours · 8 en revue</t>
+            <t xml:space="preserve">30 lus · 16 en revue</t>
           </r>
         </is>
       </c>
@@ -4526,7 +4884,7 @@
               <color rgb="FF334155"/>
               <sz val="8"/>
             </rPr>
-            <t xml:space="preserve">JEV OUTLOOK</t>
+            <t xml:space="preserve">RISK OUTLOOK</t>
           </r>
         </is>
       </c>
@@ -5222,7 +5580,7 @@
       <c r="B70" s="80"/>
       <c r="C70" s="83" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV PD 12M 15,4 % (HYBRID)  ·  Contrepartie déjà douteuse : mise en demeure et proposition d'un protocole d'apurement daté avant le 15/10/2026 ; rechercher des actifs sais</t>
+          <t xml:space="preserve">RISK OUTLOOK PD 12M 13,7 % (MARKOV)  ·  Contrepartie déjà douteuse : mise en demeure et proposition d'un protocole d'apurement daté avant le 15/10/2026 ; rechercher des actifs sais</t>
         </is>
       </c>
       <c r="D70" s="83"/>
@@ -5388,7 +5746,7 @@
       <c r="B74" s="80"/>
       <c r="C74" s="83" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV PD 12M 100,0 % (OBSERVED)  ·  Surveillance renforcée</t>
+          <t xml:space="preserve">RISK OUTLOOK PD 12M 100,0 % (OBSERVED)  ·  Surveillance renforcée</t>
         </is>
       </c>
       <c r="D74" s="83"/>
@@ -5399,7 +5757,7 @@
       <c r="I74" s="83"/>
       <c r="J74" s="83"/>
       <c r="S74" s="92">
-        <v>0.15</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="T74" s="91"/>
       <c r="U74" s="91"/>
@@ -5554,7 +5912,7 @@
       <c r="B78" s="80"/>
       <c r="C78" s="83" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV PD 12M 100,0 % (OBSERVED)  ·  Surveillance renforcée</t>
+          <t xml:space="preserve">RISK OUTLOOK PD 12M 100,0 % (OBSERVED)  ·  Surveillance renforcée</t>
         </is>
       </c>
       <c r="D78" s="83"/>
@@ -5720,7 +6078,7 @@
       <c r="B82" s="80"/>
       <c r="C82" s="83" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV PD 12M 100,0 % (OBSERVED)  ·  Surveillance renforcée</t>
+          <t xml:space="preserve">RISK OUTLOOK PD 12M 100,0 % (OBSERVED)  ·  Surveillance renforcée</t>
         </is>
       </c>
       <c r="D82" s="83"/>
@@ -5837,6 +6195,15 @@
             </rPr>
             <t xml:space="preserve">IMPAYÉS EN HAUSSE</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="7"/>
+            </rPr>
+            <t xml:space="preserve">  ◆ LECTURE DU COMITÉ</t>
+          </r>
         </is>
       </c>
       <c r="B87" s="97"/>
@@ -5853,7 +6220,7 @@
               <color rgb="FFC8A951"/>
               <sz val="12"/>
             </rPr>
-            <t xml:space="preserve">02  </t>
+            <t xml:space="preserve">05  </t>
           </r>
           <r>
             <rPr>
@@ -5862,7 +6229,7 @@
               <color rgb="FF334155"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">CONCENTRATION</t>
+            <t xml:space="preserve">STAGE 2 &amp; 3</t>
           </r>
         </is>
       </c>
@@ -5871,7 +6238,7 @@
       <c r="J87" s="100"/>
       <c r="K87" s="100"/>
       <c r="L87" s="100"/>
-      <c r="M87" s="102" t="inlineStr">
+      <c r="M87" s="97" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5880,7 +6247,7 @@
               <color rgb="FFC8A951"/>
               <sz val="12"/>
             </rPr>
-            <t xml:space="preserve">03  </t>
+            <t xml:space="preserve">04  </t>
           </r>
           <r>
             <rPr>
@@ -5889,16 +6256,16 @@
               <color rgb="FF334155"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">MIGRATION</t>
-          </r>
-        </is>
-      </c>
-      <c r="N87" s="102"/>
-      <c r="O87" s="102"/>
-      <c r="P87" s="102"/>
-      <c r="Q87" s="102"/>
-      <c r="R87" s="102"/>
-      <c r="S87" s="97" t="inlineStr">
+            <t xml:space="preserve">ACTION</t>
+          </r>
+        </is>
+      </c>
+      <c r="N87" s="97"/>
+      <c r="O87" s="97"/>
+      <c r="P87" s="97"/>
+      <c r="Q87" s="97"/>
+      <c r="R87" s="97"/>
+      <c r="S87" s="102" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5907,7 +6274,7 @@
               <color rgb="FFC8A951"/>
               <sz val="12"/>
             </rPr>
-            <t xml:space="preserve">04  </t>
+            <t xml:space="preserve">06  </t>
           </r>
           <r>
             <rPr>
@@ -5916,15 +6283,15 @@
               <color rgb="FF334155"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">ACTION</t>
-          </r>
-        </is>
-      </c>
-      <c r="T87" s="97"/>
-      <c r="U87" s="97"/>
-      <c r="V87" s="97"/>
-      <c r="W87" s="97"/>
-      <c r="X87" s="97"/>
+            <t xml:space="preserve">RÉGULARISATIONS</t>
+          </r>
+        </is>
+      </c>
+      <c r="T87" s="102"/>
+      <c r="U87" s="102"/>
+      <c r="V87" s="102"/>
+      <c r="W87" s="102"/>
+      <c r="X87" s="102"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="98" t="inlineStr">
@@ -5939,7 +6306,7 @@
       <c r="F88" s="98"/>
       <c r="G88" s="101" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOP 10 = 8,3 %</t>
+          <t xml:space="preserve">583,23 Md XOF</t>
         </is>
       </c>
       <c r="H88" s="101"/>
@@ -5947,26 +6314,26 @@
       <c r="J88" s="101"/>
       <c r="K88" s="101"/>
       <c r="L88" s="101"/>
-      <c r="M88" s="103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 dossiers</t>
-        </is>
-      </c>
-      <c r="N88" s="103"/>
-      <c r="O88" s="103"/>
-      <c r="P88" s="103"/>
-      <c r="Q88" s="103"/>
-      <c r="R88" s="103"/>
-      <c r="S88" s="98" t="inlineStr">
+      <c r="M88" s="98" t="inlineStr">
         <is>
           <t xml:space="preserve">54 dossiers</t>
         </is>
       </c>
-      <c r="T88" s="98"/>
-      <c r="U88" s="98"/>
-      <c r="V88" s="98"/>
-      <c r="W88" s="98"/>
-      <c r="X88" s="98"/>
+      <c r="N88" s="98"/>
+      <c r="O88" s="98"/>
+      <c r="P88" s="98"/>
+      <c r="Q88" s="98"/>
+      <c r="R88" s="98"/>
+      <c r="S88" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 dossiers</t>
+        </is>
+      </c>
+      <c r="T88" s="103"/>
+      <c r="U88" s="103"/>
+      <c r="V88" s="103"/>
+      <c r="W88" s="103"/>
+      <c r="X88" s="103"/>
     </row>
     <row r="89" ht="46" customHeight="1">
       <c r="A89" s="99" t="inlineStr">
@@ -5981,7 +6348,7 @@
       <c r="F89" s="99"/>
       <c r="G89" s="99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les 10 premiers clients portent 70,74 Md XOF sur 850,39 Md. Premier client : SOCIETE 0378 (1,0 %). Premier segment : X (100 %).</t>
+          <t xml:space="preserve">Stage 2 : 259,46 Md (30,5 % de l'encours) ; −947,9 M sur le mois. Stage 3 : 323,78 Md (38,1 %) ; +3,49 Md. Provisions : 37,32 Md XOF.</t>
         </is>
       </c>
       <c r="H89" s="99"/>
@@ -5991,7 +6358,7 @@
       <c r="L89" s="99"/>
       <c r="M89" s="99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 clients ont migré vers une tranche d'impayé plus dégradée (1,3 % des clients suivis), dont 6 au-delà de 90 jours ou en Stage 3 pour 3,49 Md XOF d'encours.</t>
+          <t xml:space="preserve">6 dossiers critiques (3,49 Md XOF) et 48 en priorité haute nécessitent une intervention. Premier dossier : SOCIETE 0450 (3,03 Md, 304 j).</t>
         </is>
       </c>
       <c r="N89" s="99"/>
@@ -6001,7 +6368,7 @@
       <c r="R89" s="99"/>
       <c r="S89" s="99" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 dossiers critiques (3,49 Md XOF) et 48 en priorité haute nécessitent une intervention. Premier dossier : SOCIETE 0450 (3,03 Md, 304 j).</t>
+          <t xml:space="preserve">0 clients en impayé au 31/08/2026 sont revenus à jour, soit 0 XOF d'impayés résorbés.</t>
         </is>
       </c>
       <c r="T89" s="99"/>
@@ -6444,7 +6811,7 @@
     <tabColor rgb="FFC8A951"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.4" customWidth="1"/>
@@ -6588,6 +6955,25 @@
             </rPr>
             <t xml:space="preserve">Lecture éditoriale de l'arrêté · chaque chiffre est calculé sur les données</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+30 SEPTEMBER 2026   ·   PORTFOLIO MONITORING</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFBFD3FF"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t xml:space="preserve">
+Portefeuille Ecobank Sénégal · 700 clients · 2 500 lignes ACTE 7</t>
+          </r>
         </is>
       </c>
       <c r="B2" s="3"/>
@@ -6900,7 +7286,7 @@
               <color rgb="FF64748B"/>
               <sz val="7"/>
             </rPr>
-            <t xml:space="preserve">JEV · PD 12M  </t>
+            <t xml:space="preserve">OUTLOOK · PD 12M  </t>
           </r>
           <r>
             <rPr>
@@ -6935,7 +7321,7 @@
               <color rgb="FF64748B"/>
               <sz val="7"/>
             </rPr>
-            <t xml:space="preserve">TYPESAFE  </t>
+            <t xml:space="preserve">SÉMANTIQUE  </t>
           </r>
           <r>
             <rPr>
@@ -6944,7 +7330,7 @@
               <color rgb="FF001B4D"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">24 retours · 8 en revue</t>
+            <t xml:space="preserve">30 lus · 16 en revue</t>
           </r>
         </is>
       </c>
@@ -7024,7 +7410,24 @@
       <c r="C13" s="105"/>
       <c r="D13" s="106" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMPAYÉS EN HAUSSE</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">IMPAYÉS EN HAUSSE</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">   ◆ LECTURE DU COMITÉ</t>
+          </r>
         </is>
       </c>
       <c r="E13" s="106"/>
@@ -7037,14 +7440,22 @@
       <c r="L13" s="20"/>
       <c r="M13" s="105" t="inlineStr">
         <is>
-          <t xml:space="preserve">02</t>
+          <t xml:space="preserve">05</t>
         </is>
       </c>
       <c r="N13" s="105"/>
       <c r="O13" s="105"/>
       <c r="P13" s="106" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONCENTRATION</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">STAGE 2 &amp; 3</t>
+          </r>
         </is>
       </c>
       <c r="Q13" s="106"/>
@@ -7078,7 +7489,7 @@
       <c r="O14" s="105"/>
       <c r="P14" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOP 10 = 8,3 %</t>
+          <t xml:space="preserve">583,23 Md XOF</t>
         </is>
       </c>
       <c r="Q14" s="114"/>
@@ -7112,7 +7523,7 @@
       <c r="O15" s="108"/>
       <c r="P15" s="109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les 10 premiers clients portent 70,74 Md XOF sur 850,39 Md. Premier client : SOCIETE 0378 (1,0 %). Premier segment : X (100 %).</t>
+          <t xml:space="preserve">Stage 2 : 259,46 Md (30,5 % de l'encours) ; −947,9 M sur le mois. Stage 3 : 323,78 Md (38,1 %) ; +3,49 Md. Provisions : 37,32 Md XOF.</t>
         </is>
       </c>
       <c r="Q15" s="109"/>
@@ -7175,40 +7586,48 @@
       <c r="X17" s="20"/>
     </row>
     <row r="19" ht="8" customHeight="1">
-      <c r="A19" s="115"/>
-      <c r="B19" s="115"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="115"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="115"/>
-      <c r="M19" s="104"/>
-      <c r="N19" s="104"/>
-      <c r="O19" s="104"/>
-      <c r="P19" s="104"/>
-      <c r="Q19" s="104"/>
-      <c r="R19" s="104"/>
-      <c r="S19" s="104"/>
-      <c r="T19" s="104"/>
-      <c r="U19" s="104"/>
-      <c r="V19" s="104"/>
-      <c r="W19" s="104"/>
+      <c r="A19" s="104"/>
+      <c r="B19" s="104"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="104"/>
+      <c r="M19" s="115"/>
+      <c r="N19" s="115"/>
+      <c r="O19" s="115"/>
+      <c r="P19" s="115"/>
+      <c r="Q19" s="115"/>
+      <c r="R19" s="115"/>
+      <c r="S19" s="115"/>
+      <c r="T19" s="115"/>
+      <c r="U19" s="115"/>
+      <c r="V19" s="115"/>
+      <c r="W19" s="115"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="105" t="inlineStr">
         <is>
-          <t xml:space="preserve">03</t>
+          <t xml:space="preserve">04</t>
         </is>
       </c>
       <c r="B20" s="105"/>
       <c r="C20" s="105"/>
       <c r="D20" s="106" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">ACTION</t>
+          </r>
         </is>
       </c>
       <c r="E20" s="106"/>
@@ -7221,14 +7640,22 @@
       <c r="L20" s="20"/>
       <c r="M20" s="105" t="inlineStr">
         <is>
-          <t xml:space="preserve">04</t>
+          <t xml:space="preserve">06</t>
         </is>
       </c>
       <c r="N20" s="105"/>
       <c r="O20" s="105"/>
       <c r="P20" s="106" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACTION</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">RÉGULARISATIONS</t>
+          </r>
         </is>
       </c>
       <c r="Q20" s="106"/>
@@ -7244,34 +7671,34 @@
       <c r="A21" s="105"/>
       <c r="B21" s="105"/>
       <c r="C21" s="105"/>
-      <c r="D21" s="116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 dossiers</t>
-        </is>
-      </c>
-      <c r="E21" s="116"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="116"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="116"/>
+      <c r="D21" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54 dossiers</t>
+        </is>
+      </c>
+      <c r="E21" s="107"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="107"/>
+      <c r="I21" s="107"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="107"/>
       <c r="L21" s="20"/>
       <c r="M21" s="105"/>
       <c r="N21" s="105"/>
       <c r="O21" s="105"/>
-      <c r="P21" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54 dossiers</t>
-        </is>
-      </c>
-      <c r="Q21" s="107"/>
-      <c r="R21" s="107"/>
-      <c r="S21" s="107"/>
-      <c r="T21" s="107"/>
-      <c r="U21" s="107"/>
-      <c r="V21" s="107"/>
-      <c r="W21" s="107"/>
+      <c r="P21" s="116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 dossiers</t>
+        </is>
+      </c>
+      <c r="Q21" s="116"/>
+      <c r="R21" s="116"/>
+      <c r="S21" s="116"/>
+      <c r="T21" s="116"/>
+      <c r="U21" s="116"/>
+      <c r="V21" s="116"/>
+      <c r="W21" s="116"/>
       <c r="X21" s="20"/>
     </row>
     <row r="22" ht="44" customHeight="1">
@@ -7280,7 +7707,7 @@
       <c r="C22" s="108"/>
       <c r="D22" s="109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 clients ont migré vers une tranche d'impayé plus dégradée (1,3 % des clients suivis), dont 6 au-delà de 90 jours ou en Stage 3 pour 3,49 Md XOF d'encours.</t>
+          <t xml:space="preserve">6 dossiers critiques (3,49 Md XOF) et 48 en priorité haute nécessitent une intervention. Premier dossier : SOCIETE 0450 (3,03 Md, 304 j).</t>
         </is>
       </c>
       <c r="E22" s="109"/>
@@ -7296,7 +7723,7 @@
       <c r="O22" s="108"/>
       <c r="P22" s="109" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 dossiers critiques (3,49 Md XOF) et 48 en priorité haute nécessitent une intervention. Premier dossier : SOCIETE 0450 (3,03 Md, 304 j).</t>
+          <t xml:space="preserve">0 clients en impayé au 31/08/2026 sont revenus à jour, soit 0 XOF d'impayés résorbés.</t>
         </is>
       </c>
       <c r="Q22" s="109"/>
@@ -7385,14 +7812,22 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="105" t="inlineStr">
         <is>
-          <t xml:space="preserve">05</t>
+          <t xml:space="preserve">03</t>
         </is>
       </c>
       <c r="B27" s="105"/>
       <c r="C27" s="105"/>
       <c r="D27" s="106" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAGE 2 &amp; 3</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">MIGRATION</t>
+          </r>
         </is>
       </c>
       <c r="E27" s="106"/>
@@ -7405,14 +7840,22 @@
       <c r="L27" s="20"/>
       <c r="M27" s="105" t="inlineStr">
         <is>
-          <t xml:space="preserve">06</t>
+          <t xml:space="preserve">07</t>
         </is>
       </c>
       <c r="N27" s="105"/>
       <c r="O27" s="105"/>
       <c r="P27" s="106" t="inlineStr">
         <is>
-          <t xml:space="preserve">RÉGULARISATIONS</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">PROSPECTIF · RISK OUTLOOK</t>
+          </r>
         </is>
       </c>
       <c r="Q27" s="106"/>
@@ -7430,7 +7873,7 @@
       <c r="C28" s="105"/>
       <c r="D28" s="118" t="inlineStr">
         <is>
-          <t xml:space="preserve">583,23 Md XOF</t>
+          <t xml:space="preserve">9 dossiers</t>
         </is>
       </c>
       <c r="E28" s="118"/>
@@ -7446,7 +7889,7 @@
       <c r="O28" s="105"/>
       <c r="P28" s="120" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 dossiers</t>
+          <t xml:space="preserve">PD 12M = 3,8 %</t>
         </is>
       </c>
       <c r="Q28" s="120"/>
@@ -7464,7 +7907,7 @@
       <c r="C29" s="108"/>
       <c r="D29" s="109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage 2 : 259,46 Md (30,5 % de l'encours) ; −947,9 M sur le mois. Stage 3 : 323,78 Md (38,1 %) ; +3,49 Md. Provisions : 37,32 Md XOF.</t>
+          <t xml:space="preserve">9 clients ont migré vers une tranche d'impayé plus dégradée (1,3 % des clients suivis), dont 6 au-delà de 90 jours ou en Stage 3 pour 3,49 Md XOF d'encours.</t>
         </is>
       </c>
       <c r="E29" s="109"/>
@@ -7480,7 +7923,7 @@
       <c r="O29" s="108"/>
       <c r="P29" s="109" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 clients en impayé au 31/08/2026 sont revenus à jour, soit 0 XOF d'impayés résorbés.</t>
+          <t xml:space="preserve">Probabilité qu'un client sain aujourd'hui devienne douteux sous 12 mois (MARKOV, N = 17 850, 9 mois, confiance faible). Scénario sévère : 66,36 Md XOF d'entrées en douteux attendues (SIMULATED). Estimation indicative : historique insuffisant pour une calibration robuste.</t>
         </is>
       </c>
       <c r="Q29" s="109"/>
@@ -7569,14 +8012,22 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="105" t="inlineStr">
         <is>
-          <t xml:space="preserve">07</t>
+          <t xml:space="preserve">02</t>
         </is>
       </c>
       <c r="B34" s="105"/>
       <c r="C34" s="105"/>
       <c r="D34" s="106" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROSPECTIF · JEV</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">CONCENTRATION</t>
+          </r>
         </is>
       </c>
       <c r="E34" s="106"/>
@@ -7589,14 +8040,22 @@
       <c r="L34" s="20"/>
       <c r="M34" s="105" t="inlineStr">
         <is>
-          <t xml:space="preserve">08</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="N34" s="105"/>
       <c r="O34" s="105"/>
       <c r="P34" s="106" t="inlineStr">
         <is>
-          <t xml:space="preserve">TYPESAFE · RETOURS</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">ANALYSES AVANCÉES</t>
+          </r>
         </is>
       </c>
       <c r="Q34" s="106"/>
@@ -7614,7 +8073,7 @@
       <c r="C35" s="105"/>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t xml:space="preserve">PD 12M = 3,8 %</t>
+          <t xml:space="preserve">TOP 10 = 8,3 %</t>
         </is>
       </c>
       <c r="E35" s="122"/>
@@ -7630,7 +8089,7 @@
       <c r="O35" s="105"/>
       <c r="P35" s="124" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 commentaires lus</t>
+          <t xml:space="preserve">Guérison 31-60 j = 0,0 %</t>
         </is>
       </c>
       <c r="Q35" s="124"/>
@@ -7648,7 +8107,7 @@
       <c r="C36" s="108"/>
       <c r="D36" s="109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Probabilité qu'un client sain aujourd'hui devienne douteux sous 12 mois (MARKOV, N = 17 850, 9 mois, confiance faible). Scénario sévère : 66,36 Md XOF d'entrées en douteux attendues (SIMULATED). Estimation indicative : historique insuffisant pour une calibration robuste.</t>
+          <t xml:space="preserve">Les 10 premiers clients portent 70,74 Md XOF sur 850,39 Md. Premier client : BAOBAB NEGOCE SA (1,0 %). Premier segment : X (100 %).</t>
         </is>
       </c>
       <c r="E36" s="109"/>
@@ -7664,7 +8123,7 @@
       <c r="O36" s="108"/>
       <c r="P36" s="109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 dossiers en revue analyste (confiance faible ou incohérence), dont 0 par contrôle d'auto-cohérence ; 2 promesses tombent après la date de bascule. TypeSafe ne produit aucun chiffre.</t>
+          <t xml:space="preserve">Un client sain met en moyenne — mois avant le défaut (MARKOV). Probabilité de guérison : 0,0 % depuis 31-60 j, 0,0 % depuis 61-90 j. PD 12M : IC 90 % 3,1 % – 4,6 % (SIMULATED). Backtest : 8,2 entrées prévues contre 8 observées. Un facteur ×2,00 sur les dégradations double la PD (STRESS).</t>
         </is>
       </c>
       <c r="Q36" s="109"/>
@@ -7726,8 +8185,208 @@
       <c r="W38" s="21"/>
       <c r="X38" s="20"/>
     </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="75" t="inlineStr">
+    <row r="40" ht="8" customHeight="1">
+      <c r="A40" s="117"/>
+      <c r="B40" s="117"/>
+      <c r="C40" s="117"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="117"/>
+      <c r="G40" s="117"/>
+      <c r="H40" s="117"/>
+      <c r="I40" s="117"/>
+      <c r="J40" s="117"/>
+      <c r="K40" s="117"/>
+      <c r="M40" s="123"/>
+      <c r="N40" s="123"/>
+      <c r="O40" s="123"/>
+      <c r="P40" s="123"/>
+      <c r="Q40" s="123"/>
+      <c r="R40" s="123"/>
+      <c r="S40" s="123"/>
+      <c r="T40" s="123"/>
+      <c r="U40" s="123"/>
+      <c r="V40" s="123"/>
+      <c r="W40" s="123"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09</t>
+        </is>
+      </c>
+      <c r="B41" s="105"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="106" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">STRESS NARRATIF</t>
+          </r>
+        </is>
+      </c>
+      <c r="E41" s="106"/>
+      <c r="F41" s="106"/>
+      <c r="G41" s="106"/>
+      <c r="H41" s="106"/>
+      <c r="I41" s="106"/>
+      <c r="J41" s="106"/>
+      <c r="K41" s="106"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08</t>
+        </is>
+      </c>
+      <c r="N41" s="105"/>
+      <c r="O41" s="105"/>
+      <c r="P41" s="106" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FF334155"/>
+              <sz val="9.5"/>
+            </rPr>
+            <t xml:space="preserve">ANALYSE SÉMANTIQUE · RETOURS</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q41" s="106"/>
+      <c r="R41" s="106"/>
+      <c r="S41" s="106"/>
+      <c r="T41" s="106"/>
+      <c r="U41" s="106"/>
+      <c r="V41" s="106"/>
+      <c r="W41" s="106"/>
+      <c r="X41" s="20"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="105"/>
+      <c r="B42" s="105"/>
+      <c r="C42" s="105"/>
+      <c r="D42" s="118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 dossiers · Prix à l'importation</t>
+        </is>
+      </c>
+      <c r="E42" s="118"/>
+      <c r="F42" s="118"/>
+      <c r="G42" s="118"/>
+      <c r="H42" s="118"/>
+      <c r="I42" s="118"/>
+      <c r="J42" s="118"/>
+      <c r="K42" s="118"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="105"/>
+      <c r="N42" s="105"/>
+      <c r="O42" s="105"/>
+      <c r="P42" s="124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 commentaires lus</t>
+        </is>
+      </c>
+      <c r="Q42" s="124"/>
+      <c r="R42" s="124"/>
+      <c r="S42" s="124"/>
+      <c r="T42" s="124"/>
+      <c r="U42" s="124"/>
+      <c r="V42" s="124"/>
+      <c r="W42" s="124"/>
+      <c r="X42" s="20"/>
+    </row>
+    <row r="43" ht="44" customHeight="1">
+      <c r="A43" s="108"/>
+      <c r="B43" s="108"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 dossiers sont directement exposés au scénario « Prix à l'importation » pour 23,76 Md XOF d'encours (exposition jugée par l'analyse sémantique). Sous stress ×2 (EXPERT), les entrées en douteux attendues passent de 3,13 Md à 5,51 Md XOF (calcul Risk Outlook). Autres scénarios : Perte d'un donneur d'ordre (4), Paiements de l'État (3), Crise sanitaire (4).</t>
+        </is>
+      </c>
+      <c r="E43" s="109"/>
+      <c r="F43" s="109"/>
+      <c r="G43" s="109"/>
+      <c r="H43" s="109"/>
+      <c r="I43" s="109"/>
+      <c r="J43" s="109"/>
+      <c r="K43" s="109"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="108"/>
+      <c r="N43" s="108"/>
+      <c r="O43" s="108"/>
+      <c r="P43" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16 dossiers en revue analyste (confiance faible ou incohérence), dont 2 par contrôle d'auto-cohérence ; 2 promesses tombent après la date de bascule. Analyse sémantique ne produit aucun chiffre.</t>
+        </is>
+      </c>
+      <c r="Q43" s="109"/>
+      <c r="R43" s="109"/>
+      <c r="S43" s="109"/>
+      <c r="T43" s="109"/>
+      <c r="U43" s="109"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="109"/>
+      <c r="X43" s="20"/>
+    </row>
+    <row r="44" ht="8" customHeight="1">
+      <c r="A44" s="111"/>
+      <c r="B44" s="110"/>
+      <c r="C44" s="110"/>
+      <c r="D44" s="110"/>
+      <c r="E44" s="110"/>
+      <c r="F44" s="110"/>
+      <c r="G44" s="110"/>
+      <c r="H44" s="110"/>
+      <c r="I44" s="110"/>
+      <c r="J44" s="110"/>
+      <c r="K44" s="112"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="111"/>
+      <c r="N44" s="110"/>
+      <c r="O44" s="110"/>
+      <c r="P44" s="110"/>
+      <c r="Q44" s="110"/>
+      <c r="R44" s="110"/>
+      <c r="S44" s="110"/>
+      <c r="T44" s="110"/>
+      <c r="U44" s="110"/>
+      <c r="V44" s="110"/>
+      <c r="W44" s="112"/>
+      <c r="X44" s="20"/>
+    </row>
+    <row r="45" ht="8" customHeight="1">
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="20"/>
+      <c r="N45" s="21"/>
+      <c r="O45" s="21"/>
+      <c r="P45" s="21"/>
+      <c r="Q45" s="21"/>
+      <c r="R45" s="21"/>
+      <c r="S45" s="21"/>
+      <c r="T45" s="21"/>
+      <c r="U45" s="21"/>
+      <c r="V45" s="21"/>
+      <c r="W45" s="21"/>
+      <c r="X45" s="20"/>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="75" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7745,7 +8404,7 @@
               <color rgb="FF001B4D"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">TYPESAFE · RETOURS GESTIONNAIRES</t>
+            <t xml:space="preserve">ANALYSE SÉMANTIQUE · RETOURS GESTIONNAIRES</t>
           </r>
           <r>
             <rPr>
@@ -7754,66 +8413,66 @@
               <color rgb="FF64748B"/>
               <sz val="8"/>
             </rPr>
-            <t xml:space="preserve">    jugements jev-latest sur les commentaires (aucun chiffre produit par TypeSafe)</t>
-          </r>
-        </is>
-      </c>
-      <c r="B41" s="75"/>
-      <c r="C41" s="75"/>
-      <c r="D41" s="75"/>
-      <c r="E41" s="75"/>
-      <c r="F41" s="75"/>
-      <c r="G41" s="75"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="75"/>
-      <c r="J41" s="75"/>
-      <c r="K41" s="75"/>
-      <c r="L41" s="75"/>
-      <c r="M41" s="75"/>
-      <c r="N41" s="75"/>
-      <c r="O41" s="75"/>
-      <c r="P41" s="75"/>
-      <c r="Q41" s="75"/>
-      <c r="R41" s="75"/>
-      <c r="S41" s="75"/>
-      <c r="T41" s="75"/>
-      <c r="U41" s="75"/>
-      <c r="V41" s="75"/>
-      <c r="W41" s="75"/>
-      <c r="X41" s="75"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 retours lus · 8 en revue analyste · 2 promesses après la date de bascule · 3 sans commentaire</t>
-        </is>
-      </c>
-      <c r="B42" s="125"/>
-      <c r="C42" s="125"/>
-      <c r="D42" s="125"/>
-      <c r="E42" s="125"/>
-      <c r="F42" s="125"/>
-      <c r="G42" s="125"/>
-      <c r="H42" s="125"/>
-      <c r="I42" s="125"/>
-      <c r="J42" s="125"/>
-      <c r="K42" s="125"/>
-      <c r="L42" s="125"/>
-      <c r="M42" s="125"/>
-      <c r="N42" s="125"/>
-      <c r="O42" s="125"/>
-      <c r="P42" s="125"/>
-      <c r="Q42" s="125"/>
-      <c r="R42" s="125"/>
-      <c r="S42" s="125"/>
-      <c r="T42" s="125"/>
-      <c r="U42" s="125"/>
-      <c r="V42" s="125"/>
-      <c r="W42" s="125"/>
-      <c r="X42" s="125"/>
+            <t xml:space="preserve">    jugements moteur sémantique sur les commentaires (aucun chiffre produit par Analyse sémantique)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B48" s="75"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="75"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="75"/>
+      <c r="H48" s="75"/>
+      <c r="I48" s="75"/>
+      <c r="J48" s="75"/>
+      <c r="K48" s="75"/>
+      <c r="L48" s="75"/>
+      <c r="M48" s="75"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="75"/>
+      <c r="P48" s="75"/>
+      <c r="Q48" s="75"/>
+      <c r="R48" s="75"/>
+      <c r="S48" s="75"/>
+      <c r="T48" s="75"/>
+      <c r="U48" s="75"/>
+      <c r="V48" s="75"/>
+      <c r="W48" s="75"/>
+      <c r="X48" s="75"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 retours lus · 16 en revue analyste · 2 promesses après la date de bascule · 3 sans commentaire</t>
+        </is>
+      </c>
+      <c r="B49" s="125"/>
+      <c r="C49" s="125"/>
+      <c r="D49" s="125"/>
+      <c r="E49" s="125"/>
+      <c r="F49" s="125"/>
+      <c r="G49" s="125"/>
+      <c r="H49" s="125"/>
+      <c r="I49" s="125"/>
+      <c r="J49" s="125"/>
+      <c r="K49" s="125"/>
+      <c r="L49" s="125"/>
+      <c r="M49" s="125"/>
+      <c r="N49" s="125"/>
+      <c r="O49" s="125"/>
+      <c r="P49" s="125"/>
+      <c r="Q49" s="125"/>
+      <c r="R49" s="125"/>
+      <c r="S49" s="125"/>
+      <c r="T49" s="125"/>
+      <c r="U49" s="125"/>
+      <c r="V49" s="125"/>
+      <c r="W49" s="125"/>
+      <c r="X49" s="125"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="67">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="S1:X1"/>
     <mergeCell ref="A2:O6"/>
@@ -7869,8 +8528,18 @@
     <mergeCell ref="P35:W35"/>
     <mergeCell ref="M36:O36"/>
     <mergeCell ref="P36:W36"/>
-    <mergeCell ref="A41:X41"/>
-    <mergeCell ref="A42:X42"/>
+    <mergeCell ref="A41:C42"/>
+    <mergeCell ref="D41:K41"/>
+    <mergeCell ref="D42:K42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:K43"/>
+    <mergeCell ref="M41:O42"/>
+    <mergeCell ref="P41:W41"/>
+    <mergeCell ref="P42:W42"/>
+    <mergeCell ref="M43:O43"/>
+    <mergeCell ref="P43:W43"/>
+    <mergeCell ref="A48:X48"/>
+    <mergeCell ref="A49:X49"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A8" location="'EXECUTIVE'!A1" display="EXECUTIVE"/>
@@ -7886,6 +8555,7 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="25" max="16383" man="1"/>
   </rowBreaks>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7895,7 +8565,7 @@
     <tabColor rgb="FF001B4D"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -8008,6 +8678,25 @@
             </rPr>
             <t xml:space="preserve">Traçabilité, contrôles automatiques et provenance</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+30 SEPTEMBER 2026   ·   PORTFOLIO MONITORING</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFBFD3FF"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t xml:space="preserve">
+Portefeuille Ecobank Sénégal · 700 clients · 2 500 lignes ACTE 7</t>
+          </r>
         </is>
       </c>
       <c r="B2" s="3"/>
@@ -8112,9 +8801,7 @@
           </r>
         </is>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8135,9 +8822,9 @@
           </r>
         </is>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8158,6 +8845,8 @@
           </r>
         </is>
       </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
     </row>
@@ -8211,7 +8900,7 @@
               <color rgb="FF64748B"/>
               <sz val="7"/>
             </rPr>
-            <t xml:space="preserve">JEV · PD 12M  </t>
+            <t xml:space="preserve">OUTLOOK · PD 12M  </t>
           </r>
           <r>
             <rPr>
@@ -8243,7 +8932,7 @@
               <color rgb="FF64748B"/>
               <sz val="7"/>
             </rPr>
-            <t xml:space="preserve">TYPESAFE  </t>
+            <t xml:space="preserve">SÉMANTIQUE  </t>
           </r>
           <r>
             <rPr>
@@ -8252,7 +8941,7 @@
               <color rgb="FF001B4D"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">24 retours · 8 en revue</t>
+            <t xml:space="preserve">30 lus · 16 en revue</t>
           </r>
         </is>
       </c>
@@ -8361,7 +9050,7 @@
       </c>
       <c r="B14" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_01.xlsx</t>
+          <t xml:space="preserve">N_01.xlsx</t>
         </is>
       </c>
       <c r="C14" s="127" t="inlineStr">
@@ -8383,7 +9072,7 @@
       </c>
       <c r="B15" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_02.xlsx</t>
+          <t xml:space="preserve">N_02.xlsx</t>
         </is>
       </c>
       <c r="C15" s="128" t="inlineStr">
@@ -8405,7 +9094,7 @@
       </c>
       <c r="B16" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_03.xlsx</t>
+          <t xml:space="preserve">N_03.xlsx</t>
         </is>
       </c>
       <c r="C16" s="127" t="inlineStr">
@@ -8427,7 +9116,7 @@
       </c>
       <c r="B17" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_04.xlsx</t>
+          <t xml:space="preserve">N_04.xlsx</t>
         </is>
       </c>
       <c r="C17" s="128" t="inlineStr">
@@ -8449,7 +9138,7 @@
       </c>
       <c r="B18" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_05.xlsx</t>
+          <t xml:space="preserve">N_05.xlsx</t>
         </is>
       </c>
       <c r="C18" s="127" t="inlineStr">
@@ -8471,7 +9160,7 @@
       </c>
       <c r="B19" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_06.xlsx</t>
+          <t xml:space="preserve">N_06.xlsx</t>
         </is>
       </c>
       <c r="C19" s="128" t="inlineStr">
@@ -8493,7 +9182,7 @@
       </c>
       <c r="B20" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_07.xlsx</t>
+          <t xml:space="preserve">N_07.xlsx</t>
         </is>
       </c>
       <c r="C20" s="127" t="inlineStr">
@@ -8515,7 +9204,7 @@
       </c>
       <c r="B21" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_08.xlsx</t>
+          <t xml:space="preserve">N_08.xlsx</t>
         </is>
       </c>
       <c r="C21" s="128" t="inlineStr">
@@ -8537,7 +9226,7 @@
       </c>
       <c r="B22" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_09.xlsx</t>
+          <t xml:space="preserve">N_09.xlsx</t>
         </is>
       </c>
       <c r="C22" s="127" t="inlineStr">
@@ -8749,7 +9438,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valeurs non numériques (NaN / Infini)</t>
+          <t xml:space="preserve">Valeurs non numériques (non-nombres, infinis)</t>
         </is>
       </c>
       <c r="B32" s="127" t="inlineStr">
@@ -8793,7 +9482,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV : PD avec provenance pour chaque client de la watchlist</t>
+          <t xml:space="preserve">RISK OUTLOOK : PD avec provenance pour chaque client de la watchlist</t>
         </is>
       </c>
       <c r="B34" s="127" t="inlineStr">
@@ -8976,7 +9665,7 @@
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">TypeSafe</t>
+          <t xml:space="preserve">Analyse sémantique</t>
         </is>
       </c>
       <c r="B45" s="131" t="inlineStr">
@@ -8990,7 +9679,7 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV</t>
+          <t xml:space="preserve">RISK OUTLOOK</t>
         </is>
       </c>
       <c r="B46" s="132" t="inlineStr">
@@ -9020,7 +9709,7 @@
               <color rgb="FF001B4D"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">COUVERTURE JEV &amp; TYPESAFE</t>
+            <t xml:space="preserve">COUVERTURE RISK OUTLOOK &amp; ANALYSE SÉMANTIQUE</t>
           </r>
           <r>
             <rPr>
@@ -9072,7 +9761,7 @@
       </c>
       <c r="B50" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV · MARKOV / HYBRID</t>
+          <t xml:space="preserve">RISK OUTLOOK · MARKOV / HYBRID</t>
         </is>
       </c>
       <c r="C50" s="127" t="inlineStr">
@@ -9094,7 +9783,7 @@
       </c>
       <c r="B51" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV · EMPIRICAL</t>
+          <t xml:space="preserve">RISK OUTLOOK · EMPIRICAL</t>
         </is>
       </c>
       <c r="C51" s="128" t="inlineStr">
@@ -9116,7 +9805,7 @@
       </c>
       <c r="B52" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV · STRESS / SIMULATED</t>
+          <t xml:space="preserve">RISK OUTLOOK · STRESS / SIMULATED</t>
         </is>
       </c>
       <c r="C52" s="127" t="inlineStr">
@@ -9138,7 +9827,7 @@
       </c>
       <c r="B53" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV · HYBRID (Markov + EWS + expert)</t>
+          <t xml:space="preserve">RISK OUTLOOK · HYBRID (Markov + EWS + expert)</t>
         </is>
       </c>
       <c r="C53" s="128" t="inlineStr">
@@ -9148,7 +9837,7 @@
       </c>
       <c r="D53" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">signaux TypeSafe et APEX en multiplicateurs EXPERT affichés</t>
+          <t xml:space="preserve">signaux Analyse sémantique et APEX en multiplicateurs EXPERT affichés</t>
         </is>
       </c>
     </row>
@@ -9160,7 +9849,7 @@
       </c>
       <c r="B54" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV · recalcul par le code</t>
+          <t xml:space="preserve">RISK OUTLOOK · recalcul par le code</t>
         </is>
       </c>
       <c r="C54" s="127" t="inlineStr">
@@ -9177,130 +9866,372 @@
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motif, crédibilité, incohérence, statut</t>
+          <t xml:space="preserve">Analyses avancées</t>
         </is>
       </c>
       <c r="B55" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">TypeSafe · Choice / Score / Noul</t>
+          <t xml:space="preserve">RISK OUTLOOK · MARKOV / SIMULATED / EMPIRICAL / STRESS</t>
         </is>
       </c>
       <c r="C55" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">✔ 24 dossiers</t>
+          <t xml:space="preserve">✔ actif</t>
         </is>
       </c>
       <c r="D55" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">commentaires gestionnaires (feuille _TYPESAFE)</t>
+          <t xml:space="preserve">structure par terme, temps avant défaut, guérison, IC bootstrap, backtest, stress inverse, sensibilité</t>
         </is>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nature de l'entité, intra-groupe, segment</t>
+          <t xml:space="preserve">Motif, crédibilité, incohérence, statut</t>
         </is>
       </c>
       <c r="B56" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">TypeSafe · Choice / Noul</t>
+          <t xml:space="preserve">Analyse sémantique · Choice / Score / Noul</t>
         </is>
       </c>
       <c r="C56" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">✔ actif</t>
+          <t xml:space="preserve">✔ 30 dossiers</t>
         </is>
       </c>
       <c r="D56" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">noms de clients</t>
+          <t xml:space="preserve">commentaires gestionnaires (feuille _SEMANTIQUE)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Urgence et orientation (re-classement, routage)</t>
+          <t xml:space="preserve">Nature de l'entité, intra-groupe, segment</t>
         </is>
       </c>
       <c r="B57" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">TypeSafe · Score / Choice</t>
+          <t xml:space="preserve">Analyse sémantique · Choice / Noul</t>
         </is>
       </c>
       <c r="C57" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">en attente</t>
+          <t xml:space="preserve">✔ actif</t>
         </is>
       </c>
       <c r="D57" s="128" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacités avancées</t>
+          <t xml:space="preserve">noms de clients</t>
         </is>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auto-cohérence et cohérence du plan</t>
+          <t xml:space="preserve">Urgence et orientation (re-classement, routage)</t>
         </is>
       </c>
       <c r="B58" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">TypeSafe · Noul + Choice croisés</t>
+          <t xml:space="preserve">Analyse sémantique · Score / Choice</t>
         </is>
       </c>
       <c r="C58" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">en attente</t>
+          <t xml:space="preserve">✔ 27 dossiers</t>
         </is>
       </c>
       <c r="D58" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">divergence → revue analyste</t>
+          <t xml:space="preserve">capacités avancées</t>
         </is>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Auto-cohérence et cohérence du plan</t>
+        </is>
+      </c>
+      <c r="B59" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Noul + Choice croisés</t>
+        </is>
+      </c>
+      <c r="C59" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D59" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">divergence → revue analyste</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="19" customHeight="1">
+      <c r="A60" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dates par composants (jour, mois, relatif)</t>
+        </is>
+      </c>
+      <c r="B60" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Choice ; assemblage en code</t>
+        </is>
+      </c>
+      <c r="C60" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D60" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">limite connue du modèle : dates comparées en code</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données personnelles sensibles</t>
+        </is>
+      </c>
+      <c r="B61" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Noul</t>
+        </is>
+      </c>
+      <c r="C61" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D61" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commentaire à anonymiser avant diffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="19" customHeight="1">
+      <c r="A62" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Famille de motif et repli selon la confiance</t>
+        </is>
+      </c>
+      <c r="B62" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Choice hiérarchique</t>
+        </is>
+      </c>
+      <c r="C62" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D62" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">motif détaillé incertain → famille retenue si confiance ≥ 0,9</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Action recommandée (catalogue du code)</t>
+        </is>
+      </c>
+      <c r="B63" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Choice</t>
+        </is>
+      </c>
+      <c r="C63" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D63" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 actions types</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="19" customHeight="1">
+      <c r="A64" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contrôle d'ordre des options</t>
+        </is>
+      </c>
+      <c r="B64" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Choice inversé</t>
+        </is>
+      </c>
+      <c r="C64" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D64" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">divergence → revue analyste</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="19" customHeight="1">
+      <c r="A65" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stabilité (rééchantillonnage)</t>
+        </is>
+      </c>
+      <c r="B65" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · 3 tirages avec sel</t>
+        </is>
+      </c>
+      <c r="C65" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D65" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">instabilité → revue analyste</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stress narratif (8 scénarios macro)</t>
+        </is>
+      </c>
+      <c r="B66" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Noul ; agrégats et PD en code</t>
+        </is>
+      </c>
+      <c r="C66" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ 8 scénario(s) avec exposition</t>
+        </is>
+      </c>
+      <c r="D66" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exposition jugée, montants calculés</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="19" customHeight="1">
+      <c r="A67" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phrase de lecture et ordre des constats</t>
+        </is>
+      </c>
+      <c r="B67" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Score + Choice (portefeuille)</t>
+        </is>
+      </c>
+      <c r="C67" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D67" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">constats calculés par le code</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="19" customHeight="1">
+      <c r="A68" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bénéficiaires potentiellement liés</t>
+        </is>
+      </c>
+      <c r="B68" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Score + Noul (portefeuille)</t>
+        </is>
+      </c>
+      <c r="C68" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ 5 paire(s)</t>
+        </is>
+      </c>
+      <c r="D68" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paires repérées par le code</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Version exacte du modèle et jetons</t>
+        </is>
+      </c>
+      <c r="B69" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Réponse de l'API</t>
+        </is>
+      </c>
+      <c r="C69" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ conservés</t>
+        </is>
+      </c>
+      <c r="D69" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piste d'audit (_SEMANTIQUE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="19" customHeight="1">
+      <c r="A70" s="127" t="inlineStr">
+        <is>
           <t xml:space="preserve">Montants, ratios, classes BCEAO / IFRS 9 / ACTE 7</t>
         </is>
       </c>
-      <c r="B59" s="128" t="inlineStr">
+      <c r="B70" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">Code APEX uniquement</t>
         </is>
       </c>
-      <c r="C59" s="128" t="inlineStr">
+      <c r="C70" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">✔ code</t>
         </is>
       </c>
-      <c r="D59" s="128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jamais confiés à TypeSafe ni à JEV</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Généré le 03/10/2026 13:32:39 · RI 1.0 · APEX Credit Risk OS · source : M_09.xlsx</t>
-        </is>
-      </c>
-      <c r="B61" s="134"/>
-      <c r="C61" s="134"/>
-      <c r="D61" s="134"/>
-      <c r="E61" s="134"/>
-      <c r="F61" s="134"/>
-      <c r="G61" s="134"/>
-      <c r="H61" s="134"/>
-      <c r="I61" s="134"/>
+      <c r="D70" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jamais confiés à Analyse sémantique ni à RISK OUTLOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Généré le 03/10/2026 15:12:05 · RI 1.0 · APEX Credit Risk OS · source : N_09.xlsx</t>
+        </is>
+      </c>
+      <c r="B72" s="134"/>
+      <c r="C72" s="134"/>
+      <c r="D72" s="134"/>
+      <c r="E72" s="134"/>
+      <c r="F72" s="134"/>
+      <c r="G72" s="134"/>
+      <c r="H72" s="134"/>
+      <c r="I72" s="134"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="27">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="A2:F6"/>
@@ -9309,9 +10240,8 @@
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="G6:I6"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:I8"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="F10:G10"/>
@@ -9328,11 +10258,11 @@
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="A48:I48"/>
-    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A72:I72"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A8" location="'EXECUTIVE'!A1" display="EXECUTIVE"/>
-    <hyperlink ref="D8" location="'INSIGHTS'!A1" display="INSIGHTS"/>
+    <hyperlink ref="B8" location="'INSIGHTS'!A1" display="INSIGHTS"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.45" bottom="0.5" header="0.2" footer="0.25"/>
@@ -9341,6 +10271,7 @@
     <oddHeader>&amp;L&amp;8&amp;K003DA5ECOBANK SÉNÉGAL · CREDIT RISK INTELLIGENCE&amp;R&amp;8&amp;K64748BArrêté 30/09/2026</oddHeader>
     <oddFooter>&amp;L&amp;8&amp;K64748BAUDIT · INTERNAL USE ONLY&amp;R&amp;8&amp;K64748BPage &amp;P / &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
